--- a/WB_Election_Results_2026.xlsx
+++ b/WB_Election_Results_2026.xlsx
@@ -4274,7 +4274,7 @@
         <v>23</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>312</v>
@@ -4283,7 +4283,7 @@
         <v>601</v>
       </c>
       <c r="F4">
-        <v>120624</v>
+        <v>128201</v>
       </c>
       <c r="G4" t="s">
         <v>608</v>
@@ -4299,7 +4299,7 @@
         <v>602</v>
       </c>
       <c r="K4">
-        <v>68678</v>
+        <v>71076</v>
       </c>
       <c r="L4" t="s">
         <v>900</v>
@@ -4311,7 +4311,7 @@
         <v>605</v>
       </c>
       <c r="O4">
-        <v>3858</v>
+        <v>4265</v>
       </c>
       <c r="P4" t="s">
         <v>900</v>
@@ -4529,7 +4529,7 @@
         <v>22</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>317</v>
@@ -4538,7 +4538,7 @@
         <v>601</v>
       </c>
       <c r="F9">
-        <v>119316</v>
+        <v>124086</v>
       </c>
       <c r="G9" t="s">
         <v>608</v>
@@ -4554,7 +4554,7 @@
         <v>602</v>
       </c>
       <c r="K9">
-        <v>81685</v>
+        <v>88019</v>
       </c>
       <c r="L9" t="s">
         <v>900</v>
@@ -4566,7 +4566,7 @@
         <v>605</v>
       </c>
       <c r="O9">
-        <v>5069</v>
+        <v>6230</v>
       </c>
       <c r="P9" t="s">
         <v>900</v>
@@ -4577,10 +4577,10 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>318</v>
@@ -4589,7 +4589,7 @@
         <v>601</v>
       </c>
       <c r="F10">
-        <v>110876</v>
+        <v>117331</v>
       </c>
       <c r="G10" t="s">
         <v>608</v>
@@ -4605,7 +4605,7 @@
         <v>602</v>
       </c>
       <c r="K10">
-        <v>78380</v>
+        <v>84312</v>
       </c>
       <c r="L10" t="s">
         <v>900</v>
@@ -4617,7 +4617,7 @@
         <v>605</v>
       </c>
       <c r="O10">
-        <v>3665</v>
+        <v>4081</v>
       </c>
       <c r="P10" t="s">
         <v>900</v>
@@ -4733,7 +4733,7 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>321</v>
@@ -4742,7 +4742,7 @@
         <v>601</v>
       </c>
       <c r="F13">
-        <v>103129</v>
+        <v>110043</v>
       </c>
       <c r="G13" t="s">
         <v>608</v>
@@ -4758,7 +4758,7 @@
         <v>602</v>
       </c>
       <c r="K13">
-        <v>55324</v>
+        <v>57780</v>
       </c>
       <c r="L13" t="s">
         <v>900</v>
@@ -4770,7 +4770,7 @@
         <v>605</v>
       </c>
       <c r="O13">
-        <v>5655</v>
+        <v>5926</v>
       </c>
       <c r="P13" t="s">
         <v>900</v>
@@ -4784,7 +4784,7 @@
         <v>24</v>
       </c>
       <c r="C14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
         <v>322</v>
@@ -4793,7 +4793,7 @@
         <v>601</v>
       </c>
       <c r="F14">
-        <v>120835</v>
+        <v>133451</v>
       </c>
       <c r="G14" t="s">
         <v>608</v>
@@ -4809,7 +4809,7 @@
         <v>602</v>
       </c>
       <c r="K14">
-        <v>83364</v>
+        <v>88055</v>
       </c>
       <c r="L14" t="s">
         <v>900</v>
@@ -4821,7 +4821,7 @@
         <v>605</v>
       </c>
       <c r="O14">
-        <v>5658</v>
+        <v>6117</v>
       </c>
       <c r="P14" t="s">
         <v>900</v>
@@ -4835,7 +4835,7 @@
         <v>19</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
         <v>323</v>
@@ -4844,7 +4844,7 @@
         <v>601</v>
       </c>
       <c r="F15">
-        <v>101950</v>
+        <v>102438</v>
       </c>
       <c r="G15" t="s">
         <v>608</v>
@@ -4860,7 +4860,7 @@
         <v>602</v>
       </c>
       <c r="K15">
-        <v>61034</v>
+        <v>61281</v>
       </c>
       <c r="L15" t="s">
         <v>900</v>
@@ -4872,7 +4872,7 @@
         <v>1193</v>
       </c>
       <c r="O15">
-        <v>3115</v>
+        <v>3121</v>
       </c>
       <c r="P15" t="s">
         <v>900</v>
@@ -6059,7 +6059,7 @@
         <v>17</v>
       </c>
       <c r="C39">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
         <v>347</v>
@@ -6068,10 +6068,10 @@
         <v>602</v>
       </c>
       <c r="F39">
-        <v>82396</v>
+        <v>82791</v>
       </c>
       <c r="G39" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H39">
         <f>F39-K39</f>
@@ -6084,10 +6084,10 @@
         <v>601</v>
       </c>
       <c r="K39">
-        <v>75789</v>
+        <v>76106</v>
       </c>
       <c r="L39" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M39" t="s">
         <v>937</v>
@@ -6096,10 +6096,10 @@
         <v>605</v>
       </c>
       <c r="O39">
-        <v>10092</v>
+        <v>10149</v>
       </c>
       <c r="P39" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -6263,7 +6263,7 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
         <v>351</v>
@@ -6272,7 +6272,7 @@
         <v>602</v>
       </c>
       <c r="F43">
-        <v>84793</v>
+        <v>90090</v>
       </c>
       <c r="G43" t="s">
         <v>608</v>
@@ -6288,7 +6288,7 @@
         <v>601</v>
       </c>
       <c r="K43">
-        <v>82610</v>
+        <v>88258</v>
       </c>
       <c r="L43" t="s">
         <v>900</v>
@@ -6300,7 +6300,7 @@
         <v>603</v>
       </c>
       <c r="O43">
-        <v>8169</v>
+        <v>8313</v>
       </c>
       <c r="P43" t="s">
         <v>900</v>
@@ -7079,7 +7079,7 @@
         <v>21</v>
       </c>
       <c r="C59">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
         <v>367</v>
@@ -7088,10 +7088,10 @@
         <v>601</v>
       </c>
       <c r="F59">
-        <v>85063</v>
+        <v>91201</v>
       </c>
       <c r="G59" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H59">
         <f>F59-K59</f>
@@ -7104,10 +7104,10 @@
         <v>602</v>
       </c>
       <c r="K59">
-        <v>73955</v>
+        <v>80659</v>
       </c>
       <c r="L59" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M59" t="s">
         <v>957</v>
@@ -7116,10 +7116,10 @@
         <v>603</v>
       </c>
       <c r="O59">
-        <v>28749</v>
+        <v>31228</v>
       </c>
       <c r="P59" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -8048,7 +8048,7 @@
         <v>23</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
         <v>385</v>
@@ -8057,10 +8057,10 @@
         <v>601</v>
       </c>
       <c r="F78">
-        <v>97955</v>
+        <v>105234</v>
       </c>
       <c r="G78" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H78">
         <f>F78-K78</f>
@@ -8073,10 +8073,10 @@
         <v>602</v>
       </c>
       <c r="K78">
-        <v>89359</v>
+        <v>95049</v>
       </c>
       <c r="L78" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M78" t="s">
         <v>976</v>
@@ -8085,10 +8085,10 @@
         <v>605</v>
       </c>
       <c r="O78">
-        <v>18673</v>
+        <v>19334</v>
       </c>
       <c r="P78" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -8108,7 +8108,7 @@
         <v>601</v>
       </c>
       <c r="F79">
-        <v>109070</v>
+        <v>110471</v>
       </c>
       <c r="G79" t="s">
         <v>608</v>
@@ -8124,7 +8124,7 @@
         <v>602</v>
       </c>
       <c r="K79">
-        <v>76366</v>
+        <v>77111</v>
       </c>
       <c r="L79" t="s">
         <v>900</v>
@@ -8136,7 +8136,7 @@
         <v>605</v>
       </c>
       <c r="O79">
-        <v>20716</v>
+        <v>20927</v>
       </c>
       <c r="P79" t="s">
         <v>900</v>
@@ -8405,7 +8405,7 @@
         <v>14</v>
       </c>
       <c r="C85">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
         <v>392</v>
@@ -8414,7 +8414,7 @@
         <v>601</v>
       </c>
       <c r="F85">
-        <v>95694</v>
+        <v>105086</v>
       </c>
       <c r="G85" t="s">
         <v>608</v>
@@ -8430,7 +8430,7 @@
         <v>602</v>
       </c>
       <c r="K85">
-        <v>76278</v>
+        <v>81612</v>
       </c>
       <c r="L85" t="s">
         <v>900</v>
@@ -8442,7 +8442,7 @@
         <v>605</v>
       </c>
       <c r="O85">
-        <v>13293</v>
+        <v>14305</v>
       </c>
       <c r="P85" t="s">
         <v>900</v>
@@ -8813,7 +8813,7 @@
         <v>23</v>
       </c>
       <c r="C93">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D93" t="s">
         <v>400</v>
@@ -8822,10 +8822,10 @@
         <v>601</v>
       </c>
       <c r="F93">
-        <v>109798</v>
+        <v>114469</v>
       </c>
       <c r="G93" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H93">
         <f>F93-K93</f>
@@ -8838,10 +8838,10 @@
         <v>602</v>
       </c>
       <c r="K93">
-        <v>75882</v>
+        <v>79677</v>
       </c>
       <c r="L93" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M93" t="s">
         <v>991</v>
@@ -8850,10 +8850,10 @@
         <v>605</v>
       </c>
       <c r="O93">
-        <v>14003</v>
+        <v>15037</v>
       </c>
       <c r="P93" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -8864,7 +8864,7 @@
         <v>22</v>
       </c>
       <c r="C94">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D94" t="s">
         <v>401</v>
@@ -8873,10 +8873,10 @@
         <v>601</v>
       </c>
       <c r="F94">
-        <v>105793</v>
+        <v>107900</v>
       </c>
       <c r="G94" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H94">
         <f>F94-K94</f>
@@ -8889,10 +8889,10 @@
         <v>602</v>
       </c>
       <c r="K94">
-        <v>84375</v>
+        <v>85845</v>
       </c>
       <c r="L94" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M94" t="s">
         <v>992</v>
@@ -8901,10 +8901,10 @@
         <v>605</v>
       </c>
       <c r="O94">
-        <v>12103</v>
+        <v>12370</v>
       </c>
       <c r="P94" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -9128,7 +9128,7 @@
         <v>602</v>
       </c>
       <c r="F99">
-        <v>84354</v>
+        <v>85020</v>
       </c>
       <c r="G99" t="s">
         <v>608</v>
@@ -9144,7 +9144,7 @@
         <v>601</v>
       </c>
       <c r="K99">
-        <v>69357</v>
+        <v>70143</v>
       </c>
       <c r="L99" t="s">
         <v>900</v>
@@ -9156,7 +9156,7 @@
         <v>605</v>
       </c>
       <c r="O99">
-        <v>35240</v>
+        <v>35435</v>
       </c>
       <c r="P99" t="s">
         <v>900</v>
@@ -9527,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D107" t="s">
         <v>414</v>
@@ -9536,7 +9536,7 @@
         <v>601</v>
       </c>
       <c r="F107">
-        <v>53006</v>
+        <v>61564</v>
       </c>
       <c r="G107" t="s">
         <v>608</v>
@@ -9552,7 +9552,7 @@
         <v>602</v>
       </c>
       <c r="K107">
-        <v>43398</v>
+        <v>49779</v>
       </c>
       <c r="L107" t="s">
         <v>900</v>
@@ -9564,7 +9564,7 @@
         <v>1192</v>
       </c>
       <c r="O107">
-        <v>4819</v>
+        <v>6177</v>
       </c>
       <c r="P107" t="s">
         <v>900</v>
@@ -9578,7 +9578,7 @@
         <v>14</v>
       </c>
       <c r="C108">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D108" t="s">
         <v>415</v>
@@ -9587,7 +9587,7 @@
         <v>601</v>
       </c>
       <c r="F108">
-        <v>70647</v>
+        <v>78400</v>
       </c>
       <c r="G108" t="s">
         <v>608</v>
@@ -9603,7 +9603,7 @@
         <v>602</v>
       </c>
       <c r="K108">
-        <v>56681</v>
+        <v>61849</v>
       </c>
       <c r="L108" t="s">
         <v>900</v>
@@ -9615,7 +9615,7 @@
         <v>605</v>
       </c>
       <c r="O108">
-        <v>14027</v>
+        <v>15295</v>
       </c>
       <c r="P108" t="s">
         <v>900</v>
@@ -9629,7 +9629,7 @@
         <v>15</v>
       </c>
       <c r="C109">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D109" t="s">
         <v>416</v>
@@ -9638,10 +9638,10 @@
         <v>601</v>
       </c>
       <c r="F109">
-        <v>75625</v>
+        <v>78466</v>
       </c>
       <c r="G109" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H109">
         <f>F109-K109</f>
@@ -9654,10 +9654,10 @@
         <v>602</v>
       </c>
       <c r="K109">
-        <v>60081</v>
+        <v>62644</v>
       </c>
       <c r="L109" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M109" t="s">
         <v>1006</v>
@@ -9666,10 +9666,10 @@
         <v>605</v>
       </c>
       <c r="O109">
-        <v>9920</v>
+        <v>10197</v>
       </c>
       <c r="P109" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -9782,7 +9782,7 @@
         <v>13</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D112" t="s">
         <v>419</v>
@@ -9791,7 +9791,7 @@
         <v>601</v>
       </c>
       <c r="F112">
-        <v>63812</v>
+        <v>77026</v>
       </c>
       <c r="G112" t="s">
         <v>608</v>
@@ -9807,7 +9807,7 @@
         <v>602</v>
       </c>
       <c r="K112">
-        <v>41245</v>
+        <v>50435</v>
       </c>
       <c r="L112" t="s">
         <v>900</v>
@@ -9819,7 +9819,7 @@
         <v>605</v>
       </c>
       <c r="O112">
-        <v>16965</v>
+        <v>20943</v>
       </c>
       <c r="P112" t="s">
         <v>900</v>
@@ -9935,7 +9935,7 @@
         <v>15</v>
       </c>
       <c r="C115">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D115" t="s">
         <v>422</v>
@@ -9944,10 +9944,10 @@
         <v>601</v>
       </c>
       <c r="F115">
-        <v>92093</v>
+        <v>99181</v>
       </c>
       <c r="G115" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H115">
         <f>F115-K115</f>
@@ -9960,10 +9960,10 @@
         <v>602</v>
       </c>
       <c r="K115">
-        <v>67468</v>
+        <v>73908</v>
       </c>
       <c r="L115" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M115" t="s">
         <v>1012</v>
@@ -9972,10 +9972,10 @@
         <v>605</v>
       </c>
       <c r="O115">
-        <v>18584</v>
+        <v>20576</v>
       </c>
       <c r="P115" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -9986,7 +9986,7 @@
         <v>17</v>
       </c>
       <c r="C116">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D116" t="s">
         <v>423</v>
@@ -9995,7 +9995,7 @@
         <v>602</v>
       </c>
       <c r="F116">
-        <v>84473</v>
+        <v>90558</v>
       </c>
       <c r="G116" t="s">
         <v>608</v>
@@ -10011,7 +10011,7 @@
         <v>601</v>
       </c>
       <c r="K116">
-        <v>71745</v>
+        <v>77779</v>
       </c>
       <c r="L116" t="s">
         <v>900</v>
@@ -10023,7 +10023,7 @@
         <v>605</v>
       </c>
       <c r="O116">
-        <v>24307</v>
+        <v>26833</v>
       </c>
       <c r="P116" t="s">
         <v>900</v>
@@ -10088,7 +10088,7 @@
         <v>14</v>
       </c>
       <c r="C118">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D118" t="s">
         <v>425</v>
@@ -10097,10 +10097,10 @@
         <v>601</v>
       </c>
       <c r="F118">
-        <v>95021</v>
+        <v>101277</v>
       </c>
       <c r="G118" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H118">
         <f>F118-K118</f>
@@ -10113,10 +10113,10 @@
         <v>602</v>
       </c>
       <c r="K118">
-        <v>69676</v>
+        <v>73520</v>
       </c>
       <c r="L118" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M118" t="s">
         <v>1015</v>
@@ -10125,10 +10125,10 @@
         <v>605</v>
       </c>
       <c r="O118">
-        <v>15640</v>
+        <v>16476</v>
       </c>
       <c r="P118" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -10190,7 +10190,7 @@
         <v>23</v>
       </c>
       <c r="C120">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D120" t="s">
         <v>427</v>
@@ -10199,10 +10199,10 @@
         <v>601</v>
       </c>
       <c r="F120">
-        <v>121869</v>
+        <v>122171</v>
       </c>
       <c r="G120" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H120">
         <f>F120-K120</f>
@@ -10215,10 +10215,10 @@
         <v>602</v>
       </c>
       <c r="K120">
-        <v>87200</v>
+        <v>87613</v>
       </c>
       <c r="L120" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M120" t="s">
         <v>1017</v>
@@ -10227,10 +10227,10 @@
         <v>1192</v>
       </c>
       <c r="O120">
-        <v>18652</v>
+        <v>18700</v>
       </c>
       <c r="P120" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -10751,7 +10751,7 @@
         <v>23</v>
       </c>
       <c r="C131">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D131" t="s">
         <v>438</v>
@@ -10760,7 +10760,7 @@
         <v>602</v>
       </c>
       <c r="F131">
-        <v>102624</v>
+        <v>108377</v>
       </c>
       <c r="G131" t="s">
         <v>608</v>
@@ -10776,7 +10776,7 @@
         <v>601</v>
       </c>
       <c r="K131">
-        <v>97237</v>
+        <v>102873</v>
       </c>
       <c r="L131" t="s">
         <v>900</v>
@@ -10788,7 +10788,7 @@
         <v>605</v>
       </c>
       <c r="O131">
-        <v>10754</v>
+        <v>11040</v>
       </c>
       <c r="P131" t="s">
         <v>900</v>
@@ -10955,7 +10955,7 @@
         <v>23</v>
       </c>
       <c r="C135">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
         <v>442</v>
@@ -10964,7 +10964,7 @@
         <v>602</v>
       </c>
       <c r="F135">
-        <v>78994</v>
+        <v>89353</v>
       </c>
       <c r="G135" t="s">
         <v>608</v>
@@ -10980,7 +10980,7 @@
         <v>601</v>
       </c>
       <c r="K135">
-        <v>67505</v>
+        <v>80730</v>
       </c>
       <c r="L135" t="s">
         <v>900</v>
@@ -10992,7 +10992,7 @@
         <v>605</v>
       </c>
       <c r="O135">
-        <v>15163</v>
+        <v>16521</v>
       </c>
       <c r="P135" t="s">
         <v>900</v>
@@ -11006,7 +11006,7 @@
         <v>20</v>
       </c>
       <c r="C136">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D136" t="s">
         <v>443</v>
@@ -11015,7 +11015,7 @@
         <v>602</v>
       </c>
       <c r="F136">
-        <v>79775</v>
+        <v>84668</v>
       </c>
       <c r="G136" t="s">
         <v>608</v>
@@ -11031,7 +11031,7 @@
         <v>601</v>
       </c>
       <c r="K136">
-        <v>77514</v>
+        <v>83344</v>
       </c>
       <c r="L136" t="s">
         <v>900</v>
@@ -11043,7 +11043,7 @@
         <v>606</v>
       </c>
       <c r="O136">
-        <v>18962</v>
+        <v>19431</v>
       </c>
       <c r="P136" t="s">
         <v>900</v>
@@ -11108,7 +11108,7 @@
         <v>18</v>
       </c>
       <c r="C138">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D138" t="s">
         <v>445</v>
@@ -11117,7 +11117,7 @@
         <v>602</v>
       </c>
       <c r="F138">
-        <v>92165</v>
+        <v>100805</v>
       </c>
       <c r="G138" t="s">
         <v>608</v>
@@ -11133,7 +11133,7 @@
         <v>601</v>
       </c>
       <c r="K138">
-        <v>74215</v>
+        <v>79175</v>
       </c>
       <c r="L138" t="s">
         <v>900</v>
@@ -11145,7 +11145,7 @@
         <v>605</v>
       </c>
       <c r="O138">
-        <v>15280</v>
+        <v>16489</v>
       </c>
       <c r="P138" t="s">
         <v>900</v>
@@ -11159,7 +11159,7 @@
         <v>23</v>
       </c>
       <c r="C139">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D139" t="s">
         <v>446</v>
@@ -11168,10 +11168,10 @@
         <v>602</v>
       </c>
       <c r="F139">
-        <v>120329</v>
+        <v>120548</v>
       </c>
       <c r="G139" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H139">
         <f>F139-K139</f>
@@ -11184,10 +11184,10 @@
         <v>601</v>
       </c>
       <c r="K139">
-        <v>79536</v>
+        <v>79883</v>
       </c>
       <c r="L139" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M139" t="s">
         <v>1036</v>
@@ -11196,10 +11196,10 @@
         <v>606</v>
       </c>
       <c r="O139">
-        <v>23904</v>
+        <v>23908</v>
       </c>
       <c r="P139" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -11363,7 +11363,7 @@
         <v>19</v>
       </c>
       <c r="C143">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D143" t="s">
         <v>450</v>
@@ -11372,7 +11372,7 @@
         <v>602</v>
       </c>
       <c r="F143">
-        <v>81718</v>
+        <v>89177</v>
       </c>
       <c r="G143" t="s">
         <v>608</v>
@@ -11388,7 +11388,7 @@
         <v>601</v>
       </c>
       <c r="K143">
-        <v>37230</v>
+        <v>39087</v>
       </c>
       <c r="L143" t="s">
         <v>900</v>
@@ -11400,7 +11400,7 @@
         <v>606</v>
       </c>
       <c r="O143">
-        <v>20600</v>
+        <v>22654</v>
       </c>
       <c r="P143" t="s">
         <v>900</v>
@@ -11516,7 +11516,7 @@
         <v>18</v>
       </c>
       <c r="C146">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D146" t="s">
         <v>453</v>
@@ -11525,7 +11525,7 @@
         <v>601</v>
       </c>
       <c r="F146">
-        <v>105829</v>
+        <v>111016</v>
       </c>
       <c r="G146" t="s">
         <v>608</v>
@@ -11541,7 +11541,7 @@
         <v>602</v>
       </c>
       <c r="K146">
-        <v>103200</v>
+        <v>109975</v>
       </c>
       <c r="L146" t="s">
         <v>900</v>
@@ -11553,7 +11553,7 @@
         <v>605</v>
       </c>
       <c r="O146">
-        <v>10934</v>
+        <v>11718</v>
       </c>
       <c r="P146" t="s">
         <v>900</v>
@@ -11666,10 +11666,10 @@
         <v>163</v>
       </c>
       <c r="B149">
+        <v>18</v>
+      </c>
+      <c r="C149">
         <v>17</v>
-      </c>
-      <c r="C149">
-        <v>16</v>
       </c>
       <c r="D149" t="s">
         <v>456</v>
@@ -11678,7 +11678,7 @@
         <v>606</v>
       </c>
       <c r="F149">
-        <v>119971</v>
+        <v>125427</v>
       </c>
       <c r="G149" t="s">
         <v>608</v>
@@ -11694,7 +11694,7 @@
         <v>602</v>
       </c>
       <c r="K149">
-        <v>88271</v>
+        <v>93353</v>
       </c>
       <c r="L149" t="s">
         <v>900</v>
@@ -11706,7 +11706,7 @@
         <v>601</v>
       </c>
       <c r="O149">
-        <v>27078</v>
+        <v>29267</v>
       </c>
       <c r="P149" t="s">
         <v>900</v>
@@ -11771,7 +11771,7 @@
         <v>26</v>
       </c>
       <c r="C151">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D151" t="s">
         <v>458</v>
@@ -11780,7 +11780,7 @@
         <v>601</v>
       </c>
       <c r="F151">
-        <v>83908</v>
+        <v>88478</v>
       </c>
       <c r="G151" t="s">
         <v>608</v>
@@ -11796,7 +11796,7 @@
         <v>602</v>
       </c>
       <c r="K151">
-        <v>62801</v>
+        <v>66236</v>
       </c>
       <c r="L151" t="s">
         <v>900</v>
@@ -11808,7 +11808,7 @@
         <v>605</v>
       </c>
       <c r="O151">
-        <v>31222</v>
+        <v>33582</v>
       </c>
       <c r="P151" t="s">
         <v>900</v>
@@ -11831,7 +11831,7 @@
         <v>601</v>
       </c>
       <c r="F152">
-        <v>113202</v>
+        <v>114046</v>
       </c>
       <c r="G152" t="s">
         <v>608</v>
@@ -11847,7 +11847,7 @@
         <v>602</v>
       </c>
       <c r="K152">
-        <v>101692</v>
+        <v>102190</v>
       </c>
       <c r="L152" t="s">
         <v>900</v>
@@ -11859,7 +11859,7 @@
         <v>605</v>
       </c>
       <c r="O152">
-        <v>18158</v>
+        <v>18338</v>
       </c>
       <c r="P152" t="s">
         <v>900</v>
@@ -11975,7 +11975,7 @@
         <v>26</v>
       </c>
       <c r="C155">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D155" t="s">
         <v>462</v>
@@ -11984,7 +11984,7 @@
         <v>601</v>
       </c>
       <c r="F155">
-        <v>95839</v>
+        <v>101279</v>
       </c>
       <c r="G155" t="s">
         <v>608</v>
@@ -12000,7 +12000,7 @@
         <v>602</v>
       </c>
       <c r="K155">
-        <v>71608</v>
+        <v>76158</v>
       </c>
       <c r="L155" t="s">
         <v>900</v>
@@ -12012,7 +12012,7 @@
         <v>605</v>
       </c>
       <c r="O155">
-        <v>26798</v>
+        <v>28211</v>
       </c>
       <c r="P155" t="s">
         <v>900</v>
@@ -12485,7 +12485,7 @@
         <v>23</v>
       </c>
       <c r="C165">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D165" t="s">
         <v>472</v>
@@ -12494,7 +12494,7 @@
         <v>602</v>
       </c>
       <c r="F165">
-        <v>88010</v>
+        <v>92591</v>
       </c>
       <c r="G165" t="s">
         <v>608</v>
@@ -12510,7 +12510,7 @@
         <v>601</v>
       </c>
       <c r="K165">
-        <v>59357</v>
+        <v>63496</v>
       </c>
       <c r="L165" t="s">
         <v>900</v>
@@ -12522,7 +12522,7 @@
         <v>605</v>
       </c>
       <c r="O165">
-        <v>9824</v>
+        <v>10289</v>
       </c>
       <c r="P165" t="s">
         <v>900</v>
@@ -12740,7 +12740,7 @@
         <v>15</v>
       </c>
       <c r="C170">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D170" t="s">
         <v>477</v>
@@ -12749,7 +12749,7 @@
         <v>601</v>
       </c>
       <c r="F170">
-        <v>38698</v>
+        <v>44482</v>
       </c>
       <c r="G170" t="s">
         <v>608</v>
@@ -12765,7 +12765,7 @@
         <v>602</v>
       </c>
       <c r="K170">
-        <v>32480</v>
+        <v>34261</v>
       </c>
       <c r="L170" t="s">
         <v>900</v>
@@ -12777,7 +12777,7 @@
         <v>605</v>
       </c>
       <c r="O170">
-        <v>9471</v>
+        <v>9794</v>
       </c>
       <c r="P170" t="s">
         <v>900</v>
@@ -12842,7 +12842,7 @@
         <v>17</v>
       </c>
       <c r="C172">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D172" t="s">
         <v>479</v>
@@ -12851,10 +12851,10 @@
         <v>602</v>
       </c>
       <c r="F172">
-        <v>95459</v>
+        <v>95948</v>
       </c>
       <c r="G172" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H172">
         <f>F172-K172</f>
@@ -12867,10 +12867,10 @@
         <v>601</v>
       </c>
       <c r="K172">
-        <v>79187</v>
+        <v>79865</v>
       </c>
       <c r="L172" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M172" t="s">
         <v>1069</v>
@@ -12879,10 +12879,10 @@
         <v>605</v>
       </c>
       <c r="O172">
-        <v>11259</v>
+        <v>11280</v>
       </c>
       <c r="P172" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -13301,7 +13301,7 @@
         <v>19</v>
       </c>
       <c r="C181">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D181" t="s">
         <v>488</v>
@@ -13310,7 +13310,7 @@
         <v>602</v>
       </c>
       <c r="F181">
-        <v>85355</v>
+        <v>90840</v>
       </c>
       <c r="G181" t="s">
         <v>608</v>
@@ -13326,7 +13326,7 @@
         <v>601</v>
       </c>
       <c r="K181">
-        <v>79798</v>
+        <v>85630</v>
       </c>
       <c r="L181" t="s">
         <v>900</v>
@@ -13338,7 +13338,7 @@
         <v>605</v>
       </c>
       <c r="O181">
-        <v>11350</v>
+        <v>12193</v>
       </c>
       <c r="P181" t="s">
         <v>900</v>
@@ -13412,7 +13412,7 @@
         <v>602</v>
       </c>
       <c r="F183">
-        <v>91090</v>
+        <v>91776</v>
       </c>
       <c r="G183" t="s">
         <v>608</v>
@@ -13428,7 +13428,7 @@
         <v>601</v>
       </c>
       <c r="K183">
-        <v>82754</v>
+        <v>83333</v>
       </c>
       <c r="L183" t="s">
         <v>900</v>
@@ -13440,7 +13440,7 @@
         <v>605</v>
       </c>
       <c r="O183">
-        <v>6657</v>
+        <v>6780</v>
       </c>
       <c r="P183" t="s">
         <v>900</v>
@@ -13556,7 +13556,7 @@
         <v>27</v>
       </c>
       <c r="C186">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D186" t="s">
         <v>493</v>
@@ -13565,10 +13565,10 @@
         <v>601</v>
       </c>
       <c r="F186">
-        <v>79025</v>
+        <v>80458</v>
       </c>
       <c r="G186" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H186">
         <f>F186-K186</f>
@@ -13581,10 +13581,10 @@
         <v>602</v>
       </c>
       <c r="K186">
-        <v>69066</v>
+        <v>70167</v>
       </c>
       <c r="L186" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M186" t="s">
         <v>1083</v>
@@ -13593,10 +13593,10 @@
         <v>605</v>
       </c>
       <c r="O186">
-        <v>49141</v>
+        <v>49812</v>
       </c>
       <c r="P186" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -14117,7 +14117,7 @@
         <v>24</v>
       </c>
       <c r="C197">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D197" t="s">
         <v>504</v>
@@ -14126,7 +14126,7 @@
         <v>601</v>
       </c>
       <c r="F197">
-        <v>88876</v>
+        <v>94001</v>
       </c>
       <c r="G197" t="s">
         <v>608</v>
@@ -14142,7 +14142,7 @@
         <v>602</v>
       </c>
       <c r="K197">
-        <v>84596</v>
+        <v>90312</v>
       </c>
       <c r="L197" t="s">
         <v>900</v>
@@ -14154,7 +14154,7 @@
         <v>606</v>
       </c>
       <c r="O197">
-        <v>10064</v>
+        <v>10806</v>
       </c>
       <c r="P197" t="s">
         <v>900</v>
@@ -14729,7 +14729,7 @@
         <v>22</v>
       </c>
       <c r="C209">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D209" t="s">
         <v>516</v>
@@ -14738,7 +14738,7 @@
         <v>601</v>
       </c>
       <c r="F209">
-        <v>120629</v>
+        <v>121122</v>
       </c>
       <c r="G209" t="s">
         <v>608</v>
@@ -14754,7 +14754,7 @@
         <v>602</v>
       </c>
       <c r="K209">
-        <v>94638</v>
+        <v>95009</v>
       </c>
       <c r="L209" t="s">
         <v>900</v>
@@ -14766,7 +14766,7 @@
         <v>605</v>
       </c>
       <c r="O209">
-        <v>11431</v>
+        <v>11462</v>
       </c>
       <c r="P209" t="s">
         <v>900</v>
@@ -14933,7 +14933,7 @@
         <v>18</v>
       </c>
       <c r="C213">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D213" t="s">
         <v>519</v>
@@ -14942,7 +14942,7 @@
         <v>601</v>
       </c>
       <c r="F213">
-        <v>101905</v>
+        <v>116259</v>
       </c>
       <c r="G213" t="s">
         <v>608</v>
@@ -14958,7 +14958,7 @@
         <v>602</v>
       </c>
       <c r="K213">
-        <v>94846</v>
+        <v>107269</v>
       </c>
       <c r="L213" t="s">
         <v>900</v>
@@ -14970,7 +14970,7 @@
         <v>1197</v>
       </c>
       <c r="O213">
-        <v>4165</v>
+        <v>4590</v>
       </c>
       <c r="P213" t="s">
         <v>900</v>
@@ -15086,7 +15086,7 @@
         <v>22</v>
       </c>
       <c r="C216">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D216" t="s">
         <v>522</v>
@@ -15095,7 +15095,7 @@
         <v>601</v>
       </c>
       <c r="F216">
-        <v>112640</v>
+        <v>120197</v>
       </c>
       <c r="G216" t="s">
         <v>608</v>
@@ -15111,7 +15111,7 @@
         <v>602</v>
       </c>
       <c r="K216">
-        <v>83788</v>
+        <v>88988</v>
       </c>
       <c r="L216" t="s">
         <v>900</v>
@@ -15123,7 +15123,7 @@
         <v>605</v>
       </c>
       <c r="O216">
-        <v>4844</v>
+        <v>5125</v>
       </c>
       <c r="P216" t="s">
         <v>900</v>
@@ -15137,7 +15137,7 @@
         <v>26</v>
       </c>
       <c r="C217">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D217" t="s">
         <v>496</v>
@@ -15146,10 +15146,10 @@
         <v>601</v>
       </c>
       <c r="F217">
-        <v>117390</v>
+        <v>118219</v>
       </c>
       <c r="G217" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H217">
         <f>F217-K217</f>
@@ -15162,10 +15162,10 @@
         <v>602</v>
       </c>
       <c r="K217">
-        <v>86359</v>
+        <v>86747</v>
       </c>
       <c r="L217" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M217" t="s">
         <v>1114</v>
@@ -15174,10 +15174,10 @@
         <v>1197</v>
       </c>
       <c r="O217">
-        <v>3850</v>
+        <v>3868</v>
       </c>
       <c r="P217" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -15554,7 +15554,7 @@
         <v>601</v>
       </c>
       <c r="F225">
-        <v>83833</v>
+        <v>84784</v>
       </c>
       <c r="G225" t="s">
         <v>608</v>
@@ -15570,7 +15570,7 @@
         <v>602</v>
       </c>
       <c r="K225">
-        <v>54798</v>
+        <v>55178</v>
       </c>
       <c r="L225" t="s">
         <v>900</v>
@@ -15582,7 +15582,7 @@
         <v>605</v>
       </c>
       <c r="O225">
-        <v>5145</v>
+        <v>5255</v>
       </c>
       <c r="P225" t="s">
         <v>900</v>
@@ -15698,7 +15698,7 @@
         <v>24</v>
       </c>
       <c r="C228">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D228" t="s">
         <v>533</v>
@@ -15707,7 +15707,7 @@
         <v>601</v>
       </c>
       <c r="F228">
-        <v>114998</v>
+        <v>120138</v>
       </c>
       <c r="G228" t="s">
         <v>608</v>
@@ -15723,7 +15723,7 @@
         <v>602</v>
       </c>
       <c r="K228">
-        <v>97081</v>
+        <v>102383</v>
       </c>
       <c r="L228" t="s">
         <v>900</v>
@@ -15735,7 +15735,7 @@
         <v>1197</v>
       </c>
       <c r="O228">
-        <v>5599</v>
+        <v>6212</v>
       </c>
       <c r="P228" t="s">
         <v>900</v>
@@ -18656,7 +18656,7 @@
         <v>23</v>
       </c>
       <c r="C286">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D286" t="s">
         <v>591</v>
@@ -18665,7 +18665,7 @@
         <v>601</v>
       </c>
       <c r="F286">
-        <v>95683</v>
+        <v>105619</v>
       </c>
       <c r="G286" t="s">
         <v>608</v>
@@ -18681,7 +18681,7 @@
         <v>602</v>
       </c>
       <c r="K286">
-        <v>68150</v>
+        <v>76700</v>
       </c>
       <c r="L286" t="s">
         <v>900</v>
@@ -18693,7 +18693,7 @@
         <v>605</v>
       </c>
       <c r="O286">
-        <v>5184</v>
+        <v>6276</v>
       </c>
       <c r="P286" t="s">
         <v>900</v>
@@ -18707,7 +18707,7 @@
         <v>23</v>
       </c>
       <c r="C287">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D287" t="s">
         <v>592</v>
@@ -18716,7 +18716,7 @@
         <v>602</v>
       </c>
       <c r="F287">
-        <v>104336</v>
+        <v>108544</v>
       </c>
       <c r="G287" t="s">
         <v>608</v>
@@ -18732,7 +18732,7 @@
         <v>601</v>
       </c>
       <c r="K287">
-        <v>90619</v>
+        <v>94678</v>
       </c>
       <c r="L287" t="s">
         <v>900</v>
@@ -18744,7 +18744,7 @@
         <v>606</v>
       </c>
       <c r="O287">
-        <v>16367</v>
+        <v>17422</v>
       </c>
       <c r="P287" t="s">
         <v>900</v>
@@ -18758,7 +18758,7 @@
         <v>24</v>
       </c>
       <c r="C288">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D288" t="s">
         <v>593</v>
@@ -18767,7 +18767,7 @@
         <v>601</v>
       </c>
       <c r="F288">
-        <v>88546</v>
+        <v>91491</v>
       </c>
       <c r="G288" t="s">
         <v>608</v>
@@ -18783,7 +18783,7 @@
         <v>602</v>
       </c>
       <c r="K288">
-        <v>77783</v>
+        <v>84414</v>
       </c>
       <c r="L288" t="s">
         <v>900</v>
@@ -18795,7 +18795,7 @@
         <v>605</v>
       </c>
       <c r="O288">
-        <v>6841</v>
+        <v>7138</v>
       </c>
       <c r="P288" t="s">
         <v>900</v>
@@ -18860,7 +18860,7 @@
         <v>22</v>
       </c>
       <c r="C290">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D290" t="s">
         <v>595</v>
@@ -18869,7 +18869,7 @@
         <v>601</v>
       </c>
       <c r="F290">
-        <v>108425</v>
+        <v>111651</v>
       </c>
       <c r="G290" t="s">
         <v>608</v>
@@ -18885,7 +18885,7 @@
         <v>602</v>
       </c>
       <c r="K290">
-        <v>92653</v>
+        <v>98367</v>
       </c>
       <c r="L290" t="s">
         <v>900</v>
@@ -18897,7 +18897,7 @@
         <v>605</v>
       </c>
       <c r="O290">
-        <v>8378</v>
+        <v>8791</v>
       </c>
       <c r="P290" t="s">
         <v>900</v>
@@ -19013,7 +19013,7 @@
         <v>21</v>
       </c>
       <c r="C293">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D293" t="s">
         <v>598</v>
@@ -19022,7 +19022,7 @@
         <v>602</v>
       </c>
       <c r="F293">
-        <v>70683</v>
+        <v>76609</v>
       </c>
       <c r="G293" t="s">
         <v>608</v>
@@ -19038,7 +19038,7 @@
         <v>601</v>
       </c>
       <c r="K293">
-        <v>37333</v>
+        <v>40273</v>
       </c>
       <c r="L293" t="s">
         <v>900</v>
@@ -19050,7 +19050,7 @@
         <v>605</v>
       </c>
       <c r="O293">
-        <v>16788</v>
+        <v>18152</v>
       </c>
       <c r="P293" t="s">
         <v>900</v>
@@ -19115,7 +19115,7 @@
         <v>22</v>
       </c>
       <c r="C295">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D295" t="s">
         <v>600</v>
@@ -19124,7 +19124,7 @@
         <v>602</v>
       </c>
       <c r="F295">
-        <v>89913</v>
+        <v>94533</v>
       </c>
       <c r="G295" t="s">
         <v>608</v>
@@ -19140,7 +19140,7 @@
         <v>601</v>
       </c>
       <c r="K295">
-        <v>57461</v>
+        <v>58428</v>
       </c>
       <c r="L295" t="s">
         <v>900</v>
@@ -19152,7 +19152,7 @@
         <v>603</v>
       </c>
       <c r="O295">
-        <v>54609</v>
+        <v>57993</v>
       </c>
       <c r="P295" t="s">
         <v>900</v>

--- a/WB_Election_Results_2026.xlsx
+++ b/WB_Election_Results_2026.xlsx
@@ -2708,889 +2708,889 @@
     <t>ANIL KUMAR SINGH</t>
   </si>
   <si>
+    <t>SANJIBUR RAHAMAN (BAPPA)</t>
+  </si>
+  <si>
+    <t>Bharatiya Gorkha Prajatantrik Morcha</t>
+  </si>
+  <si>
+    <t>Lost</t>
+  </si>
+  <si>
+    <t>Trailing</t>
+  </si>
+  <si>
+    <t>KAMAL KUMAR ROY</t>
+  </si>
+  <si>
+    <t>KHAGEN CHANDRA BARMAN</t>
+  </si>
+  <si>
+    <t>PRANAY KARJEE</t>
+  </si>
+  <si>
+    <t>NAZMUL ALOM SARKAR</t>
+  </si>
+  <si>
+    <t>NAMADIPTI ROY ADHIKARY</t>
+  </si>
+  <si>
+    <t>RABIN ROY</t>
+  </si>
+  <si>
+    <t>BIKAS MANDAL</t>
+  </si>
+  <si>
+    <t>AKIK HASSAN</t>
+  </si>
+  <si>
+    <t>DHANANJOY RAVA</t>
+  </si>
+  <si>
+    <t>KISHOR MINJ</t>
+  </si>
+  <si>
+    <t>ANJAN CHIK BARAIK</t>
+  </si>
+  <si>
+    <t>SHYAMAL ROY</t>
+  </si>
+  <si>
+    <t>KAMAL KISHOR ROY</t>
+  </si>
+  <si>
+    <t>SUBHASH LOHAR</t>
+  </si>
+  <si>
+    <t>NIRANJAN ROY</t>
+  </si>
+  <si>
+    <t>SUDEB RAY</t>
+  </si>
+  <si>
+    <t>DEBRAJ BARMAN</t>
+  </si>
+  <si>
+    <t>KHARENDRA NATH ROY</t>
+  </si>
+  <si>
+    <t>MANU ORAON</t>
+  </si>
+  <si>
+    <t>DIL KUMAR ORAON</t>
+  </si>
+  <si>
+    <t>BHERNONE BRITTO LEPCHA</t>
+  </si>
+  <si>
+    <t>AJOY LUCAS EDWARDS</t>
+  </si>
+  <si>
+    <t>BANDANA RAI</t>
+  </si>
+  <si>
+    <t>JHAREN ROY</t>
+  </si>
+  <si>
+    <t>SARADINDU CHAKRABORTY (JOY)</t>
+  </si>
+  <si>
+    <t>NAVANEETA TIRKEY</t>
+  </si>
+  <si>
+    <t>ZAKIR ABEDIN</t>
+  </si>
+  <si>
+    <t>MD. SAMI KHAN</t>
+  </si>
+  <si>
+    <t>MD. GHULAM SARWAR</t>
+  </si>
+  <si>
+    <t>ALI IMRAN RAMZ</t>
+  </si>
+  <si>
+    <t>MD. SAHABUDDIN</t>
+  </si>
+  <si>
+    <t>ANAMIKA ROY</t>
+  </si>
+  <si>
+    <t>HIRU ROY SARKAR</t>
+  </si>
+  <si>
+    <t>MOHIT SENGUPTA</t>
+  </si>
+  <si>
+    <t>AMAL ACHARJEE</t>
+  </si>
+  <si>
+    <t>JYOTIRMOY ROY</t>
+  </si>
+  <si>
+    <t>MOFAZZAL HOSSAIN</t>
+  </si>
+  <si>
+    <t>ARNAB CHOWDHURY</t>
+  </si>
+  <si>
+    <t>BAPPAI HORO</t>
+  </si>
+  <si>
+    <t>BIPLAB BARMAN</t>
+  </si>
+  <si>
+    <t>SUBHASISH PAL (SONA)</t>
+  </si>
+  <si>
+    <t>BASUDEV MURMU</t>
+  </si>
+  <si>
+    <t>KSHITISH CHANDRA SARKAR</t>
+  </si>
+  <si>
+    <t>ASIF MEHBUB</t>
+  </si>
+  <si>
+    <t>MOSTAQUE ALAM</t>
+  </si>
+  <si>
+    <t>ASHIS DAS</t>
+  </si>
+  <si>
+    <t>ALAM MOTTAKIN</t>
+  </si>
+  <si>
+    <t>ANSARUL HAQUE (KALU)</t>
+  </si>
+  <si>
+    <t>BHUPENDRA NATH HALDER (ARJUN)</t>
+  </si>
+  <si>
+    <t>AMBAR MITRA</t>
+  </si>
+  <si>
+    <t>SAYEM CHOWDHURY (BABU)</t>
+  </si>
+  <si>
+    <t>MD. KARIMULLAH HAQUE</t>
+  </si>
+  <si>
+    <t>MAMUNI MANDAL</t>
+  </si>
+  <si>
+    <t>AMIRUL ISLAM</t>
+  </si>
+  <si>
+    <t>SASTI CHARAN GHOSH</t>
+  </si>
+  <si>
+    <t>ALFAJUDDIN BISWAS</t>
+  </si>
+  <si>
+    <t>MOHAMMAD IMRAN ALI</t>
+  </si>
+  <si>
+    <t>SUROJIT PODDAR</t>
+  </si>
+  <si>
+    <t>MASIUR RAHAMAN</t>
+  </si>
+  <si>
+    <t>AMAR KUMAR DAS</t>
+  </si>
+  <si>
+    <t>ANJU BEGAM</t>
+  </si>
+  <si>
+    <t>JAMAL HOSSAIN</t>
+  </si>
+  <si>
+    <t>ALI SIDDIQUE</t>
+  </si>
+  <si>
+    <t>HIRU HALDAR</t>
+  </si>
+  <si>
+    <t>DHRUBAJOTI SAHA</t>
+  </si>
+  <si>
+    <t>SANJIT DAS</t>
+  </si>
+  <si>
+    <t>SHAMIM RANA</t>
+  </si>
+  <si>
+    <t>AZHERUDDIN MD (SIZAR)</t>
+  </si>
+  <si>
+    <t>ATAUR RAHAMAN</t>
+  </si>
+  <si>
+    <t>SHOAIB AHMED</t>
+  </si>
+  <si>
+    <t>NARU GOPAL MUKHERJEE</t>
+  </si>
+  <si>
+    <t>TANMOY BISWAS</t>
+  </si>
+  <si>
+    <t>SAHINA MOMTAZ KHAN</t>
+  </si>
+  <si>
+    <t>BEGAM SAHANAJ</t>
+  </si>
+  <si>
+    <t>NABA KUMAR SARKAR</t>
+  </si>
+  <si>
+    <t>PRABHAS MAJUMDAR</t>
+  </si>
+  <si>
+    <t>SUBODH CHANDRA BISWAS</t>
+  </si>
+  <si>
+    <t>MD SAMSUR ALI MALLICK</t>
+  </si>
+  <si>
+    <t>SABINA IYASMIN SEKH</t>
+  </si>
+  <si>
+    <t>SUKLA SAHA</t>
+  </si>
+  <si>
+    <t>JAKIR  HOSSAIN MONDAL</t>
+  </si>
+  <si>
+    <t>ADWAITA BISWAS</t>
+  </si>
+  <si>
+    <t>SWARNENDU SINHA</t>
+  </si>
+  <si>
+    <t>LABANI JANGI</t>
+  </si>
+  <si>
+    <t>SOUMEN MAHATO</t>
+  </si>
+  <si>
+    <t>DEBASISH  CHAKRABORTY(DEBU)</t>
+  </si>
+  <si>
+    <t>ARCHANA BISWAS</t>
+  </si>
+  <si>
+    <t>MRINAL BISWAS (MINI)</t>
+  </si>
+  <si>
+    <t>ARINDAM BISWAS</t>
+  </si>
+  <si>
+    <t>NARAYAN DAS GUPTA</t>
+  </si>
+  <si>
+    <t>SABUJ DAS</t>
+  </si>
+  <si>
+    <t>SWAPAN KUMAR SARKAR</t>
+  </si>
+  <si>
+    <t>GOUR BISWAS</t>
+  </si>
+  <si>
+    <t>PIJUSH KANTI SAHA</t>
+  </si>
+  <si>
+    <t>ASISH KUMAR SARKAR</t>
+  </si>
+  <si>
+    <t>SAJAL BISWAS</t>
+  </si>
+  <si>
+    <t>BISWAJIT  MONDAL</t>
+  </si>
+  <si>
+    <t>MD. KUTUBUDDIN FATEHE</t>
+  </si>
+  <si>
+    <t>RIJINANDAN BISWAS</t>
+  </si>
+  <si>
+    <t>BISWAJIT MAITY</t>
+  </si>
+  <si>
+    <t>DEBASISH RAKSHIT</t>
+  </si>
+  <si>
+    <t>DEBAJYOTI MAJUMDER</t>
+  </si>
+  <si>
+    <t>ASH NARAYAN SINGH</t>
+  </si>
+  <si>
+    <t>PARVEZ AHMAD KHAN</t>
+  </si>
+  <si>
+    <t>GARGI CHATTERJEE</t>
+  </si>
+  <si>
+    <t>SUMAN RANJAN BANDYOPADHYAY</t>
+  </si>
+  <si>
+    <t>DEBAJYOTI DAS (SUBHO)</t>
+  </si>
+  <si>
+    <t>DIPSITA DHAR</t>
+  </si>
+  <si>
+    <t>KALATAN DASGUPTA</t>
+  </si>
+  <si>
+    <t>MANASH MUKHERJEE</t>
+  </si>
+  <si>
+    <t>SAYANDEEP MITRA</t>
+  </si>
+  <si>
+    <t>MAYUKH BISWAS</t>
+  </si>
+  <si>
+    <t>SAPTARSHI DEB</t>
+  </si>
+  <si>
+    <t>SOUMYAJIT RAHA</t>
+  </si>
+  <si>
+    <t>SUBHAJIT DASGUPTA</t>
+  </si>
+  <si>
+    <t>PRIYANKA BARMAN</t>
+  </si>
+  <si>
+    <t>HEMANTA DAS</t>
+  </si>
+  <si>
+    <t>TARUN KANTI GHOSH</t>
+  </si>
+  <si>
+    <t>BHASKAR KUMAR MONDAL</t>
+  </si>
+  <si>
+    <t>PRATIK MONDAL</t>
+  </si>
+  <si>
+    <t>RABINDRA NATH MAHATA</t>
+  </si>
+  <si>
+    <t>AYNUL AREFIN(RAJU AHMED)</t>
+  </si>
+  <si>
+    <t>KOUSHIK SIDHARTHA</t>
+  </si>
+  <si>
+    <t>SANGITA MANDAL</t>
+  </si>
+  <si>
+    <t>ADWAITYA JOTDAR</t>
+  </si>
+  <si>
+    <t>ASIT ROY</t>
+  </si>
+  <si>
+    <t>RAMSANKAR HALDER</t>
+  </si>
+  <si>
+    <t>SATYARANJAN DAS</t>
+  </si>
+  <si>
+    <t>NARAYAN DAS</t>
+  </si>
+  <si>
+    <t>SWAPAN SINGHA</t>
+  </si>
+  <si>
+    <t>ABDUL MALEQUE MOLLA</t>
+  </si>
+  <si>
+    <t>SAMYA GANGULY</t>
+  </si>
+  <si>
+    <t>ASHOKE KUMAR GAYEN</t>
+  </si>
+  <si>
+    <t>APURBA PRAMANIK (APU)</t>
+  </si>
+  <si>
+    <t>SWAPAN NASKAR</t>
+  </si>
+  <si>
+    <t>PRABIR MONDAL</t>
+  </si>
+  <si>
+    <t>ASHIM SANPUI</t>
+  </si>
+  <si>
+    <t>MD LAHEK ALI</t>
+  </si>
+  <si>
+    <t>CHANDAN SAHA</t>
+  </si>
+  <si>
+    <t>ABDUL AZIZ AL HASSAN</t>
+  </si>
+  <si>
+    <t>SAMAR NAIYA</t>
+  </si>
+  <si>
+    <t>DEBANGSHU PANDA</t>
+  </si>
+  <si>
+    <t>GOUTAM PAL</t>
+  </si>
+  <si>
+    <t>SHYAMAL DAL</t>
+  </si>
+  <si>
+    <t>PARAMITA DASGUPTA</t>
+  </si>
+  <si>
+    <t>JAYANTA GAYEN</t>
+  </si>
+  <si>
+    <t>DIPU DAS</t>
+  </si>
+  <si>
+    <t>BIKASHRANJAN BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>MONALISA SINHA</t>
+  </si>
+  <si>
+    <t>PARTHA PRATIM BISWAS</t>
+  </si>
+  <si>
+    <t>DR NILAY MAJUMDAR</t>
+  </si>
+  <si>
+    <t>NIHAR BHAKTA</t>
+  </si>
+  <si>
+    <t>SAYAN BANERJEE</t>
+  </si>
+  <si>
+    <t>MUJIBAR RAHMAN KAYAL</t>
+  </si>
+  <si>
+    <t>MONIRUL ISLAM</t>
+  </si>
+  <si>
+    <t>FAIYAZ AHMAD KHAN</t>
+  </si>
+  <si>
+    <t>SHRIJEEB BISWAS</t>
+  </si>
+  <si>
+    <t>MANAS GHOSH</t>
+  </si>
+  <si>
+    <t>AFREEN BEGUM</t>
+  </si>
+  <si>
+    <t>SANJAY BASU</t>
+  </si>
+  <si>
+    <t>ABDUL RAUF</t>
+  </si>
+  <si>
+    <t>PARAMITA ROY</t>
+  </si>
+  <si>
+    <t>BHARATRAM TEWARI</t>
+  </si>
+  <si>
+    <t>JHUMA DAS</t>
+  </si>
+  <si>
+    <t>MOUSUMI GHOSH</t>
+  </si>
+  <si>
+    <t>RAJENDRA GUPTA</t>
+  </si>
+  <si>
+    <t>SANKAR MAITRA</t>
+  </si>
+  <si>
+    <t>GAUTAM RAY</t>
+  </si>
+  <si>
+    <t>IMTEAZ AHMED</t>
+  </si>
+  <si>
+    <t>DR. JAGANNATH BHATTACHARYYA</t>
+  </si>
+  <si>
+    <t>ABHIJIT BANERJEE</t>
+  </si>
+  <si>
+    <t>SAMIR MALICK</t>
+  </si>
+  <si>
+    <t>FARID MOLLAH</t>
+  </si>
+  <si>
+    <t>NASIR KHAN</t>
+  </si>
+  <si>
+    <t>ASHOK DALUI</t>
+  </si>
+  <si>
+    <t>AMIRUL ISLAM KHAN</t>
+  </si>
+  <si>
+    <t>ASIT BARAN SAU</t>
+  </si>
+  <si>
+    <t>BHASKAR ROY</t>
+  </si>
+  <si>
+    <t>JOSHIMUDDIN MALLICK</t>
+  </si>
+  <si>
+    <t>SASTHI MAJI</t>
+  </si>
+  <si>
+    <t>NAZIRA KHATUN</t>
+  </si>
+  <si>
+    <t>DULU DAS</t>
+  </si>
+  <si>
+    <t>MINAKSHI MUKHERJEE</t>
+  </si>
+  <si>
+    <t>NABANITA CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>CHANDRANATH BANERJEE</t>
+  </si>
+  <si>
+    <t>DEBASHIS CHATTERJEE</t>
+  </si>
+  <si>
+    <t>Monish Panda</t>
+  </si>
+  <si>
+    <t>SUNIL KUMAR SAHA</t>
+  </si>
+  <si>
+    <t>BIKASH GOLDER</t>
+  </si>
+  <si>
+    <t>AMJAD HOSSAIN SK</t>
+  </si>
+  <si>
+    <t>ANIRBAN SARKAR</t>
+  </si>
+  <si>
+    <t>ASIF ALI</t>
+  </si>
+  <si>
+    <t>SUDIPTA SARKAR</t>
+  </si>
+  <si>
+    <t>SK.MUJAFFAR ALI  (MAJA)</t>
+  </si>
+  <si>
+    <t>RUMA AHIRI</t>
+  </si>
+  <si>
+    <t>ADESH KHAMRUI</t>
+  </si>
+  <si>
+    <t>SANDIP KUMAR SAMANTA</t>
+  </si>
+  <si>
+    <t>BITHIKA PANDIT</t>
+  </si>
+  <si>
+    <t>MUKTARAM DHAWREY</t>
+  </si>
+  <si>
+    <t>SK SADDAM HOSSAIN</t>
+  </si>
+  <si>
+    <t>NABENDU GHARA</t>
+  </si>
+  <si>
+    <t>SK IBRAHIM ALI</t>
+  </si>
+  <si>
+    <t>ABJAL ALI SHA</t>
+  </si>
+  <si>
+    <t>SWAPAN KUMAR BARMAN</t>
+  </si>
+  <si>
+    <t>CHANDAN MAITI</t>
+  </si>
+  <si>
+    <t>PARITOSH PATTANAYAK</t>
+  </si>
+  <si>
+    <t>ASOKE KUMAR PATRA</t>
+  </si>
+  <si>
+    <t>SANTI GOPAL GIRI</t>
+  </si>
+  <si>
+    <t>RITA DAS</t>
+  </si>
+  <si>
+    <t>SAIKAT GIRI</t>
+  </si>
+  <si>
+    <t>SUTANU MAITY</t>
+  </si>
+  <si>
+    <t>PRATIVA RANI KAR SHASMAL</t>
+  </si>
+  <si>
+    <t>HIMANGSHU DAS</t>
+  </si>
+  <si>
+    <t>TEHERAN HOSSAIN</t>
+  </si>
+  <si>
+    <t>ASOKE KUMAR MAITI</t>
+  </si>
+  <si>
+    <t>SUBRATA PANDA</t>
+  </si>
+  <si>
+    <t>SHYAMAL KANTI DASPATTANAYEK</t>
+  </si>
+  <si>
+    <t>DR. PULIN BIHARI BASKE</t>
+  </si>
+  <si>
+    <t>BIKASH SHARANGI</t>
+  </si>
+  <si>
+    <t>ARJUN KUMAR MAHATA</t>
+  </si>
+  <si>
+    <t>MALINA MURMU</t>
+  </si>
+  <si>
+    <t>MADHUSUDAN ROY</t>
+  </si>
+  <si>
+    <t>TAPAS SINHA</t>
+  </si>
+  <si>
+    <t>NAKUL CHANDRA BERA</t>
+  </si>
+  <si>
+    <t>ASHOK SEN</t>
+  </si>
+  <si>
+    <t>SK SAJAHAN ALI</t>
+  </si>
+  <si>
+    <t>SUMIT ADHIKARI</t>
+  </si>
+  <si>
+    <t>RANAJIT PAL</t>
+  </si>
+  <si>
+    <t>SANTI NATH SATICK</t>
+  </si>
+  <si>
+    <t>SUPARNA DOLAI MALLICK</t>
+  </si>
+  <si>
+    <t>GHOSH TAPAN KUMAR</t>
+  </si>
+  <si>
+    <t>MOHAN TUDU</t>
+  </si>
+  <si>
+    <t>GURUPADA MONDAL</t>
+  </si>
+  <si>
+    <t>MANIKUNTAL KHAMRAI</t>
+  </si>
+  <si>
+    <t>RABINDRANATH SARDAR</t>
+  </si>
+  <si>
+    <t>RATHU SINGH</t>
+  </si>
+  <si>
+    <t>NAMITA MAHATO</t>
+  </si>
+  <si>
+    <t>NEPAL CHANDRA MAHATO</t>
+  </si>
+  <si>
+    <t>PHANIBHUSHAN KUMAR</t>
+  </si>
+  <si>
+    <t>SAYANTAN GHOSH</t>
+  </si>
+  <si>
+    <t>SHANTIMANI MURMU</t>
+  </si>
+  <si>
+    <t>BAURI SULEKHA</t>
+  </si>
+  <si>
+    <t>ALOKE KUMAR BAURI</t>
+  </si>
+  <si>
+    <t>GANESH BOURI</t>
+  </si>
+  <si>
+    <t>NANDADULAL BAURI</t>
+  </si>
+  <si>
+    <t>RAJIB LOCHAN KAR</t>
+  </si>
+  <si>
+    <t>DEBLINA HEMBRAM</t>
+  </si>
+  <si>
+    <t>RAMCHANDRA MANDI</t>
+  </si>
+  <si>
+    <t>DEBKANTI MAHANTI</t>
+  </si>
+  <si>
+    <t>AVOYANANDA MUKHOPADHYAY</t>
+  </si>
+  <si>
+    <t>SUJIT CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>ASIT BARAN SARMA</t>
+  </si>
+  <si>
+    <t>TITAS GUPTA</t>
+  </si>
+  <si>
+    <t>RAMCHANDRA ROY</t>
+  </si>
+  <si>
+    <t>JHARNA MALLIK</t>
+  </si>
+  <si>
+    <t>AJIT RAY</t>
+  </si>
+  <si>
+    <t>RAMJIBAN RAY</t>
+  </si>
+  <si>
+    <t>SUDIPTA GUPTA</t>
+  </si>
+  <si>
+    <t>SOMNATH MAJI</t>
+  </si>
+  <si>
+    <t>SAMAR HAZRA</t>
+  </si>
+  <si>
+    <t>SHARMISTHA NAG SAHA</t>
+  </si>
+  <si>
+    <t>KRISHANU BHADRA</t>
+  </si>
+  <si>
+    <t>MAMONI MONDAL (ROY)</t>
+  </si>
+  <si>
+    <t>HASINA KHATUN</t>
+  </si>
+  <si>
+    <t>JIYADUL SEKH</t>
+  </si>
+  <si>
+    <t>PRADIP KUMAR SAHA</t>
+  </si>
+  <si>
+    <t>SANJIB KUMAR DAS</t>
+  </si>
+  <si>
+    <t>JAKIR GAINE</t>
+  </si>
+  <si>
+    <t>MIRAJ ALAM SEKH</t>
+  </si>
+  <si>
+    <t>CHANCHAL KUMAR MAJHI</t>
+  </si>
+  <si>
+    <t>MANIMALA DAS</t>
+  </si>
+  <si>
+    <t>PRABIR KUMAR MONDAL</t>
+  </si>
+  <si>
+    <t>SIMANTA CHATTERJEE</t>
+  </si>
+  <si>
+    <t>PRAVASH SAIN</t>
+  </si>
+  <si>
+    <t>NARAN BAURI</t>
+  </si>
+  <si>
+    <t>MD. SABBIR HUSSAIN</t>
+  </si>
+  <si>
+    <t>SILPI CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>AKHILESH KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>BHABANI CHARAN ACHARYA</t>
+  </si>
+  <si>
+    <t>BISWAJIT BAURI (BAPI)</t>
+  </si>
+  <si>
+    <t>BIJOY BAGDI</t>
+  </si>
+  <si>
+    <t>MOTIUR RAHAMAN</t>
+  </si>
+  <si>
+    <t>BAPI SOREN</t>
+  </si>
+  <si>
+    <t>SHYAMALI PRADHAN</t>
+  </si>
+  <si>
+    <t>MANASA HANSDA</t>
+  </si>
+  <si>
+    <t>DEBU CHUNARI</t>
+  </si>
+  <si>
+    <t>JAYANTA BHALLA</t>
+  </si>
+  <si>
+    <t>SANJIB MALLICK</t>
+  </si>
+  <si>
+    <t>KAMAL HASAN</t>
+  </si>
+  <si>
+    <t>DR ABDUL KARIM</t>
+  </si>
+  <si>
     <t>RINKI GHOSH</t>
-  </si>
-  <si>
-    <t>Bharatiya Gorkha Prajatantrik Morcha</t>
-  </si>
-  <si>
-    <t>Lost</t>
-  </si>
-  <si>
-    <t>Trailing</t>
-  </si>
-  <si>
-    <t>KAMAL KUMAR ROY</t>
-  </si>
-  <si>
-    <t>KHAGEN CHANDRA BARMAN</t>
-  </si>
-  <si>
-    <t>PRANAY KARJEE</t>
-  </si>
-  <si>
-    <t>NAZMUL ALOM SARKAR</t>
-  </si>
-  <si>
-    <t>NAMADIPTI ROY ADHIKARY</t>
-  </si>
-  <si>
-    <t>RABIN ROY</t>
-  </si>
-  <si>
-    <t>BIKAS MANDAL</t>
-  </si>
-  <si>
-    <t>AKIK HASSAN</t>
-  </si>
-  <si>
-    <t>DHANANJOY RAVA</t>
-  </si>
-  <si>
-    <t>KISHOR MINJ</t>
-  </si>
-  <si>
-    <t>ANJAN CHIK BARAIK</t>
-  </si>
-  <si>
-    <t>SHYAMAL ROY</t>
-  </si>
-  <si>
-    <t>KAMAL KISHOR ROY</t>
-  </si>
-  <si>
-    <t>SUBHASH LOHAR</t>
-  </si>
-  <si>
-    <t>NIRANJAN ROY</t>
-  </si>
-  <si>
-    <t>SUDEB RAY</t>
-  </si>
-  <si>
-    <t>DEBRAJ BARMAN</t>
-  </si>
-  <si>
-    <t>KHARENDRA NATH ROY</t>
-  </si>
-  <si>
-    <t>MANU ORAON</t>
-  </si>
-  <si>
-    <t>DIL KUMAR ORAON</t>
-  </si>
-  <si>
-    <t>BHERNONE BRITTO LEPCHA</t>
-  </si>
-  <si>
-    <t>AJOY LUCAS EDWARDS</t>
-  </si>
-  <si>
-    <t>BANDANA RAI</t>
-  </si>
-  <si>
-    <t>JHAREN ROY</t>
-  </si>
-  <si>
-    <t>SARADINDU CHAKRABORTY (JOY)</t>
-  </si>
-  <si>
-    <t>NAVANEETA TIRKEY</t>
-  </si>
-  <si>
-    <t>ZAKIR ABEDIN</t>
-  </si>
-  <si>
-    <t>MD. SAMI KHAN</t>
-  </si>
-  <si>
-    <t>MD. GHULAM SARWAR</t>
-  </si>
-  <si>
-    <t>ALI IMRAN RAMZ</t>
-  </si>
-  <si>
-    <t>MD. SAHABUDDIN</t>
-  </si>
-  <si>
-    <t>ANAMIKA ROY</t>
-  </si>
-  <si>
-    <t>HIRU ROY SARKAR</t>
-  </si>
-  <si>
-    <t>MOHIT SENGUPTA</t>
-  </si>
-  <si>
-    <t>AMAL ACHARJEE</t>
-  </si>
-  <si>
-    <t>JYOTIRMOY ROY</t>
-  </si>
-  <si>
-    <t>MOFAZZAL HOSSAIN</t>
-  </si>
-  <si>
-    <t>ARNAB CHOWDHURY</t>
-  </si>
-  <si>
-    <t>BAPPAI HORO</t>
-  </si>
-  <si>
-    <t>BIPLAB BARMAN</t>
-  </si>
-  <si>
-    <t>SUBHASISH PAL (SONA)</t>
-  </si>
-  <si>
-    <t>BASUDEV MURMU</t>
-  </si>
-  <si>
-    <t>KSHITISH CHANDRA SARKAR</t>
-  </si>
-  <si>
-    <t>ASIF MEHBUB</t>
-  </si>
-  <si>
-    <t>MOSTAQUE ALAM</t>
-  </si>
-  <si>
-    <t>ASHIS DAS</t>
-  </si>
-  <si>
-    <t>ALAM MOTTAKIN</t>
-  </si>
-  <si>
-    <t>ANSARUL HAQUE (KALU)</t>
-  </si>
-  <si>
-    <t>BHUPENDRA NATH HALDER (ARJUN)</t>
-  </si>
-  <si>
-    <t>AMBAR MITRA</t>
-  </si>
-  <si>
-    <t>SAYEM CHOWDHURY (BABU)</t>
-  </si>
-  <si>
-    <t>MD. KARIMULLAH HAQUE</t>
-  </si>
-  <si>
-    <t>MAMUNI MANDAL</t>
-  </si>
-  <si>
-    <t>AMIRUL ISLAM</t>
-  </si>
-  <si>
-    <t>SASTI CHARAN GHOSH</t>
-  </si>
-  <si>
-    <t>ALFAJUDDIN BISWAS</t>
-  </si>
-  <si>
-    <t>MOHAMMAD IMRAN ALI</t>
-  </si>
-  <si>
-    <t>SUROJIT PODDAR</t>
-  </si>
-  <si>
-    <t>MASIUR RAHAMAN</t>
-  </si>
-  <si>
-    <t>AMAR KUMAR DAS</t>
-  </si>
-  <si>
-    <t>ANJU BEGAM</t>
-  </si>
-  <si>
-    <t>JAMAL HOSSAIN</t>
-  </si>
-  <si>
-    <t>ALI SIDDIQUE</t>
-  </si>
-  <si>
-    <t>HIRU HALDAR</t>
-  </si>
-  <si>
-    <t>DHRUBAJOTI SAHA</t>
-  </si>
-  <si>
-    <t>SANJIT DAS</t>
-  </si>
-  <si>
-    <t>SHAMIM RANA</t>
-  </si>
-  <si>
-    <t>AZHERUDDIN MD (SIZAR)</t>
-  </si>
-  <si>
-    <t>ATAUR RAHAMAN</t>
-  </si>
-  <si>
-    <t>SHOAIB AHMED</t>
-  </si>
-  <si>
-    <t>NARU GOPAL MUKHERJEE</t>
-  </si>
-  <si>
-    <t>TANMOY BISWAS</t>
-  </si>
-  <si>
-    <t>SAHINA MOMTAZ KHAN</t>
-  </si>
-  <si>
-    <t>BEGAM SAHANAJ</t>
-  </si>
-  <si>
-    <t>NABA KUMAR SARKAR</t>
-  </si>
-  <si>
-    <t>PRABHAS MAJUMDAR</t>
-  </si>
-  <si>
-    <t>SUBODH CHANDRA BISWAS</t>
-  </si>
-  <si>
-    <t>MD SAMSUR ALI MALLICK</t>
-  </si>
-  <si>
-    <t>SABINA IYASMIN SEKH</t>
-  </si>
-  <si>
-    <t>SUKLA SAHA</t>
-  </si>
-  <si>
-    <t>JAKIR  HOSSAIN MONDAL</t>
-  </si>
-  <si>
-    <t>ADWAITA BISWAS</t>
-  </si>
-  <si>
-    <t>SWARNENDU SINHA</t>
-  </si>
-  <si>
-    <t>LABANI JANGI</t>
-  </si>
-  <si>
-    <t>SOUMEN MAHATO</t>
-  </si>
-  <si>
-    <t>DEBASISH  CHAKRABORTY(DEBU)</t>
-  </si>
-  <si>
-    <t>ARCHANA BISWAS</t>
-  </si>
-  <si>
-    <t>MRINAL BISWAS (MINI)</t>
-  </si>
-  <si>
-    <t>ARINDAM BISWAS</t>
-  </si>
-  <si>
-    <t>NARAYAN DAS GUPTA</t>
-  </si>
-  <si>
-    <t>SABUJ DAS</t>
-  </si>
-  <si>
-    <t>SWAPAN KUMAR SARKAR</t>
-  </si>
-  <si>
-    <t>GOUR BISWAS</t>
-  </si>
-  <si>
-    <t>PIJUSH KANTI SAHA</t>
-  </si>
-  <si>
-    <t>ASISH KUMAR SARKAR</t>
-  </si>
-  <si>
-    <t>SAJAL BISWAS</t>
-  </si>
-  <si>
-    <t>BISWAJIT  MONDAL</t>
-  </si>
-  <si>
-    <t>MD. KUTUBUDDIN FATEHE</t>
-  </si>
-  <si>
-    <t>RIJINANDAN BISWAS</t>
-  </si>
-  <si>
-    <t>BISWAJIT MAITY</t>
-  </si>
-  <si>
-    <t>DEBASISH RAKSHIT</t>
-  </si>
-  <si>
-    <t>DEBAJYOTI MAJUMDER</t>
-  </si>
-  <si>
-    <t>ASH NARAYAN SINGH</t>
-  </si>
-  <si>
-    <t>PARVEZ AHMAD KHAN</t>
-  </si>
-  <si>
-    <t>GARGI CHATTERJEE</t>
-  </si>
-  <si>
-    <t>SUMAN RANJAN BANDYOPADHYAY</t>
-  </si>
-  <si>
-    <t>DEBAJYOTI DAS (SUBHO)</t>
-  </si>
-  <si>
-    <t>DIPSITA DHAR</t>
-  </si>
-  <si>
-    <t>KALATAN DASGUPTA</t>
-  </si>
-  <si>
-    <t>MANASH MUKHERJEE</t>
-  </si>
-  <si>
-    <t>SAYANDEEP MITRA</t>
-  </si>
-  <si>
-    <t>MAYUKH BISWAS</t>
-  </si>
-  <si>
-    <t>SAPTARSHI DEB</t>
-  </si>
-  <si>
-    <t>SOUMYAJIT RAHA</t>
-  </si>
-  <si>
-    <t>SUBHAJIT DASGUPTA</t>
-  </si>
-  <si>
-    <t>PRIYANKA BARMAN</t>
-  </si>
-  <si>
-    <t>HEMANTA DAS</t>
-  </si>
-  <si>
-    <t>TARUN KANTI GHOSH</t>
-  </si>
-  <si>
-    <t>BHASKAR KUMAR MONDAL</t>
-  </si>
-  <si>
-    <t>PRATIK MONDAL</t>
-  </si>
-  <si>
-    <t>RABINDRA NATH MAHATA</t>
-  </si>
-  <si>
-    <t>AYNUL AREFIN(RAJU AHMED)</t>
-  </si>
-  <si>
-    <t>KOUSHIK SIDHARTHA</t>
-  </si>
-  <si>
-    <t>SANGITA MANDAL</t>
-  </si>
-  <si>
-    <t>ADWAITYA JOTDAR</t>
-  </si>
-  <si>
-    <t>ASIT ROY</t>
-  </si>
-  <si>
-    <t>RAMSANKAR HALDER</t>
-  </si>
-  <si>
-    <t>SATYARANJAN DAS</t>
-  </si>
-  <si>
-    <t>NARAYAN DAS</t>
-  </si>
-  <si>
-    <t>SWAPAN SINGHA</t>
-  </si>
-  <si>
-    <t>ABDUL MALEQUE MOLLA</t>
-  </si>
-  <si>
-    <t>SAMYA GANGULY</t>
-  </si>
-  <si>
-    <t>ASHOKE KUMAR GAYEN</t>
-  </si>
-  <si>
-    <t>APURBA PRAMANIK (APU)</t>
-  </si>
-  <si>
-    <t>SWAPAN NASKAR</t>
-  </si>
-  <si>
-    <t>PRABIR MONDAL</t>
-  </si>
-  <si>
-    <t>ASHIM SANPUI</t>
-  </si>
-  <si>
-    <t>MD LAHEK ALI</t>
-  </si>
-  <si>
-    <t>CHANDAN SAHA</t>
-  </si>
-  <si>
-    <t>ABDUL AZIZ AL HASSAN</t>
-  </si>
-  <si>
-    <t>SAMAR NAIYA</t>
-  </si>
-  <si>
-    <t>DEBANGSHU PANDA</t>
-  </si>
-  <si>
-    <t>GOUTAM PAL</t>
-  </si>
-  <si>
-    <t>SHYAMAL DAL</t>
-  </si>
-  <si>
-    <t>PARAMITA DASGUPTA</t>
-  </si>
-  <si>
-    <t>JAYANTA GAYEN</t>
-  </si>
-  <si>
-    <t>DIPU DAS</t>
-  </si>
-  <si>
-    <t>BIKASHRANJAN BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>MONALISA SINHA</t>
-  </si>
-  <si>
-    <t>PARTHA PRATIM BISWAS</t>
-  </si>
-  <si>
-    <t>DR NILAY MAJUMDAR</t>
-  </si>
-  <si>
-    <t>NIHAR BHAKTA</t>
-  </si>
-  <si>
-    <t>SAYAN BANERJEE</t>
-  </si>
-  <si>
-    <t>MUJIBAR RAHMAN KAYAL</t>
-  </si>
-  <si>
-    <t>MONIRUL ISLAM</t>
-  </si>
-  <si>
-    <t>FAIYAZ AHMAD KHAN</t>
-  </si>
-  <si>
-    <t>SHRIJEEB BISWAS</t>
-  </si>
-  <si>
-    <t>MANAS GHOSH</t>
-  </si>
-  <si>
-    <t>AFREEN BEGUM</t>
-  </si>
-  <si>
-    <t>SANJAY BASU</t>
-  </si>
-  <si>
-    <t>ABDUL RAUF</t>
-  </si>
-  <si>
-    <t>PARAMITA ROY</t>
-  </si>
-  <si>
-    <t>BHARATRAM TEWARI</t>
-  </si>
-  <si>
-    <t>JHUMA DAS</t>
-  </si>
-  <si>
-    <t>MOUSUMI GHOSH</t>
-  </si>
-  <si>
-    <t>RAJENDRA GUPTA</t>
-  </si>
-  <si>
-    <t>SANKAR MAITRA</t>
-  </si>
-  <si>
-    <t>GAUTAM RAY</t>
-  </si>
-  <si>
-    <t>IMTEAZ AHMED</t>
-  </si>
-  <si>
-    <t>DR. JAGANNATH BHATTACHARYYA</t>
-  </si>
-  <si>
-    <t>ABHIJIT BANERJEE</t>
-  </si>
-  <si>
-    <t>SAMIR MALICK</t>
-  </si>
-  <si>
-    <t>FARID MOLLAH</t>
-  </si>
-  <si>
-    <t>NASIR KHAN</t>
-  </si>
-  <si>
-    <t>ASHOK DALUI</t>
-  </si>
-  <si>
-    <t>AMIRUL ISLAM KHAN</t>
-  </si>
-  <si>
-    <t>ASIT BARAN SAU</t>
-  </si>
-  <si>
-    <t>BHASKAR ROY</t>
-  </si>
-  <si>
-    <t>JOSHIMUDDIN MALLICK</t>
-  </si>
-  <si>
-    <t>SASTHI MAJI</t>
-  </si>
-  <si>
-    <t>NAZIRA KHATUN</t>
-  </si>
-  <si>
-    <t>DULU DAS</t>
-  </si>
-  <si>
-    <t>MINAKSHI MUKHERJEE</t>
-  </si>
-  <si>
-    <t>NABANITA CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>CHANDRANATH BANERJEE</t>
-  </si>
-  <si>
-    <t>DEBASHIS CHATTERJEE</t>
-  </si>
-  <si>
-    <t>Monish Panda</t>
-  </si>
-  <si>
-    <t>SUNIL KUMAR SAHA</t>
-  </si>
-  <si>
-    <t>BIKASH GOLDER</t>
-  </si>
-  <si>
-    <t>AMJAD HOSSAIN SK</t>
-  </si>
-  <si>
-    <t>ANIRBAN SARKAR</t>
-  </si>
-  <si>
-    <t>ASIF ALI</t>
-  </si>
-  <si>
-    <t>SUDIPTA SARKAR</t>
-  </si>
-  <si>
-    <t>SK.MUJAFFAR ALI  (MAJA)</t>
-  </si>
-  <si>
-    <t>RUMA AHIRI</t>
-  </si>
-  <si>
-    <t>ADESH KHAMRUI</t>
-  </si>
-  <si>
-    <t>SANDIP KUMAR SAMANTA</t>
-  </si>
-  <si>
-    <t>BITHIKA PANDIT</t>
-  </si>
-  <si>
-    <t>MUKTARAM DHAWREY</t>
-  </si>
-  <si>
-    <t>SK SADDAM HOSSAIN</t>
-  </si>
-  <si>
-    <t>NABENDU GHARA</t>
-  </si>
-  <si>
-    <t>SK IBRAHIM ALI</t>
-  </si>
-  <si>
-    <t>ABJAL ALI SHA</t>
-  </si>
-  <si>
-    <t>SWAPAN KUMAR BARMAN</t>
-  </si>
-  <si>
-    <t>CHANDAN MAITI</t>
-  </si>
-  <si>
-    <t>PARITOSH PATTANAYAK</t>
-  </si>
-  <si>
-    <t>ASOKE KUMAR PATRA</t>
-  </si>
-  <si>
-    <t>SANTI GOPAL GIRI</t>
-  </si>
-  <si>
-    <t>RITA DAS</t>
-  </si>
-  <si>
-    <t>SAIKAT GIRI</t>
-  </si>
-  <si>
-    <t>SUTANU MAITY</t>
-  </si>
-  <si>
-    <t>PRATIVA RANI KAR SHASMAL</t>
-  </si>
-  <si>
-    <t>HIMANGSHU DAS</t>
-  </si>
-  <si>
-    <t>TEHERAN HOSSAIN</t>
-  </si>
-  <si>
-    <t>ASOKE KUMAR MAITI</t>
-  </si>
-  <si>
-    <t>SUBRATA PANDA</t>
-  </si>
-  <si>
-    <t>SHYAMAL KANTI DASPATTANAYEK</t>
-  </si>
-  <si>
-    <t>DR. PULIN BIHARI BASKE</t>
-  </si>
-  <si>
-    <t>BIKASH SHARANGI</t>
-  </si>
-  <si>
-    <t>ARJUN KUMAR MAHATA</t>
-  </si>
-  <si>
-    <t>MALINA MURMU</t>
-  </si>
-  <si>
-    <t>MADHUSUDAN ROY</t>
-  </si>
-  <si>
-    <t>TAPAS SINHA</t>
-  </si>
-  <si>
-    <t>NAKUL CHANDRA BERA</t>
-  </si>
-  <si>
-    <t>ASHOK SEN</t>
-  </si>
-  <si>
-    <t>SK SAJAHAN ALI</t>
-  </si>
-  <si>
-    <t>SUMIT ADHIKARI</t>
-  </si>
-  <si>
-    <t>RANAJIT PAL</t>
-  </si>
-  <si>
-    <t>SANTI NATH SATICK</t>
-  </si>
-  <si>
-    <t>SUPARNA DOLAI MALLICK</t>
-  </si>
-  <si>
-    <t>GHOSH TAPAN KUMAR</t>
-  </si>
-  <si>
-    <t>MOHAN TUDU</t>
-  </si>
-  <si>
-    <t>GURUPADA MONDAL</t>
-  </si>
-  <si>
-    <t>MANIKUNTAL KHAMRAI</t>
-  </si>
-  <si>
-    <t>RABINDRANATH SARDAR</t>
-  </si>
-  <si>
-    <t>RATHU SINGH</t>
-  </si>
-  <si>
-    <t>NAMITA MAHATO</t>
-  </si>
-  <si>
-    <t>NEPAL CHANDRA MAHATO</t>
-  </si>
-  <si>
-    <t>PHANIBHUSHAN KUMAR</t>
-  </si>
-  <si>
-    <t>SAYANTAN GHOSH</t>
-  </si>
-  <si>
-    <t>SHANTIMANI MURMU</t>
-  </si>
-  <si>
-    <t>BAURI SULEKHA</t>
-  </si>
-  <si>
-    <t>ALOKE KUMAR BAURI</t>
-  </si>
-  <si>
-    <t>GANESH BOURI</t>
-  </si>
-  <si>
-    <t>NANDADULAL BAURI</t>
-  </si>
-  <si>
-    <t>RAJIB LOCHAN KAR</t>
-  </si>
-  <si>
-    <t>DEBLINA HEMBRAM</t>
-  </si>
-  <si>
-    <t>RAMCHANDRA MANDI</t>
-  </si>
-  <si>
-    <t>DEBKANTI MAHANTI</t>
-  </si>
-  <si>
-    <t>AVOYANANDA MUKHOPADHYAY</t>
-  </si>
-  <si>
-    <t>SUJIT CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>ASIT BARAN SARMA</t>
-  </si>
-  <si>
-    <t>TITAS GUPTA</t>
-  </si>
-  <si>
-    <t>RAMCHANDRA ROY</t>
-  </si>
-  <si>
-    <t>JHARNA MALLIK</t>
-  </si>
-  <si>
-    <t>AJIT RAY</t>
-  </si>
-  <si>
-    <t>RAMJIBAN RAY</t>
-  </si>
-  <si>
-    <t>SUDIPTA GUPTA</t>
-  </si>
-  <si>
-    <t>SOMNATH MAJI</t>
-  </si>
-  <si>
-    <t>SAMAR HAZRA</t>
-  </si>
-  <si>
-    <t>SHARMISTHA NAG SAHA</t>
-  </si>
-  <si>
-    <t>KRISHANU BHADRA</t>
-  </si>
-  <si>
-    <t>MAMONI MONDAL (ROY)</t>
-  </si>
-  <si>
-    <t>HASINA KHATUN</t>
-  </si>
-  <si>
-    <t>JIYADUL SEKH</t>
-  </si>
-  <si>
-    <t>PRADIP KUMAR SAHA</t>
-  </si>
-  <si>
-    <t>SANJIB KUMAR DAS</t>
-  </si>
-  <si>
-    <t>JAKIR GAINE</t>
-  </si>
-  <si>
-    <t>MIRAJ ALAM SEKH</t>
-  </si>
-  <si>
-    <t>CHANCHAL KUMAR MAJHI</t>
-  </si>
-  <si>
-    <t>MANIMALA DAS</t>
-  </si>
-  <si>
-    <t>PRABIR KUMAR MONDAL</t>
-  </si>
-  <si>
-    <t>SIMANTA CHATTERJEE</t>
-  </si>
-  <si>
-    <t>PRAVASH SAIN</t>
-  </si>
-  <si>
-    <t>NARAN BAURI</t>
-  </si>
-  <si>
-    <t>MD. SABBIR HUSSAIN</t>
-  </si>
-  <si>
-    <t>SILPI CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>AKHILESH KUMAR SINGH</t>
-  </si>
-  <si>
-    <t>BHABANI CHARAN ACHARYA</t>
-  </si>
-  <si>
-    <t>BISWAJIT BAURI (BAPI)</t>
-  </si>
-  <si>
-    <t>BIJOY BAGDI</t>
-  </si>
-  <si>
-    <t>MOTIUR RAHAMAN</t>
-  </si>
-  <si>
-    <t>BAPI SOREN</t>
-  </si>
-  <si>
-    <t>SHYAMALI PRADHAN</t>
-  </si>
-  <si>
-    <t>MANASA HANSDA</t>
-  </si>
-  <si>
-    <t>DEBU CHUNARI</t>
-  </si>
-  <si>
-    <t>JAYANTA BHALLA</t>
-  </si>
-  <si>
-    <t>SANJIB MALLICK</t>
-  </si>
-  <si>
-    <t>KAMAL HASAN</t>
-  </si>
-  <si>
-    <t>DR ABDUL KARIM</t>
-  </si>
-  <si>
-    <t>SANJIBUR RAHAMAN (BAPPA)</t>
   </si>
   <si>
     <t>All India Forward Bloc</t>
@@ -4274,7 +4274,7 @@
         <v>23</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>312</v>
@@ -4283,7 +4283,7 @@
         <v>601</v>
       </c>
       <c r="F4">
-        <v>128201</v>
+        <v>135473</v>
       </c>
       <c r="G4" t="s">
         <v>608</v>
@@ -4299,7 +4299,7 @@
         <v>602</v>
       </c>
       <c r="K4">
-        <v>71076</v>
+        <v>73257</v>
       </c>
       <c r="L4" t="s">
         <v>900</v>
@@ -4311,7 +4311,7 @@
         <v>605</v>
       </c>
       <c r="O4">
-        <v>4265</v>
+        <v>4463</v>
       </c>
       <c r="P4" t="s">
         <v>900</v>
@@ -4580,7 +4580,7 @@
         <v>22</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
         <v>318</v>
@@ -4589,10 +4589,10 @@
         <v>601</v>
       </c>
       <c r="F10">
-        <v>117331</v>
+        <v>122525</v>
       </c>
       <c r="G10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H10">
         <f>F10-K10</f>
@@ -4605,10 +4605,10 @@
         <v>602</v>
       </c>
       <c r="K10">
-        <v>84312</v>
+        <v>96068</v>
       </c>
       <c r="L10" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M10" t="s">
         <v>909</v>
@@ -4617,10 +4617,10 @@
         <v>605</v>
       </c>
       <c r="O10">
-        <v>4081</v>
+        <v>4863</v>
       </c>
       <c r="P10" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -4733,7 +4733,7 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
         <v>321</v>
@@ -4742,7 +4742,7 @@
         <v>601</v>
       </c>
       <c r="F13">
-        <v>110043</v>
+        <v>122808</v>
       </c>
       <c r="G13" t="s">
         <v>608</v>
@@ -4758,7 +4758,7 @@
         <v>602</v>
       </c>
       <c r="K13">
-        <v>57780</v>
+        <v>64288</v>
       </c>
       <c r="L13" t="s">
         <v>900</v>
@@ -4770,7 +4770,7 @@
         <v>605</v>
       </c>
       <c r="O13">
-        <v>5926</v>
+        <v>6480</v>
       </c>
       <c r="P13" t="s">
         <v>900</v>
@@ -4784,7 +4784,7 @@
         <v>24</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
         <v>322</v>
@@ -4793,10 +4793,10 @@
         <v>601</v>
       </c>
       <c r="F14">
-        <v>133451</v>
+        <v>134370</v>
       </c>
       <c r="G14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H14">
         <f>F14-K14</f>
@@ -4809,10 +4809,10 @@
         <v>602</v>
       </c>
       <c r="K14">
-        <v>88055</v>
+        <v>88371</v>
       </c>
       <c r="L14" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M14" t="s">
         <v>913</v>
@@ -4821,10 +4821,10 @@
         <v>605</v>
       </c>
       <c r="O14">
-        <v>6117</v>
+        <v>6133</v>
       </c>
       <c r="P14" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -4835,7 +4835,7 @@
         <v>19</v>
       </c>
       <c r="C15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
         <v>323</v>
@@ -4844,10 +4844,10 @@
         <v>601</v>
       </c>
       <c r="F15">
-        <v>102438</v>
+        <v>102488</v>
       </c>
       <c r="G15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H15">
         <f>F15-K15</f>
@@ -4860,10 +4860,10 @@
         <v>602</v>
       </c>
       <c r="K15">
-        <v>61281</v>
+        <v>61578</v>
       </c>
       <c r="L15" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M15" t="s">
         <v>914</v>
@@ -4872,10 +4872,10 @@
         <v>1193</v>
       </c>
       <c r="O15">
-        <v>3121</v>
+        <v>3129</v>
       </c>
       <c r="P15" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -6263,7 +6263,7 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
         <v>351</v>
@@ -6272,10 +6272,10 @@
         <v>602</v>
       </c>
       <c r="F43">
-        <v>90090</v>
+        <v>93098</v>
       </c>
       <c r="G43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H43">
         <f>F43-K43</f>
@@ -6288,10 +6288,10 @@
         <v>601</v>
       </c>
       <c r="K43">
-        <v>88258</v>
+        <v>91112</v>
       </c>
       <c r="L43" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M43" t="s">
         <v>941</v>
@@ -6300,10 +6300,10 @@
         <v>603</v>
       </c>
       <c r="O43">
-        <v>8313</v>
+        <v>8462</v>
       </c>
       <c r="P43" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -8099,7 +8099,7 @@
         <v>23</v>
       </c>
       <c r="C79">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D79" t="s">
         <v>386</v>
@@ -8108,7 +8108,7 @@
         <v>601</v>
       </c>
       <c r="F79">
-        <v>110471</v>
+        <v>111417</v>
       </c>
       <c r="G79" t="s">
         <v>608</v>
@@ -8124,7 +8124,7 @@
         <v>602</v>
       </c>
       <c r="K79">
-        <v>77111</v>
+        <v>82344</v>
       </c>
       <c r="L79" t="s">
         <v>900</v>
@@ -8136,7 +8136,7 @@
         <v>605</v>
       </c>
       <c r="O79">
-        <v>20927</v>
+        <v>24202</v>
       </c>
       <c r="P79" t="s">
         <v>900</v>
@@ -8405,7 +8405,7 @@
         <v>14</v>
       </c>
       <c r="C85">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
         <v>392</v>
@@ -8414,10 +8414,10 @@
         <v>601</v>
       </c>
       <c r="F85">
-        <v>105086</v>
+        <v>108631</v>
       </c>
       <c r="G85" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H85">
         <f>F85-K85</f>
@@ -8430,10 +8430,10 @@
         <v>602</v>
       </c>
       <c r="K85">
-        <v>81612</v>
+        <v>87187</v>
       </c>
       <c r="L85" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M85" t="s">
         <v>983</v>
@@ -8442,10 +8442,10 @@
         <v>605</v>
       </c>
       <c r="O85">
-        <v>14305</v>
+        <v>15612</v>
       </c>
       <c r="P85" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -8507,7 +8507,7 @@
         <v>16</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
         <v>394</v>
@@ -8516,7 +8516,7 @@
         <v>601</v>
       </c>
       <c r="F87">
-        <v>104744</v>
+        <v>116881</v>
       </c>
       <c r="G87" t="s">
         <v>608</v>
@@ -8532,7 +8532,7 @@
         <v>602</v>
       </c>
       <c r="K87">
-        <v>67531</v>
+        <v>72335</v>
       </c>
       <c r="L87" t="s">
         <v>900</v>
@@ -8544,7 +8544,7 @@
         <v>605</v>
       </c>
       <c r="O87">
-        <v>10945</v>
+        <v>11461</v>
       </c>
       <c r="P87" t="s">
         <v>900</v>
@@ -8558,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D88" t="s">
         <v>395</v>
@@ -8567,7 +8567,7 @@
         <v>601</v>
       </c>
       <c r="F88">
-        <v>101958</v>
+        <v>109260</v>
       </c>
       <c r="G88" t="s">
         <v>608</v>
@@ -8583,7 +8583,7 @@
         <v>602</v>
       </c>
       <c r="K88">
-        <v>57749</v>
+        <v>61709</v>
       </c>
       <c r="L88" t="s">
         <v>900</v>
@@ -8595,7 +8595,7 @@
         <v>605</v>
       </c>
       <c r="O88">
-        <v>7088</v>
+        <v>8279</v>
       </c>
       <c r="P88" t="s">
         <v>900</v>
@@ -9017,7 +9017,7 @@
         <v>21</v>
       </c>
       <c r="C97">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
         <v>404</v>
@@ -9026,10 +9026,10 @@
         <v>601</v>
       </c>
       <c r="F97">
-        <v>114795</v>
+        <v>119399</v>
       </c>
       <c r="G97" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H97">
         <f>F97-K97</f>
@@ -9042,10 +9042,10 @@
         <v>602</v>
       </c>
       <c r="K97">
-        <v>78587</v>
+        <v>81585</v>
       </c>
       <c r="L97" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M97" t="s">
         <v>995</v>
@@ -9054,10 +9054,10 @@
         <v>605</v>
       </c>
       <c r="O97">
-        <v>5938</v>
+        <v>6197</v>
       </c>
       <c r="P97" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -9119,7 +9119,7 @@
         <v>16</v>
       </c>
       <c r="C99">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D99" t="s">
         <v>406</v>
@@ -9128,7 +9128,7 @@
         <v>602</v>
       </c>
       <c r="F99">
-        <v>85020</v>
+        <v>92089</v>
       </c>
       <c r="G99" t="s">
         <v>608</v>
@@ -9144,7 +9144,7 @@
         <v>601</v>
       </c>
       <c r="K99">
-        <v>70143</v>
+        <v>77125</v>
       </c>
       <c r="L99" t="s">
         <v>900</v>
@@ -9156,7 +9156,7 @@
         <v>605</v>
       </c>
       <c r="O99">
-        <v>35435</v>
+        <v>37539</v>
       </c>
       <c r="P99" t="s">
         <v>900</v>
@@ -9332,7 +9332,7 @@
         <v>602</v>
       </c>
       <c r="F103">
-        <v>76077</v>
+        <v>76429</v>
       </c>
       <c r="G103" t="s">
         <v>608</v>
@@ -9348,7 +9348,7 @@
         <v>601</v>
       </c>
       <c r="K103">
-        <v>72068</v>
+        <v>72610</v>
       </c>
       <c r="L103" t="s">
         <v>900</v>
@@ -9360,7 +9360,7 @@
         <v>606</v>
       </c>
       <c r="O103">
-        <v>44481</v>
+        <v>44613</v>
       </c>
       <c r="P103" t="s">
         <v>900</v>
@@ -9527,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
         <v>414</v>
@@ -9536,7 +9536,7 @@
         <v>601</v>
       </c>
       <c r="F107">
-        <v>61564</v>
+        <v>71753</v>
       </c>
       <c r="G107" t="s">
         <v>608</v>
@@ -9552,7 +9552,7 @@
         <v>602</v>
       </c>
       <c r="K107">
-        <v>49779</v>
+        <v>57481</v>
       </c>
       <c r="L107" t="s">
         <v>900</v>
@@ -9564,7 +9564,7 @@
         <v>1192</v>
       </c>
       <c r="O107">
-        <v>6177</v>
+        <v>7070</v>
       </c>
       <c r="P107" t="s">
         <v>900</v>
@@ -9587,7 +9587,7 @@
         <v>601</v>
       </c>
       <c r="F108">
-        <v>78400</v>
+        <v>79332</v>
       </c>
       <c r="G108" t="s">
         <v>608</v>
@@ -9603,7 +9603,7 @@
         <v>602</v>
       </c>
       <c r="K108">
-        <v>61849</v>
+        <v>62496</v>
       </c>
       <c r="L108" t="s">
         <v>900</v>
@@ -9615,7 +9615,7 @@
         <v>605</v>
       </c>
       <c r="O108">
-        <v>15295</v>
+        <v>15597</v>
       </c>
       <c r="P108" t="s">
         <v>900</v>
@@ -9728,10 +9728,10 @@
         <v>125</v>
       </c>
       <c r="B111">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C111">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
         <v>418</v>
@@ -9740,10 +9740,10 @@
         <v>601</v>
       </c>
       <c r="F111">
-        <v>91951</v>
+        <v>103284</v>
       </c>
       <c r="G111" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H111">
         <f>F111-K111</f>
@@ -9756,10 +9756,10 @@
         <v>602</v>
       </c>
       <c r="K111">
-        <v>69722</v>
+        <v>76880</v>
       </c>
       <c r="L111" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M111" t="s">
         <v>1008</v>
@@ -9768,10 +9768,10 @@
         <v>605</v>
       </c>
       <c r="O111">
-        <v>34156</v>
+        <v>38428</v>
       </c>
       <c r="P111" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -9782,7 +9782,7 @@
         <v>13</v>
       </c>
       <c r="C112">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D112" t="s">
         <v>419</v>
@@ -9791,10 +9791,10 @@
         <v>601</v>
       </c>
       <c r="F112">
-        <v>77026</v>
+        <v>87977</v>
       </c>
       <c r="G112" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H112">
         <f>F112-K112</f>
@@ -9807,10 +9807,10 @@
         <v>602</v>
       </c>
       <c r="K112">
-        <v>50435</v>
+        <v>59141</v>
       </c>
       <c r="L112" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M112" t="s">
         <v>1009</v>
@@ -9819,10 +9819,10 @@
         <v>605</v>
       </c>
       <c r="O112">
-        <v>20943</v>
+        <v>24032</v>
       </c>
       <c r="P112" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -10751,7 +10751,7 @@
         <v>23</v>
       </c>
       <c r="C131">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D131" t="s">
         <v>438</v>
@@ -10760,10 +10760,10 @@
         <v>602</v>
       </c>
       <c r="F131">
-        <v>108377</v>
+        <v>117164</v>
       </c>
       <c r="G131" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H131">
         <f>F131-K131</f>
@@ -10776,10 +10776,10 @@
         <v>601</v>
       </c>
       <c r="K131">
-        <v>102873</v>
+        <v>112291</v>
       </c>
       <c r="L131" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M131" t="s">
         <v>1028</v>
@@ -10788,10 +10788,10 @@
         <v>605</v>
       </c>
       <c r="O131">
-        <v>11040</v>
+        <v>11491</v>
       </c>
       <c r="P131" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -10955,7 +10955,7 @@
         <v>23</v>
       </c>
       <c r="C135">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D135" t="s">
         <v>442</v>
@@ -10964,7 +10964,7 @@
         <v>602</v>
       </c>
       <c r="F135">
-        <v>89353</v>
+        <v>93881</v>
       </c>
       <c r="G135" t="s">
         <v>608</v>
@@ -10980,7 +10980,7 @@
         <v>601</v>
       </c>
       <c r="K135">
-        <v>80730</v>
+        <v>86407</v>
       </c>
       <c r="L135" t="s">
         <v>900</v>
@@ -10992,7 +10992,7 @@
         <v>605</v>
       </c>
       <c r="O135">
-        <v>16521</v>
+        <v>17156</v>
       </c>
       <c r="P135" t="s">
         <v>900</v>
@@ -11015,7 +11015,7 @@
         <v>602</v>
       </c>
       <c r="F136">
-        <v>84668</v>
+        <v>85157</v>
       </c>
       <c r="G136" t="s">
         <v>608</v>
@@ -11031,7 +11031,7 @@
         <v>601</v>
       </c>
       <c r="K136">
-        <v>83344</v>
+        <v>83956</v>
       </c>
       <c r="L136" t="s">
         <v>900</v>
@@ -11043,7 +11043,7 @@
         <v>606</v>
       </c>
       <c r="O136">
-        <v>19431</v>
+        <v>19483</v>
       </c>
       <c r="P136" t="s">
         <v>900</v>
@@ -11108,7 +11108,7 @@
         <v>18</v>
       </c>
       <c r="C138">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D138" t="s">
         <v>445</v>
@@ -11117,7 +11117,7 @@
         <v>602</v>
       </c>
       <c r="F138">
-        <v>100805</v>
+        <v>109166</v>
       </c>
       <c r="G138" t="s">
         <v>608</v>
@@ -11133,7 +11133,7 @@
         <v>601</v>
       </c>
       <c r="K138">
-        <v>79175</v>
+        <v>83335</v>
       </c>
       <c r="L138" t="s">
         <v>900</v>
@@ -11145,7 +11145,7 @@
         <v>605</v>
       </c>
       <c r="O138">
-        <v>16489</v>
+        <v>17622</v>
       </c>
       <c r="P138" t="s">
         <v>900</v>
@@ -11363,7 +11363,7 @@
         <v>19</v>
       </c>
       <c r="C143">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D143" t="s">
         <v>450</v>
@@ -11372,7 +11372,7 @@
         <v>602</v>
       </c>
       <c r="F143">
-        <v>89177</v>
+        <v>100474</v>
       </c>
       <c r="G143" t="s">
         <v>608</v>
@@ -11388,7 +11388,7 @@
         <v>601</v>
       </c>
       <c r="K143">
-        <v>39087</v>
+        <v>45102</v>
       </c>
       <c r="L143" t="s">
         <v>900</v>
@@ -11400,7 +11400,7 @@
         <v>606</v>
       </c>
       <c r="O143">
-        <v>22654</v>
+        <v>27261</v>
       </c>
       <c r="P143" t="s">
         <v>900</v>
@@ -11669,7 +11669,7 @@
         <v>18</v>
       </c>
       <c r="C149">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D149" t="s">
         <v>456</v>
@@ -11678,10 +11678,10 @@
         <v>606</v>
       </c>
       <c r="F149">
-        <v>125427</v>
+        <v>126555</v>
       </c>
       <c r="G149" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H149">
         <f>F149-K149</f>
@@ -11694,10 +11694,10 @@
         <v>602</v>
       </c>
       <c r="K149">
-        <v>93353</v>
+        <v>94467</v>
       </c>
       <c r="L149" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M149" t="s">
         <v>1046</v>
@@ -11706,10 +11706,10 @@
         <v>601</v>
       </c>
       <c r="O149">
-        <v>29267</v>
+        <v>30177</v>
       </c>
       <c r="P149" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -11771,7 +11771,7 @@
         <v>26</v>
       </c>
       <c r="C151">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D151" t="s">
         <v>458</v>
@@ -11780,7 +11780,7 @@
         <v>601</v>
       </c>
       <c r="F151">
-        <v>88478</v>
+        <v>92412</v>
       </c>
       <c r="G151" t="s">
         <v>608</v>
@@ -11796,7 +11796,7 @@
         <v>602</v>
       </c>
       <c r="K151">
-        <v>66236</v>
+        <v>69307</v>
       </c>
       <c r="L151" t="s">
         <v>900</v>
@@ -11808,7 +11808,7 @@
         <v>605</v>
       </c>
       <c r="O151">
-        <v>33582</v>
+        <v>35450</v>
       </c>
       <c r="P151" t="s">
         <v>900</v>
@@ -11822,7 +11822,7 @@
         <v>22</v>
       </c>
       <c r="C152">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D152" t="s">
         <v>459</v>
@@ -11831,10 +11831,10 @@
         <v>601</v>
       </c>
       <c r="F152">
-        <v>114046</v>
+        <v>119824</v>
       </c>
       <c r="G152" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H152">
         <f>F152-K152</f>
@@ -11847,10 +11847,10 @@
         <v>602</v>
       </c>
       <c r="K152">
-        <v>102190</v>
+        <v>110017</v>
       </c>
       <c r="L152" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M152" t="s">
         <v>1049</v>
@@ -11859,10 +11859,10 @@
         <v>605</v>
       </c>
       <c r="O152">
-        <v>18338</v>
+        <v>19744</v>
       </c>
       <c r="P152" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -11975,7 +11975,7 @@
         <v>26</v>
       </c>
       <c r="C155">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D155" t="s">
         <v>462</v>
@@ -11984,10 +11984,10 @@
         <v>601</v>
       </c>
       <c r="F155">
-        <v>101279</v>
+        <v>113171</v>
       </c>
       <c r="G155" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H155">
         <f>F155-K155</f>
@@ -12000,10 +12000,10 @@
         <v>602</v>
       </c>
       <c r="K155">
-        <v>76158</v>
+        <v>88472</v>
       </c>
       <c r="L155" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M155" t="s">
         <v>1052</v>
@@ -12012,10 +12012,10 @@
         <v>605</v>
       </c>
       <c r="O155">
-        <v>28211</v>
+        <v>30676</v>
       </c>
       <c r="P155" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -12230,7 +12230,7 @@
         <v>20</v>
       </c>
       <c r="C160">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D160" t="s">
         <v>467</v>
@@ -12239,7 +12239,7 @@
         <v>601</v>
       </c>
       <c r="F160">
-        <v>54386</v>
+        <v>60954</v>
       </c>
       <c r="G160" t="s">
         <v>608</v>
@@ -12255,7 +12255,7 @@
         <v>602</v>
       </c>
       <c r="K160">
-        <v>53832</v>
+        <v>54728</v>
       </c>
       <c r="L160" t="s">
         <v>900</v>
@@ -12267,7 +12267,7 @@
         <v>605</v>
       </c>
       <c r="O160">
-        <v>2705</v>
+        <v>2820</v>
       </c>
       <c r="P160" t="s">
         <v>900</v>
@@ -12485,7 +12485,7 @@
         <v>23</v>
       </c>
       <c r="C165">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D165" t="s">
         <v>472</v>
@@ -12494,10 +12494,10 @@
         <v>602</v>
       </c>
       <c r="F165">
-        <v>92591</v>
+        <v>93757</v>
       </c>
       <c r="G165" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H165">
         <f>F165-K165</f>
@@ -12510,10 +12510,10 @@
         <v>601</v>
       </c>
       <c r="K165">
-        <v>63496</v>
+        <v>65181</v>
       </c>
       <c r="L165" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M165" t="s">
         <v>1062</v>
@@ -12522,10 +12522,10 @@
         <v>605</v>
       </c>
       <c r="O165">
-        <v>10289</v>
+        <v>10525</v>
       </c>
       <c r="P165" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -13310,7 +13310,7 @@
         <v>602</v>
       </c>
       <c r="F181">
-        <v>90840</v>
+        <v>91442</v>
       </c>
       <c r="G181" t="s">
         <v>608</v>
@@ -13326,7 +13326,7 @@
         <v>601</v>
       </c>
       <c r="K181">
-        <v>85630</v>
+        <v>86335</v>
       </c>
       <c r="L181" t="s">
         <v>900</v>
@@ -13338,7 +13338,7 @@
         <v>605</v>
       </c>
       <c r="O181">
-        <v>12193</v>
+        <v>12317</v>
       </c>
       <c r="P181" t="s">
         <v>900</v>
@@ -13403,7 +13403,7 @@
         <v>14</v>
       </c>
       <c r="C183">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D183" t="s">
         <v>490</v>
@@ -13412,7 +13412,7 @@
         <v>602</v>
       </c>
       <c r="F183">
-        <v>91776</v>
+        <v>100333</v>
       </c>
       <c r="G183" t="s">
         <v>608</v>
@@ -13428,7 +13428,7 @@
         <v>601</v>
       </c>
       <c r="K183">
-        <v>83333</v>
+        <v>88401</v>
       </c>
       <c r="L183" t="s">
         <v>900</v>
@@ -13440,7 +13440,7 @@
         <v>605</v>
       </c>
       <c r="O183">
-        <v>6780</v>
+        <v>7578</v>
       </c>
       <c r="P183" t="s">
         <v>900</v>
@@ -14066,7 +14066,7 @@
         <v>23</v>
       </c>
       <c r="C196">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D196" t="s">
         <v>503</v>
@@ -14075,7 +14075,7 @@
         <v>601</v>
       </c>
       <c r="F196">
-        <v>91426</v>
+        <v>96953</v>
       </c>
       <c r="G196" t="s">
         <v>608</v>
@@ -14091,7 +14091,7 @@
         <v>602</v>
       </c>
       <c r="K196">
-        <v>91110</v>
+        <v>95765</v>
       </c>
       <c r="L196" t="s">
         <v>900</v>
@@ -14103,7 +14103,7 @@
         <v>605</v>
       </c>
       <c r="O196">
-        <v>17175</v>
+        <v>17542</v>
       </c>
       <c r="P196" t="s">
         <v>900</v>
@@ -14117,7 +14117,7 @@
         <v>24</v>
       </c>
       <c r="C197">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D197" t="s">
         <v>504</v>
@@ -14126,7 +14126,7 @@
         <v>601</v>
       </c>
       <c r="F197">
-        <v>94001</v>
+        <v>102500</v>
       </c>
       <c r="G197" t="s">
         <v>608</v>
@@ -14142,7 +14142,7 @@
         <v>602</v>
       </c>
       <c r="K197">
-        <v>90312</v>
+        <v>99706</v>
       </c>
       <c r="L197" t="s">
         <v>900</v>
@@ -14154,7 +14154,7 @@
         <v>606</v>
       </c>
       <c r="O197">
-        <v>10806</v>
+        <v>11562</v>
       </c>
       <c r="P197" t="s">
         <v>900</v>
@@ -14576,7 +14576,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D206" t="s">
         <v>513</v>
@@ -14585,7 +14585,7 @@
         <v>601</v>
       </c>
       <c r="F206">
-        <v>107524</v>
+        <v>117861</v>
       </c>
       <c r="G206" t="s">
         <v>608</v>
@@ -14601,7 +14601,7 @@
         <v>602</v>
       </c>
       <c r="K206">
-        <v>74758</v>
+        <v>82808</v>
       </c>
       <c r="L206" t="s">
         <v>900</v>
@@ -14613,7 +14613,7 @@
         <v>606</v>
       </c>
       <c r="O206">
-        <v>7586</v>
+        <v>7888</v>
       </c>
       <c r="P206" t="s">
         <v>900</v>
@@ -14729,7 +14729,7 @@
         <v>22</v>
       </c>
       <c r="C209">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D209" t="s">
         <v>516</v>
@@ -14738,10 +14738,10 @@
         <v>601</v>
       </c>
       <c r="F209">
-        <v>121122</v>
+        <v>121584</v>
       </c>
       <c r="G209" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H209">
         <f>F209-K209</f>
@@ -14754,10 +14754,10 @@
         <v>602</v>
       </c>
       <c r="K209">
-        <v>95009</v>
+        <v>95346</v>
       </c>
       <c r="L209" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M209" t="s">
         <v>1106</v>
@@ -14766,10 +14766,10 @@
         <v>605</v>
       </c>
       <c r="O209">
-        <v>11462</v>
+        <v>11490</v>
       </c>
       <c r="P209" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -14933,7 +14933,7 @@
         <v>18</v>
       </c>
       <c r="C213">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D213" t="s">
         <v>519</v>
@@ -14942,10 +14942,10 @@
         <v>601</v>
       </c>
       <c r="F213">
-        <v>116259</v>
+        <v>116589</v>
       </c>
       <c r="G213" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H213">
         <f>F213-K213</f>
@@ -14958,10 +14958,10 @@
         <v>602</v>
       </c>
       <c r="K213">
-        <v>107269</v>
+        <v>107538</v>
       </c>
       <c r="L213" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M213" t="s">
         <v>1110</v>
@@ -14970,10 +14970,10 @@
         <v>1197</v>
       </c>
       <c r="O213">
-        <v>4590</v>
+        <v>4595</v>
       </c>
       <c r="P213" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -15086,7 +15086,7 @@
         <v>22</v>
       </c>
       <c r="C216">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D216" t="s">
         <v>522</v>
@@ -15095,7 +15095,7 @@
         <v>601</v>
       </c>
       <c r="F216">
-        <v>120197</v>
+        <v>125212</v>
       </c>
       <c r="G216" t="s">
         <v>608</v>
@@ -15111,7 +15111,7 @@
         <v>602</v>
       </c>
       <c r="K216">
-        <v>88988</v>
+        <v>94041</v>
       </c>
       <c r="L216" t="s">
         <v>900</v>
@@ -15123,7 +15123,7 @@
         <v>605</v>
       </c>
       <c r="O216">
-        <v>5125</v>
+        <v>5265</v>
       </c>
       <c r="P216" t="s">
         <v>900</v>
@@ -15545,7 +15545,7 @@
         <v>20</v>
       </c>
       <c r="C225">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D225" t="s">
         <v>530</v>
@@ -15554,7 +15554,7 @@
         <v>601</v>
       </c>
       <c r="F225">
-        <v>84784</v>
+        <v>88512</v>
       </c>
       <c r="G225" t="s">
         <v>608</v>
@@ -15570,7 +15570,7 @@
         <v>602</v>
       </c>
       <c r="K225">
-        <v>55178</v>
+        <v>57413</v>
       </c>
       <c r="L225" t="s">
         <v>900</v>
@@ -15582,7 +15582,7 @@
         <v>605</v>
       </c>
       <c r="O225">
-        <v>5255</v>
+        <v>5376</v>
       </c>
       <c r="P225" t="s">
         <v>900</v>
@@ -15698,7 +15698,7 @@
         <v>24</v>
       </c>
       <c r="C228">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D228" t="s">
         <v>533</v>
@@ -15707,10 +15707,10 @@
         <v>601</v>
       </c>
       <c r="F228">
-        <v>120138</v>
+        <v>124189</v>
       </c>
       <c r="G228" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H228">
         <f>F228-K228</f>
@@ -15723,10 +15723,10 @@
         <v>602</v>
       </c>
       <c r="K228">
-        <v>102383</v>
+        <v>105709</v>
       </c>
       <c r="L228" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M228" t="s">
         <v>1125</v>
@@ -15735,10 +15735,10 @@
         <v>1197</v>
       </c>
       <c r="O228">
-        <v>6212</v>
+        <v>6423</v>
       </c>
       <c r="P228" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -17687,7 +17687,7 @@
         <v>16</v>
       </c>
       <c r="C267">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D267" t="s">
         <v>572</v>
@@ -17696,7 +17696,7 @@
         <v>602</v>
       </c>
       <c r="F267">
-        <v>64220</v>
+        <v>74796</v>
       </c>
       <c r="G267" t="s">
         <v>608</v>
@@ -17712,7 +17712,7 @@
         <v>601</v>
       </c>
       <c r="K267">
-        <v>57141</v>
+        <v>60328</v>
       </c>
       <c r="L267" t="s">
         <v>900</v>
@@ -17724,7 +17724,7 @@
         <v>605</v>
       </c>
       <c r="O267">
-        <v>11245</v>
+        <v>12361</v>
       </c>
       <c r="P267" t="s">
         <v>900</v>
@@ -18656,7 +18656,7 @@
         <v>23</v>
       </c>
       <c r="C286">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D286" t="s">
         <v>591</v>
@@ -18665,7 +18665,7 @@
         <v>601</v>
       </c>
       <c r="F286">
-        <v>105619</v>
+        <v>117754</v>
       </c>
       <c r="G286" t="s">
         <v>608</v>
@@ -18681,7 +18681,7 @@
         <v>602</v>
       </c>
       <c r="K286">
-        <v>76700</v>
+        <v>83964</v>
       </c>
       <c r="L286" t="s">
         <v>900</v>
@@ -18693,7 +18693,7 @@
         <v>605</v>
       </c>
       <c r="O286">
-        <v>6276</v>
+        <v>7152</v>
       </c>
       <c r="P286" t="s">
         <v>900</v>
@@ -18716,7 +18716,7 @@
         <v>602</v>
       </c>
       <c r="F287">
-        <v>108544</v>
+        <v>109333</v>
       </c>
       <c r="G287" t="s">
         <v>608</v>
@@ -18732,7 +18732,7 @@
         <v>601</v>
       </c>
       <c r="K287">
-        <v>94678</v>
+        <v>95979</v>
       </c>
       <c r="L287" t="s">
         <v>900</v>
@@ -18744,7 +18744,7 @@
         <v>606</v>
       </c>
       <c r="O287">
-        <v>17422</v>
+        <v>17526</v>
       </c>
       <c r="P287" t="s">
         <v>900</v>
@@ -18758,7 +18758,7 @@
         <v>24</v>
       </c>
       <c r="C288">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D288" t="s">
         <v>593</v>
@@ -18767,7 +18767,7 @@
         <v>601</v>
       </c>
       <c r="F288">
-        <v>91491</v>
+        <v>96177</v>
       </c>
       <c r="G288" t="s">
         <v>608</v>
@@ -18783,7 +18783,7 @@
         <v>602</v>
       </c>
       <c r="K288">
-        <v>84414</v>
+        <v>89529</v>
       </c>
       <c r="L288" t="s">
         <v>900</v>
@@ -18795,7 +18795,7 @@
         <v>605</v>
       </c>
       <c r="O288">
-        <v>7138</v>
+        <v>7278</v>
       </c>
       <c r="P288" t="s">
         <v>900</v>
@@ -18857,10 +18857,10 @@
         <v>304</v>
       </c>
       <c r="B290">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C290">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D290" t="s">
         <v>595</v>
@@ -18869,10 +18869,10 @@
         <v>601</v>
       </c>
       <c r="F290">
-        <v>111651</v>
+        <v>115054</v>
       </c>
       <c r="G290" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H290">
         <f>F290-K290</f>
@@ -18885,10 +18885,10 @@
         <v>602</v>
       </c>
       <c r="K290">
-        <v>98367</v>
+        <v>104748</v>
       </c>
       <c r="L290" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M290" t="s">
         <v>1186</v>
@@ -18897,10 +18897,10 @@
         <v>605</v>
       </c>
       <c r="O290">
-        <v>8791</v>
+        <v>9478</v>
       </c>
       <c r="P290" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -19013,7 +19013,7 @@
         <v>21</v>
       </c>
       <c r="C293">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D293" t="s">
         <v>598</v>
@@ -19022,7 +19022,7 @@
         <v>602</v>
       </c>
       <c r="F293">
-        <v>76609</v>
+        <v>81389</v>
       </c>
       <c r="G293" t="s">
         <v>608</v>
@@ -19038,7 +19038,7 @@
         <v>601</v>
       </c>
       <c r="K293">
-        <v>40273</v>
+        <v>43919</v>
       </c>
       <c r="L293" t="s">
         <v>900</v>
@@ -19050,7 +19050,7 @@
         <v>605</v>
       </c>
       <c r="O293">
-        <v>18152</v>
+        <v>19309</v>
       </c>
       <c r="P293" t="s">
         <v>900</v>
@@ -19064,7 +19064,7 @@
         <v>20</v>
       </c>
       <c r="C294">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D294" t="s">
         <v>599</v>
@@ -19073,7 +19073,7 @@
         <v>602</v>
       </c>
       <c r="F294">
-        <v>61610</v>
+        <v>65787</v>
       </c>
       <c r="G294" t="s">
         <v>608</v>
@@ -19089,7 +19089,7 @@
         <v>601</v>
       </c>
       <c r="K294">
-        <v>54691</v>
+        <v>59048</v>
       </c>
       <c r="L294" t="s">
         <v>900</v>
@@ -19101,7 +19101,7 @@
         <v>603</v>
       </c>
       <c r="O294">
-        <v>27393</v>
+        <v>29045</v>
       </c>
       <c r="P294" t="s">
         <v>900</v>
@@ -19115,7 +19115,7 @@
         <v>22</v>
       </c>
       <c r="C295">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D295" t="s">
         <v>600</v>
@@ -19124,10 +19124,10 @@
         <v>602</v>
       </c>
       <c r="F295">
-        <v>94533</v>
+        <v>96902</v>
       </c>
       <c r="G295" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H295">
         <f>F295-K295</f>
@@ -19137,25 +19137,25 @@
         <v>897</v>
       </c>
       <c r="J295" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K295">
-        <v>58428</v>
+        <v>59197</v>
       </c>
       <c r="L295" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M295" t="s">
         <v>1191</v>
       </c>
       <c r="N295" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="O295">
-        <v>57993</v>
+        <v>58664</v>
       </c>
       <c r="P295" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>

--- a/WB_Election_Results_2026.xlsx
+++ b/WB_Election_Results_2026.xlsx
@@ -1796,822 +1796,825 @@
     <t>CHANDRANATH SINHA</t>
   </si>
   <si>
+    <t>BIDHAN CHANDRA MAJHI</t>
+  </si>
+  <si>
+    <t>DEBASIS OJHA (HAKU DA)</t>
+  </si>
+  <si>
+    <t>KRISHNA KANTA SAHA</t>
+  </si>
+  <si>
+    <t>DUDH KUMAR MONDAL</t>
+  </si>
+  <si>
+    <t>DHRUBA SAHA</t>
+  </si>
+  <si>
+    <t>FAYEZUL HAQUE (KAJAL SK)</t>
+  </si>
+  <si>
+    <t>RAJENDRA PRASAD SINGH(RAJU SINGH)</t>
+  </si>
+  <si>
+    <t>DR. MOSARRAF HOSSAIN</t>
+  </si>
+  <si>
+    <t>Bharatiya Janata Party</t>
+  </si>
+  <si>
+    <t>All India Trinamool Congress</t>
+  </si>
+  <si>
+    <t>Indian National Congress</t>
+  </si>
+  <si>
+    <t>Aam Janata Unnayan party</t>
+  </si>
+  <si>
+    <t>Communist Party of India (Marxist)</t>
+  </si>
+  <si>
+    <t>All India Secular Front</t>
+  </si>
+  <si>
+    <t>Won</t>
+  </si>
+  <si>
+    <t>Leading</t>
+  </si>
+  <si>
+    <t>ADHIKARY PARESH CHANDRA</t>
+  </si>
+  <si>
+    <t>DR. SABLU BARMAN</t>
+  </si>
+  <si>
+    <t>PARTHA PRATIM RAY</t>
+  </si>
+  <si>
+    <t>AVIJIT DE BHOWMIK</t>
+  </si>
+  <si>
+    <t>HARIHAR DAS</t>
+  </si>
+  <si>
+    <t>ASHUTOSH BARMA</t>
+  </si>
+  <si>
+    <t>UDAYAN GUHA</t>
+  </si>
+  <si>
+    <t>SAILENDRA NATH BARMA</t>
+  </si>
+  <si>
+    <t>SHIBSANKAR PAUL</t>
+  </si>
+  <si>
+    <t>RAJEEV TIRKEY</t>
+  </si>
+  <si>
+    <t>BIRENDRA BARA (ORAON)</t>
+  </si>
+  <si>
+    <t>SUMAN KANJILAL</t>
+  </si>
+  <si>
+    <t>SUBHASH CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>JAYPRAKASH TOPPO</t>
+  </si>
+  <si>
+    <t>NIRMAL CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>RAMMOHAN RAY</t>
+  </si>
+  <si>
+    <t>KRISHNA DAS</t>
+  </si>
+  <si>
+    <t>SWAPNA BARMAN</t>
+  </si>
+  <si>
+    <t>RANJAN SIL SHARMA</t>
+  </si>
+  <si>
+    <t>BULU CHIK BARAIK</t>
+  </si>
+  <si>
+    <t>SANJAY KUJUR</t>
+  </si>
+  <si>
+    <t>RUDEN SADA LEPCHA</t>
+  </si>
+  <si>
+    <t>BIJOY KUMAR RAI</t>
+  </si>
+  <si>
+    <t>AMAR LAMA</t>
+  </si>
+  <si>
+    <t>SHANKAR MALAKAR</t>
+  </si>
+  <si>
+    <t>GOUTAM DEB</t>
+  </si>
+  <si>
+    <t>REENA TOPNO EKKA</t>
+  </si>
+  <si>
+    <t>SANKAR ADHIKARI</t>
+  </si>
+  <si>
+    <t>CHITRAJIT ROY</t>
+  </si>
+  <si>
+    <t>SARAJIT BISWAS</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR JAIN</t>
+  </si>
+  <si>
+    <t>GOUTAM PAUL</t>
+  </si>
+  <si>
+    <t>SATYAJIT BARMAN</t>
+  </si>
+  <si>
+    <t>NITAI BAISHYA</t>
+  </si>
+  <si>
+    <t>KRISHNA KALYANI</t>
+  </si>
+  <si>
+    <t>SABITA BARMAN</t>
+  </si>
+  <si>
+    <t>REKHA ROY</t>
+  </si>
+  <si>
+    <t>SUBHENDU SARKAR</t>
+  </si>
+  <si>
+    <t>ARPITA GHOSH</t>
+  </si>
+  <si>
+    <t>CHINTAMANI BIHA</t>
+  </si>
+  <si>
+    <t>Goutam Das</t>
+  </si>
+  <si>
+    <t>DEBABRATA MAJUMDER</t>
+  </si>
+  <si>
+    <t>AMAL KISKU</t>
+  </si>
+  <si>
+    <t>PRASENJIT DAS</t>
+  </si>
+  <si>
+    <t>RATAN DAS</t>
+  </si>
+  <si>
+    <t>MAUSAM B NOOR</t>
+  </si>
+  <si>
+    <t>ABISHEK SINGHANIA</t>
+  </si>
+  <si>
+    <t>KABITA MANDAL</t>
+  </si>
+  <si>
+    <t>LIPIKA BARMAN GHOSH</t>
+  </si>
+  <si>
+    <t>ASIS KUNDU (PATA)</t>
+  </si>
+  <si>
+    <t>NIBARAN GHOSH</t>
+  </si>
+  <si>
+    <t>ABDUL HANNAN</t>
+  </si>
+  <si>
+    <t>CHANDANA SARKAR</t>
+  </si>
+  <si>
+    <t>SUNIL CHOWDHURI</t>
+  </si>
+  <si>
+    <t>MD NAJME ALAM</t>
+  </si>
+  <si>
+    <t>MAHABIR GHOSH</t>
+  </si>
+  <si>
+    <t>JAKIR HOSSAIN</t>
+  </si>
+  <si>
+    <t>NASIR SAIKH</t>
+  </si>
+  <si>
+    <t>TAPAS KUMAR CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>TOUHIDUR RAHAMAN SUMAN</t>
+  </si>
+  <si>
+    <t>MAHAMUDAL HASAN</t>
+  </si>
+  <si>
+    <t>ABDUL SOUMIK HOSSAIN</t>
+  </si>
+  <si>
+    <t>SHAONI SINGHA ROY</t>
+  </si>
+  <si>
+    <t>PRONAB CHANDRA DAS</t>
+  </si>
+  <si>
+    <t>ASHIS MARJIT</t>
+  </si>
+  <si>
+    <t>PROTIMA RAJAK</t>
+  </si>
+  <si>
+    <t>APURBA SARKAR (DAVID)</t>
+  </si>
+  <si>
+    <t>ANAMIKA GHOSH</t>
+  </si>
+  <si>
+    <t>BAPAN GHOSH</t>
+  </si>
+  <si>
+    <t>RABIUL ALAM CHOWDHURY</t>
+  </si>
+  <si>
+    <t>ADHIR RANJAN CHOWDHURY</t>
+  </si>
+  <si>
+    <t>BIJOY SEKH</t>
+  </si>
+  <si>
+    <t>RANA MANDAL</t>
+  </si>
+  <si>
+    <t>IANUS ALI SARKAR</t>
+  </si>
+  <si>
+    <t>SOHAM CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>DILIP KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>ANIMA DUTTA</t>
+  </si>
+  <si>
+    <t>KALLOL KHAN</t>
+  </si>
+  <si>
+    <t>SAIKAT SARKAR</t>
+  </si>
+  <si>
+    <t>SOMNATH DUTTA</t>
+  </si>
+  <si>
+    <t>PUNDARIKAKSHYA SAHA</t>
+  </si>
+  <si>
+    <t>UJJAL BISWAS</t>
+  </si>
+  <si>
+    <t>BRAJAKISHORE GOSWAMI</t>
+  </si>
+  <si>
+    <t>TAPAS KUMAR GHOSH</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>BARNALI DEY ROY</t>
+  </si>
+  <si>
+    <t>SOUGATA KUMAR BURMAN</t>
+  </si>
+  <si>
+    <t>SUBHANKAR SINGHA (JISHU)</t>
+  </si>
+  <si>
+    <t>DR. ATINDRA NATH MONDAL</t>
+  </si>
+  <si>
+    <t>DR. RAJIB BISWAS.</t>
+  </si>
+  <si>
+    <t>MADHUPARNA THAKUR</t>
+  </si>
+  <si>
+    <t>BISWAJIT DAS</t>
+  </si>
+  <si>
+    <t>RITUPARNA ADDHYA</t>
+  </si>
+  <si>
+    <t>NAROTTAM BISWAS</t>
+  </si>
+  <si>
+    <t>TARAK SAHA</t>
+  </si>
+  <si>
+    <t>SUKRITI KUMAR SARKAR</t>
+  </si>
+  <si>
+    <t>JYOTI PRIYA MALLICK</t>
+  </si>
+  <si>
+    <t>NARAYAN GOSWAMI</t>
+  </si>
+  <si>
+    <t>ARINDAM DEY</t>
+  </si>
+  <si>
+    <t>SUBODH ADHIKARY</t>
+  </si>
+  <si>
+    <t>SANAT DEY</t>
+  </si>
+  <si>
+    <t>AMIT GUPTA</t>
+  </si>
+  <si>
+    <t>SOMENATH SHYAM ICHINI</t>
+  </si>
+  <si>
+    <t>TRINANKUR BHATTACHARJEE</t>
+  </si>
+  <si>
+    <t>RAJ CHAKRABORTY (RAJU)</t>
+  </si>
+  <si>
+    <t>DEVADEEP PUROHIT</t>
+  </si>
+  <si>
+    <t>CHANDRIMA BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>TIRTHANKAR GHOSH</t>
+  </si>
+  <si>
+    <t>ARUP CHOUDHURY (PULAK)</t>
+  </si>
+  <si>
+    <t>SAYANTIKA BANERJEE</t>
+  </si>
+  <si>
+    <t>BRATYABRATA BASU</t>
+  </si>
+  <si>
+    <t>PIYUSH KANODIA</t>
+  </si>
+  <si>
+    <t>SUJIT BOSE</t>
+  </si>
+  <si>
+    <t>ADITI MUNSHI</t>
+  </si>
+  <si>
+    <t>RATHIN GHOSH</t>
+  </si>
+  <si>
+    <t>SABYASACHI DUTTA</t>
+  </si>
+  <si>
+    <t>MD MOFIDUL HOQUE SAHAJI MINTU</t>
+  </si>
+  <si>
+    <t>PIYARUL ISLAM</t>
+  </si>
+  <si>
+    <t>RUDRENDRA PATRA</t>
+  </si>
+  <si>
+    <t>JHARNA SARDAR</t>
+  </si>
+  <si>
+    <t>DR. SOURYA BANERJEE</t>
+  </si>
+  <si>
+    <t>MD. MUSA KAREMULLA</t>
+  </si>
+  <si>
+    <t>ANANDA SARKAR</t>
+  </si>
+  <si>
+    <t>SUBRATA MONDAL</t>
+  </si>
+  <si>
+    <t>BIKASH SARDAR</t>
+  </si>
+  <si>
+    <t>MADHABI MAHALDER</t>
+  </si>
+  <si>
+    <t>ASIT KUMAR HALDAR</t>
+  </si>
+  <si>
+    <t>MANTURAM PAKHIRA</t>
+  </si>
+  <si>
+    <t>BANKIM CHANDRA HAZRA</t>
+  </si>
+  <si>
+    <t>ABANI NASKAR</t>
+  </si>
+  <si>
+    <t>PALASH RANA</t>
+  </si>
+  <si>
+    <t>MALLIKA PAIK W/O - ASHOK PAIK</t>
+  </si>
+  <si>
+    <t>ALOKE HALDER</t>
+  </si>
+  <si>
+    <t>TUMPA SARDAR</t>
+  </si>
+  <si>
+    <t>Prasanta Bayen</t>
+  </si>
+  <si>
+    <t>ARABUL ISLAM</t>
+  </si>
+  <si>
+    <t>BISWAJIT PAUL</t>
+  </si>
+  <si>
+    <t>UTTAM KUMAR BANIK</t>
+  </si>
+  <si>
+    <t>GOURSUNDAR GHOSH</t>
+  </si>
+  <si>
+    <t>DIPAK KUMAR HALDER</t>
+  </si>
+  <si>
+    <t>JAHANGIR KHAN</t>
+  </si>
+  <si>
+    <t>SOMASHREE BETAL</t>
+  </si>
+  <si>
+    <t>ABHIJIT SARDAR</t>
+  </si>
+  <si>
+    <t>ARUNDHUTI MAITRA(LOVELY)</t>
+  </si>
+  <si>
+    <t>SAOKAT MOLLA</t>
+  </si>
+  <si>
+    <t>BANERJEE SANDIP</t>
+  </si>
+  <si>
+    <t>DEBABRATA MAJUMDAR (MALAY)</t>
+  </si>
+  <si>
+    <t>FIRDOUSI BEGAM</t>
+  </si>
+  <si>
+    <t>AROOP BISWAS</t>
+  </si>
+  <si>
+    <t>SUBHASISH CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>RATNA CHATTERJEE</t>
+  </si>
+  <si>
+    <t>TAMANATH BHOWMICK</t>
+  </si>
+  <si>
+    <t>DR TARUN KUMAR ADAK</t>
+  </si>
+  <si>
+    <t>BIR BAHADUR SINGH</t>
+  </si>
+  <si>
+    <t>RAKESH SINGH</t>
+  </si>
+  <si>
+    <t>MAMATA BANERJEE</t>
+  </si>
+  <si>
+    <t>DEBASISH KUMAR (DEBA)</t>
+  </si>
+  <si>
+    <t>SHATORUPA</t>
+  </si>
+  <si>
+    <t>SANTOSH KUMAR PATHAK</t>
+  </si>
+  <si>
+    <t>DR. PRIYANKA TIBREWAL</t>
+  </si>
+  <si>
+    <t>PARTHA CHAUDHURY</t>
+  </si>
+  <si>
+    <t>VIJAY UPADHYAY</t>
+  </si>
+  <si>
+    <t>SHASHI PANJA</t>
+  </si>
+  <si>
+    <t>SHRREYA PANDE</t>
+  </si>
+  <si>
+    <t>ATIN GHOSH</t>
+  </si>
+  <si>
+    <t>KAILASH KUMAR MISHRA</t>
+  </si>
+  <si>
+    <t>GAUTAM CHOWDHURY</t>
+  </si>
+  <si>
+    <t>BIPLAB KUMAR MANDAL</t>
+  </si>
+  <si>
+    <t>DR. RANA CHATTERJEE</t>
+  </si>
+  <si>
+    <t>SHYAMAL KUMAR HATI</t>
+  </si>
+  <si>
+    <t>BARNALI DHALI NASKAR</t>
+  </si>
+  <si>
+    <t>RANJAN PAUL</t>
+  </si>
+  <si>
+    <t>RUDRA PROSAD BANERJEE</t>
+  </si>
+  <si>
+    <t>BIMAL KUMAR DAS</t>
+  </si>
+  <si>
+    <t>SWAMI MANGALANANDA PURI</t>
+  </si>
+  <si>
+    <t>NADEBASI JANA</t>
+  </si>
+  <si>
+    <t>PRAMANSHU RANA</t>
+  </si>
+  <si>
+    <t>SUKANTA KUMAR PAUL</t>
+  </si>
+  <si>
+    <t>PROBHAKAR PANDIT</t>
+  </si>
+  <si>
+    <t>SUBIR CHATTERJEE (TINKAI)</t>
+  </si>
+  <si>
+    <t>GOBINDA HAZRA</t>
+  </si>
+  <si>
+    <t>SIRSANYA BANDOPADHYAY</t>
+  </si>
+  <si>
+    <t>TANMOY GHOSH</t>
+  </si>
+  <si>
+    <t>ARINDAM GUIN (BUBAI)</t>
+  </si>
+  <si>
+    <t>BECHARAM MANNA</t>
+  </si>
+  <si>
+    <t>Indranil Sen</t>
+  </si>
+  <si>
+    <t>DEBANGSHU BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>RANJAN DHARA</t>
+  </si>
+  <si>
+    <t>SAMIR CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>BIDESH RANJAN BOSE</t>
+  </si>
+  <si>
+    <t>DEBASISH MUKHERJEE</t>
+  </si>
+  <si>
+    <t>SNEHASIS CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>KARABI MANNA</t>
+  </si>
+  <si>
+    <t>BARNALI DAS</t>
+  </si>
+  <si>
+    <t>RAMENDU SINHARAY</t>
+  </si>
+  <si>
+    <t>PARTHA HAZARI</t>
+  </si>
+  <si>
+    <t>BAG MITA</t>
+  </si>
+  <si>
+    <t>DR. NIRMAL MAJI</t>
+  </si>
+  <si>
+    <t>PALASH KUMAR ROY</t>
+  </si>
+  <si>
+    <t>DIPENDRA NARAYAN ROY</t>
+  </si>
+  <si>
+    <t>ASHIM KUMAR MAJI</t>
+  </si>
+  <si>
+    <t>SIRAJ KHAN</t>
+  </si>
+  <si>
+    <t>CHANDAN MONDAL</t>
+  </si>
+  <si>
+    <t>SUKUMAR DE</t>
+  </si>
+  <si>
+    <t>TILAK KUMAR CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>TAPASI MONDAL</t>
+  </si>
+  <si>
+    <t>PABITRA KAR</t>
+  </si>
+  <si>
+    <t>UTTAM BARIK</t>
+  </si>
+  <si>
+    <t>PIJUS KANTI PANDA</t>
+  </si>
+  <si>
+    <t>DEBASIS BHUNYA</t>
+  </si>
+  <si>
+    <t>MANAB KUMAR PARUA</t>
+  </si>
+  <si>
+    <t>RABIN CHANDRA MANDAL</t>
+  </si>
+  <si>
+    <t>TARUN KUMAR JANA</t>
+  </si>
+  <si>
+    <t>AKHIL GIRI</t>
+  </si>
+  <si>
+    <t>TARUN KUMAR MAITY</t>
+  </si>
+  <si>
+    <t>MANIK MAITI</t>
+  </si>
+  <si>
+    <t>DULAL MURMU</t>
+  </si>
+  <si>
+    <t>AJIT MAHATA</t>
+  </si>
+  <si>
+    <t>MONGAL SAREN</t>
+  </si>
+  <si>
+    <t>RAMJIBAN MANDI</t>
+  </si>
+  <si>
+    <t>PRADIP SARKAR</t>
+  </si>
+  <si>
+    <t>PRATIBHA MAITI</t>
+  </si>
+  <si>
+    <t>MANAS RANJAN BHUNIA</t>
+  </si>
+  <si>
+    <t>AJIT MAITY</t>
+  </si>
+  <si>
+    <t>TAPAN BHUYA</t>
+  </si>
+  <si>
+    <t>RAJIB BANERJEE</t>
+  </si>
+  <si>
+    <t>ASHIS HUDAIT</t>
+  </si>
+  <si>
+    <t>SHYAMALI SARDAR</t>
+  </si>
+  <si>
+    <t>DOLOI SURJYA KANTA</t>
+  </si>
+  <si>
+    <t>UTTARA SINGHA (HAZRA)</t>
+  </si>
+  <si>
+    <t>SRIKANTA MAHATA</t>
+  </si>
+  <si>
+    <t>SUVENDU SAMANTA</t>
+  </si>
+  <si>
+    <t>SUJOY HAZRA</t>
+  </si>
+  <si>
+    <t>BIRBAHA HANSDA</t>
+  </si>
+  <si>
+    <t>RAJIB LOCHAN SAREN</t>
+  </si>
+  <si>
+    <t>SHANTIRAM MAHATO</t>
+  </si>
+  <si>
+    <t>SUSHANTA MAHATO</t>
+  </si>
+  <si>
+    <t>ARJUN MAHATO</t>
+  </si>
+  <si>
+    <t>SUJOY BANERJEE</t>
+  </si>
+  <si>
+    <t>SANDHYA RANI TUDU</t>
+  </si>
+  <si>
+    <t>SOUMEN BELTHARIA</t>
+  </si>
+  <si>
+    <t>MANIK CHANDRA BAURI</t>
+  </si>
+  <si>
+    <t>HAZARI BOURI</t>
+  </si>
+  <si>
+    <t>UTTAM BAURI</t>
+  </si>
+  <si>
+    <t>SWAPAN KUMAR MONDAL</t>
+  </si>
+  <si>
+    <t>TANUSHREE HANSDA</t>
+  </si>
+  <si>
+    <t>THAKURMANI SAREN</t>
+  </si>
+  <si>
+    <t>FALGUNI SINGHABABU</t>
+  </si>
+  <si>
+    <t>DR. ANUP MANDAL</t>
+  </si>
+  <si>
+    <t>GOUTAM MISHRA (SHYAM)</t>
+  </si>
+  <si>
+    <t>SUBRATA DUTTA (GOPI)</t>
+  </si>
+  <si>
+    <t>TANMAY GHOSH (BUMBA)</t>
+  </si>
+  <si>
+    <t>HARAKALI PROTIHER</t>
+  </si>
+  <si>
+    <t>SHYAMALI ROY BAGDI</t>
+  </si>
+  <si>
+    <t>KALLOL SAHA</t>
+  </si>
+  <si>
+    <t>GOUTAM DHARA</t>
+  </si>
+  <si>
     <t>KHOKAN DAS</t>
   </si>
   <si>
-    <t>DEBASIS OJHA (HAKU DA)</t>
-  </si>
-  <si>
-    <t>KRISHNA KANTA SAHA</t>
-  </si>
-  <si>
-    <t>DUDH KUMAR MONDAL</t>
-  </si>
-  <si>
-    <t>DHRUBA SAHA</t>
-  </si>
-  <si>
-    <t>FAYEZUL HAQUE (KAJAL SK)</t>
-  </si>
-  <si>
-    <t>RAJENDRA PRASAD SINGH(RAJU SINGH)</t>
-  </si>
-  <si>
-    <t>DR. MOSARRAF HOSSAIN</t>
-  </si>
-  <si>
-    <t>Bharatiya Janata Party</t>
-  </si>
-  <si>
-    <t>All India Trinamool Congress</t>
-  </si>
-  <si>
-    <t>Indian National Congress</t>
-  </si>
-  <si>
-    <t>Aam Janata Unnayan party</t>
-  </si>
-  <si>
-    <t>Communist Party of India (Marxist)</t>
-  </si>
-  <si>
-    <t>All India Secular Front</t>
-  </si>
-  <si>
-    <t>Won</t>
-  </si>
-  <si>
-    <t>Leading</t>
-  </si>
-  <si>
-    <t>ADHIKARY PARESH CHANDRA</t>
-  </si>
-  <si>
-    <t>DR. SABLU BARMAN</t>
-  </si>
-  <si>
-    <t>PARTHA PRATIM RAY</t>
-  </si>
-  <si>
-    <t>AVIJIT DE BHOWMIK</t>
-  </si>
-  <si>
-    <t>HARIHAR DAS</t>
-  </si>
-  <si>
-    <t>ASHUTOSH BARMA</t>
-  </si>
-  <si>
-    <t>UDAYAN GUHA</t>
-  </si>
-  <si>
-    <t>SAILENDRA NATH BARMA</t>
-  </si>
-  <si>
-    <t>SHIBSANKAR PAUL</t>
-  </si>
-  <si>
-    <t>RAJEEV TIRKEY</t>
-  </si>
-  <si>
-    <t>BIRENDRA BARA (ORAON)</t>
-  </si>
-  <si>
-    <t>SUMAN KANJILAL</t>
-  </si>
-  <si>
-    <t>SUBHASH CHANDRA ROY</t>
-  </si>
-  <si>
-    <t>JAYPRAKASH TOPPO</t>
-  </si>
-  <si>
-    <t>NIRMAL CHANDRA ROY</t>
-  </si>
-  <si>
-    <t>RAMMOHAN RAY</t>
-  </si>
-  <si>
-    <t>KRISHNA DAS</t>
-  </si>
-  <si>
-    <t>SWAPNA BARMAN</t>
-  </si>
-  <si>
-    <t>RANJAN SIL SHARMA</t>
-  </si>
-  <si>
-    <t>BULU CHIK BARAIK</t>
-  </si>
-  <si>
-    <t>SANJAY KUJUR</t>
-  </si>
-  <si>
-    <t>RUDEN SADA LEPCHA</t>
-  </si>
-  <si>
-    <t>BIJOY KUMAR RAI</t>
-  </si>
-  <si>
-    <t>AMAR LAMA</t>
-  </si>
-  <si>
-    <t>SHANKAR MALAKAR</t>
-  </si>
-  <si>
-    <t>GOUTAM DEB</t>
-  </si>
-  <si>
-    <t>REENA TOPNO EKKA</t>
-  </si>
-  <si>
-    <t>SANKAR ADHIKARI</t>
-  </si>
-  <si>
-    <t>CHITRAJIT ROY</t>
-  </si>
-  <si>
-    <t>SARAJIT BISWAS</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR JAIN</t>
-  </si>
-  <si>
-    <t>GOUTAM PAUL</t>
-  </si>
-  <si>
-    <t>SATYAJIT BARMAN</t>
-  </si>
-  <si>
-    <t>NITAI BAISHYA</t>
-  </si>
-  <si>
-    <t>KRISHNA KALYANI</t>
-  </si>
-  <si>
-    <t>SABITA BARMAN</t>
-  </si>
-  <si>
-    <t>REKHA ROY</t>
-  </si>
-  <si>
-    <t>SUBHENDU SARKAR</t>
-  </si>
-  <si>
-    <t>ARPITA GHOSH</t>
-  </si>
-  <si>
-    <t>CHINTAMANI BIHA</t>
-  </si>
-  <si>
-    <t>Goutam Das</t>
-  </si>
-  <si>
-    <t>DEBABRATA MAJUMDER</t>
-  </si>
-  <si>
-    <t>AMAL KISKU</t>
-  </si>
-  <si>
-    <t>PRASENJIT DAS</t>
-  </si>
-  <si>
-    <t>RATAN DAS</t>
-  </si>
-  <si>
-    <t>MAUSAM B NOOR</t>
-  </si>
-  <si>
-    <t>ABISHEK SINGHANIA</t>
-  </si>
-  <si>
-    <t>KABITA MANDAL</t>
-  </si>
-  <si>
-    <t>LIPIKA BARMAN GHOSH</t>
-  </si>
-  <si>
-    <t>ASIS KUNDU (PATA)</t>
-  </si>
-  <si>
-    <t>NIBARAN GHOSH</t>
-  </si>
-  <si>
-    <t>ABDUL HANNAN</t>
-  </si>
-  <si>
-    <t>CHANDANA SARKAR</t>
-  </si>
-  <si>
-    <t>SUNIL CHOWDHURI</t>
-  </si>
-  <si>
-    <t>MD NAJME ALAM</t>
-  </si>
-  <si>
-    <t>MAHABIR GHOSH</t>
-  </si>
-  <si>
-    <t>JAKIR HOSSAIN</t>
-  </si>
-  <si>
-    <t>NASIR SAIKH</t>
-  </si>
-  <si>
-    <t>TAPAS KUMAR CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>TOUHIDUR RAHAMAN SUMAN</t>
-  </si>
-  <si>
-    <t>MAHAMUDAL HASAN</t>
-  </si>
-  <si>
-    <t>ABDUL SOUMIK HOSSAIN</t>
-  </si>
-  <si>
-    <t>SHAONI SINGHA ROY</t>
-  </si>
-  <si>
-    <t>PRONAB CHANDRA DAS</t>
-  </si>
-  <si>
-    <t>ASHIS MARJIT</t>
-  </si>
-  <si>
-    <t>PROTIMA RAJAK</t>
-  </si>
-  <si>
-    <t>APURBA SARKAR (DAVID)</t>
-  </si>
-  <si>
-    <t>ANAMIKA GHOSH</t>
-  </si>
-  <si>
-    <t>BAPAN GHOSH</t>
-  </si>
-  <si>
-    <t>RABIUL ALAM CHOWDHURY</t>
-  </si>
-  <si>
-    <t>ADHIR RANJAN CHOWDHURY</t>
-  </si>
-  <si>
-    <t>BIJOY SEKH</t>
-  </si>
-  <si>
-    <t>RANA MANDAL</t>
-  </si>
-  <si>
-    <t>IANUS ALI SARKAR</t>
-  </si>
-  <si>
-    <t>SOHAM CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>DILIP KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>ANIMA DUTTA</t>
-  </si>
-  <si>
-    <t>KALLOL KHAN</t>
-  </si>
-  <si>
-    <t>SAIKAT SARKAR</t>
-  </si>
-  <si>
-    <t>SOMNATH DUTTA</t>
-  </si>
-  <si>
-    <t>PUNDARIKAKSHYA SAHA</t>
-  </si>
-  <si>
-    <t>UJJAL BISWAS</t>
-  </si>
-  <si>
-    <t>BRAJAKISHORE GOSWAMI</t>
-  </si>
-  <si>
-    <t>TAPAS KUMAR GHOSH</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>BARNALI DEY ROY</t>
-  </si>
-  <si>
-    <t>SOUGATA KUMAR BURMAN</t>
-  </si>
-  <si>
-    <t>SUBHANKAR SINGHA (JISHU)</t>
-  </si>
-  <si>
-    <t>DR. ATINDRA NATH MONDAL</t>
-  </si>
-  <si>
-    <t>DR. RAJIB BISWAS.</t>
-  </si>
-  <si>
-    <t>MADHUPARNA THAKUR</t>
-  </si>
-  <si>
-    <t>BISWAJIT DAS</t>
-  </si>
-  <si>
-    <t>RITUPARNA ADDHYA</t>
-  </si>
-  <si>
-    <t>NAROTTAM BISWAS</t>
-  </si>
-  <si>
-    <t>TARAK SAHA</t>
-  </si>
-  <si>
-    <t>SUKRITI KUMAR SARKAR</t>
-  </si>
-  <si>
-    <t>JYOTI PRIYA MALLICK</t>
-  </si>
-  <si>
-    <t>NARAYAN GOSWAMI</t>
-  </si>
-  <si>
-    <t>ARINDAM DEY</t>
-  </si>
-  <si>
-    <t>SUBODH ADHIKARY</t>
-  </si>
-  <si>
-    <t>SANAT DEY</t>
-  </si>
-  <si>
-    <t>AMIT GUPTA</t>
-  </si>
-  <si>
-    <t>SOMENATH SHYAM ICHINI</t>
-  </si>
-  <si>
-    <t>TRINANKUR BHATTACHARJEE</t>
-  </si>
-  <si>
-    <t>RAJ CHAKRABORTY (RAJU)</t>
-  </si>
-  <si>
-    <t>DEVADEEP PUROHIT</t>
-  </si>
-  <si>
-    <t>CHANDRIMA BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>TIRTHANKAR GHOSH</t>
-  </si>
-  <si>
-    <t>ARUP CHOUDHURY (PULAK)</t>
-  </si>
-  <si>
-    <t>SAYANTIKA BANERJEE</t>
-  </si>
-  <si>
-    <t>BRATYABRATA BASU</t>
-  </si>
-  <si>
-    <t>PIYUSH KANODIA</t>
-  </si>
-  <si>
-    <t>SUJIT BOSE</t>
-  </si>
-  <si>
-    <t>ADITI MUNSHI</t>
-  </si>
-  <si>
-    <t>RATHIN GHOSH</t>
-  </si>
-  <si>
-    <t>SABYASACHI DUTTA</t>
-  </si>
-  <si>
-    <t>MD MOFIDUL HOQUE SAHAJI MINTU</t>
-  </si>
-  <si>
-    <t>PIYARUL ISLAM</t>
-  </si>
-  <si>
-    <t>RUDRENDRA PATRA</t>
-  </si>
-  <si>
-    <t>JHARNA SARDAR</t>
-  </si>
-  <si>
-    <t>DR. SOURYA BANERJEE</t>
-  </si>
-  <si>
-    <t>MD. MUSA KAREMULLA</t>
-  </si>
-  <si>
-    <t>ANANDA SARKAR</t>
-  </si>
-  <si>
-    <t>SUBRATA MONDAL</t>
-  </si>
-  <si>
-    <t>BIKASH SARDAR</t>
-  </si>
-  <si>
-    <t>MADHABI MAHALDER</t>
-  </si>
-  <si>
-    <t>ASIT KUMAR HALDAR</t>
-  </si>
-  <si>
-    <t>MANTURAM PAKHIRA</t>
-  </si>
-  <si>
-    <t>BANKIM CHANDRA HAZRA</t>
-  </si>
-  <si>
-    <t>ABANI NASKAR</t>
-  </si>
-  <si>
-    <t>PALASH RANA</t>
-  </si>
-  <si>
-    <t>MALLIKA PAIK W/O - ASHOK PAIK</t>
-  </si>
-  <si>
-    <t>ALOKE HALDER</t>
-  </si>
-  <si>
-    <t>TUMPA SARDAR</t>
-  </si>
-  <si>
-    <t>Prasanta Bayen</t>
-  </si>
-  <si>
-    <t>ARABUL ISLAM</t>
-  </si>
-  <si>
-    <t>BISWAJIT PAUL</t>
-  </si>
-  <si>
-    <t>UTTAM KUMAR BANIK</t>
-  </si>
-  <si>
-    <t>GOURSUNDAR GHOSH</t>
-  </si>
-  <si>
-    <t>DIPAK KUMAR HALDER</t>
-  </si>
-  <si>
-    <t>JAHANGIR KHAN</t>
-  </si>
-  <si>
-    <t>SOMASHREE BETAL</t>
-  </si>
-  <si>
-    <t>ABHIJIT SARDAR</t>
-  </si>
-  <si>
-    <t>ARUNDHUTI MAITRA(LOVELY)</t>
-  </si>
-  <si>
-    <t>SAOKAT MOLLA</t>
-  </si>
-  <si>
-    <t>BANERJEE SANDIP</t>
-  </si>
-  <si>
-    <t>DEBABRATA MAJUMDAR (MALAY)</t>
-  </si>
-  <si>
-    <t>FIRDOUSI BEGAM</t>
-  </si>
-  <si>
-    <t>AROOP BISWAS</t>
-  </si>
-  <si>
-    <t>SUBHASISH CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>RATNA CHATTERJEE</t>
-  </si>
-  <si>
-    <t>TAMANATH BHOWMICK</t>
-  </si>
-  <si>
-    <t>DR TARUN KUMAR ADAK</t>
-  </si>
-  <si>
-    <t>BIR BAHADUR SINGH</t>
-  </si>
-  <si>
-    <t>RAKESH SINGH</t>
-  </si>
-  <si>
-    <t>MAMATA BANERJEE</t>
-  </si>
-  <si>
-    <t>DEBASISH KUMAR (DEBA)</t>
-  </si>
-  <si>
-    <t>SHATORUPA</t>
-  </si>
-  <si>
-    <t>SANTOSH KUMAR PATHAK</t>
-  </si>
-  <si>
-    <t>DR. PRIYANKA TIBREWAL</t>
-  </si>
-  <si>
-    <t>PARTHA CHAUDHURY</t>
-  </si>
-  <si>
-    <t>VIJAY UPADHYAY</t>
-  </si>
-  <si>
-    <t>SHASHI PANJA</t>
-  </si>
-  <si>
-    <t>SHRREYA PANDE</t>
-  </si>
-  <si>
-    <t>ATIN GHOSH</t>
-  </si>
-  <si>
-    <t>KAILASH KUMAR MISHRA</t>
-  </si>
-  <si>
-    <t>GAUTAM CHOWDHURY</t>
-  </si>
-  <si>
-    <t>BIPLAB KUMAR MANDAL</t>
-  </si>
-  <si>
-    <t>DR. RANA CHATTERJEE</t>
-  </si>
-  <si>
-    <t>SHYAMAL KUMAR HATI</t>
-  </si>
-  <si>
-    <t>BARNALI DHALI NASKAR</t>
-  </si>
-  <si>
-    <t>RANJAN PAUL</t>
-  </si>
-  <si>
-    <t>RUDRA PROSAD BANERJEE</t>
-  </si>
-  <si>
-    <t>BIMAL KUMAR DAS</t>
-  </si>
-  <si>
-    <t>SWAMI MANGALANANDA PURI</t>
-  </si>
-  <si>
-    <t>NADEBASI JANA</t>
-  </si>
-  <si>
-    <t>PRAMANSHU RANA</t>
-  </si>
-  <si>
-    <t>SUKANTA KUMAR PAUL</t>
-  </si>
-  <si>
-    <t>PROBHAKAR PANDIT</t>
-  </si>
-  <si>
-    <t>SUBIR CHATTERJEE (TINKAI)</t>
-  </si>
-  <si>
-    <t>GOBINDA HAZRA</t>
-  </si>
-  <si>
-    <t>SIRSANYA BANDOPADHYAY</t>
-  </si>
-  <si>
-    <t>TANMOY GHOSH</t>
-  </si>
-  <si>
-    <t>ARINDAM GUIN (BUBAI)</t>
-  </si>
-  <si>
-    <t>BECHARAM MANNA</t>
-  </si>
-  <si>
-    <t>Indranil Sen</t>
-  </si>
-  <si>
-    <t>DEBANGSHU BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>RANJAN DHARA</t>
-  </si>
-  <si>
-    <t>SAMIR CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>BIDESH RANJAN BOSE</t>
-  </si>
-  <si>
-    <t>DEBASISH MUKHERJEE</t>
-  </si>
-  <si>
-    <t>SNEHASIS CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>KARABI MANNA</t>
-  </si>
-  <si>
-    <t>BARNALI DAS</t>
-  </si>
-  <si>
-    <t>RAMENDU SINHARAY</t>
-  </si>
-  <si>
-    <t>PARTHA HAZARI</t>
-  </si>
-  <si>
-    <t>BAG MITA</t>
-  </si>
-  <si>
-    <t>DR. NIRMAL MAJI</t>
-  </si>
-  <si>
-    <t>PALASH KUMAR ROY</t>
-  </si>
-  <si>
-    <t>DIPENDRA NARAYAN ROY</t>
-  </si>
-  <si>
-    <t>ASHIM KUMAR MAJI</t>
-  </si>
-  <si>
-    <t>SIRAJ KHAN</t>
-  </si>
-  <si>
-    <t>CHANDAN MONDAL</t>
-  </si>
-  <si>
-    <t>SUKUMAR DE</t>
-  </si>
-  <si>
-    <t>TILAK KUMAR CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>TAPASI MONDAL</t>
-  </si>
-  <si>
-    <t>PABITRA KAR</t>
-  </si>
-  <si>
-    <t>UTTAM BARIK</t>
-  </si>
-  <si>
-    <t>PIJUS KANTI PANDA</t>
-  </si>
-  <si>
-    <t>DEBASIS BHUNYA</t>
-  </si>
-  <si>
-    <t>MANAB KUMAR PARUA</t>
-  </si>
-  <si>
-    <t>RABIN CHANDRA MANDAL</t>
-  </si>
-  <si>
-    <t>TARUN KUMAR JANA</t>
-  </si>
-  <si>
-    <t>AKHIL GIRI</t>
-  </si>
-  <si>
-    <t>TARUN KUMAR MAITY</t>
-  </si>
-  <si>
-    <t>MANIK MAITI</t>
-  </si>
-  <si>
-    <t>DULAL MURMU</t>
-  </si>
-  <si>
-    <t>AJIT MAHATA</t>
-  </si>
-  <si>
-    <t>MONGAL SAREN</t>
-  </si>
-  <si>
-    <t>RAMJIBAN MANDI</t>
-  </si>
-  <si>
-    <t>PRADIP SARKAR</t>
-  </si>
-  <si>
-    <t>PRATIBHA MAITI</t>
-  </si>
-  <si>
-    <t>MANAS RANJAN BHUNIA</t>
-  </si>
-  <si>
-    <t>AJIT MAITY</t>
-  </si>
-  <si>
-    <t>TAPAN BHUYA</t>
-  </si>
-  <si>
-    <t>RAJIB BANERJEE</t>
-  </si>
-  <si>
-    <t>ASHIS HUDAIT</t>
-  </si>
-  <si>
-    <t>SHYAMALI SARDAR</t>
-  </si>
-  <si>
-    <t>DOLOI SURJYA KANTA</t>
-  </si>
-  <si>
-    <t>UTTARA SINGHA (HAZRA)</t>
-  </si>
-  <si>
-    <t>SRIKANTA MAHATA</t>
-  </si>
-  <si>
-    <t>SUVENDU SAMANTA</t>
-  </si>
-  <si>
-    <t>SUJOY HAZRA</t>
-  </si>
-  <si>
-    <t>BIRBAHA HANSDA</t>
-  </si>
-  <si>
-    <t>RAJIB LOCHAN SAREN</t>
-  </si>
-  <si>
-    <t>SHANTIRAM MAHATO</t>
-  </si>
-  <si>
-    <t>SUSHANTA MAHATO</t>
-  </si>
-  <si>
-    <t>ARJUN MAHATO</t>
-  </si>
-  <si>
-    <t>SUJOY BANERJEE</t>
-  </si>
-  <si>
-    <t>SANDHYA RANI TUDU</t>
-  </si>
-  <si>
-    <t>SOUMEN BELTHARIA</t>
-  </si>
-  <si>
-    <t>MANIK CHANDRA BAURI</t>
-  </si>
-  <si>
-    <t>HAZARI BOURI</t>
-  </si>
-  <si>
-    <t>UTTAM BAURI</t>
-  </si>
-  <si>
-    <t>SWAPAN KUMAR MONDAL</t>
-  </si>
-  <si>
-    <t>TANUSHREE HANSDA</t>
-  </si>
-  <si>
-    <t>THAKURMANI SAREN</t>
-  </si>
-  <si>
-    <t>FALGUNI SINGHABABU</t>
-  </si>
-  <si>
-    <t>DR. ANUP MANDAL</t>
-  </si>
-  <si>
-    <t>GOUTAM MISHRA (SHYAM)</t>
-  </si>
-  <si>
-    <t>SUBRATA DUTTA (GOPI)</t>
-  </si>
-  <si>
-    <t>TANMAY GHOSH (BUMBA)</t>
-  </si>
-  <si>
-    <t>HARAKALI PROTIHER</t>
-  </si>
-  <si>
-    <t>SHYAMALI ROY BAGDI</t>
-  </si>
-  <si>
-    <t>KALLOL SAHA</t>
-  </si>
-  <si>
-    <t>GOUTAM DHARA</t>
-  </si>
-  <si>
     <t>MANDIRA DALUI</t>
   </si>
   <si>
@@ -2685,9 +2688,6 @@
   </si>
   <si>
     <t>UJJAL CHATTERJEE</t>
-  </si>
-  <si>
-    <t>BIDHAN CHANDRA MAJHI</t>
   </si>
   <si>
     <t>ABHIJIT SINHA (RANA)</t>
@@ -4274,7 +4274,7 @@
         <v>23</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>312</v>
@@ -4283,10 +4283,10 @@
         <v>601</v>
       </c>
       <c r="F4">
-        <v>135473</v>
+        <v>155327</v>
       </c>
       <c r="G4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H4">
         <f>F4-K4</f>
@@ -4299,10 +4299,10 @@
         <v>602</v>
       </c>
       <c r="K4">
-        <v>73257</v>
+        <v>84943</v>
       </c>
       <c r="L4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M4" t="s">
         <v>903</v>
@@ -4311,10 +4311,10 @@
         <v>605</v>
       </c>
       <c r="O4">
-        <v>4463</v>
+        <v>5293</v>
       </c>
       <c r="P4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -4529,7 +4529,7 @@
         <v>22</v>
       </c>
       <c r="C9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>317</v>
@@ -4538,10 +4538,10 @@
         <v>601</v>
       </c>
       <c r="F9">
-        <v>124086</v>
+        <v>126911</v>
       </c>
       <c r="G9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H9">
         <f>F9-K9</f>
@@ -4554,10 +4554,10 @@
         <v>602</v>
       </c>
       <c r="K9">
-        <v>88019</v>
+        <v>92298</v>
       </c>
       <c r="L9" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M9" t="s">
         <v>908</v>
@@ -4566,10 +4566,10 @@
         <v>605</v>
       </c>
       <c r="O9">
-        <v>6230</v>
+        <v>6606</v>
       </c>
       <c r="P9" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -4631,7 +4631,7 @@
         <v>24</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>319</v>
@@ -4640,10 +4640,10 @@
         <v>601</v>
       </c>
       <c r="F11">
-        <v>138982</v>
+        <v>143044</v>
       </c>
       <c r="G11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H11">
         <f>F11-K11</f>
@@ -4656,10 +4656,10 @@
         <v>602</v>
       </c>
       <c r="K11">
-        <v>87630</v>
+        <v>90167</v>
       </c>
       <c r="L11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M11" t="s">
         <v>910</v>
@@ -4668,10 +4668,10 @@
         <v>1193</v>
       </c>
       <c r="O11">
-        <v>3980</v>
+        <v>4111</v>
       </c>
       <c r="P11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -4733,7 +4733,7 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
         <v>321</v>
@@ -4742,7 +4742,7 @@
         <v>601</v>
       </c>
       <c r="F13">
-        <v>122808</v>
+        <v>131687</v>
       </c>
       <c r="G13" t="s">
         <v>608</v>
@@ -4758,7 +4758,7 @@
         <v>602</v>
       </c>
       <c r="K13">
-        <v>64288</v>
+        <v>67609</v>
       </c>
       <c r="L13" t="s">
         <v>900</v>
@@ -4770,7 +4770,7 @@
         <v>605</v>
       </c>
       <c r="O13">
-        <v>6480</v>
+        <v>6819</v>
       </c>
       <c r="P13" t="s">
         <v>900</v>
@@ -5138,10 +5138,10 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
         <v>329</v>
@@ -5150,7 +5150,7 @@
         <v>601</v>
       </c>
       <c r="F21">
-        <v>110214</v>
+        <v>112095</v>
       </c>
       <c r="G21" t="s">
         <v>607</v>
@@ -5166,7 +5166,7 @@
         <v>602</v>
       </c>
       <c r="K21">
-        <v>94502</v>
+        <v>96603</v>
       </c>
       <c r="L21" t="s">
         <v>899</v>
@@ -5178,7 +5178,7 @@
         <v>605</v>
       </c>
       <c r="O21">
-        <v>5758</v>
+        <v>5831</v>
       </c>
       <c r="P21" t="s">
         <v>899</v>
@@ -6005,10 +6005,10 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D38" t="s">
         <v>346</v>
@@ -6017,7 +6017,7 @@
         <v>601</v>
       </c>
       <c r="F38">
-        <v>96477</v>
+        <v>97437</v>
       </c>
       <c r="G38" t="s">
         <v>607</v>
@@ -6033,7 +6033,7 @@
         <v>602</v>
       </c>
       <c r="K38">
-        <v>87840</v>
+        <v>88374</v>
       </c>
       <c r="L38" t="s">
         <v>899</v>
@@ -6045,7 +6045,7 @@
         <v>1193</v>
       </c>
       <c r="O38">
-        <v>6840</v>
+        <v>6861</v>
       </c>
       <c r="P38" t="s">
         <v>899</v>
@@ -8099,7 +8099,7 @@
         <v>23</v>
       </c>
       <c r="C79">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D79" t="s">
         <v>386</v>
@@ -8108,10 +8108,10 @@
         <v>601</v>
       </c>
       <c r="F79">
-        <v>111417</v>
+        <v>112138</v>
       </c>
       <c r="G79" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H79">
         <f>F79-K79</f>
@@ -8124,10 +8124,10 @@
         <v>602</v>
       </c>
       <c r="K79">
-        <v>82344</v>
+        <v>83885</v>
       </c>
       <c r="L79" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M79" t="s">
         <v>977</v>
@@ -8136,10 +8136,10 @@
         <v>605</v>
       </c>
       <c r="O79">
-        <v>24202</v>
+        <v>25629</v>
       </c>
       <c r="P79" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -8504,10 +8504,10 @@
         <v>101</v>
       </c>
       <c r="B87">
+        <v>17</v>
+      </c>
+      <c r="C87">
         <v>16</v>
-      </c>
-      <c r="C87">
-        <v>15</v>
       </c>
       <c r="D87" t="s">
         <v>394</v>
@@ -8516,7 +8516,7 @@
         <v>601</v>
       </c>
       <c r="F87">
-        <v>116881</v>
+        <v>117157</v>
       </c>
       <c r="G87" t="s">
         <v>608</v>
@@ -8532,7 +8532,7 @@
         <v>602</v>
       </c>
       <c r="K87">
-        <v>72335</v>
+        <v>72464</v>
       </c>
       <c r="L87" t="s">
         <v>900</v>
@@ -8544,7 +8544,7 @@
         <v>605</v>
       </c>
       <c r="O87">
-        <v>11461</v>
+        <v>11511</v>
       </c>
       <c r="P87" t="s">
         <v>900</v>
@@ -8558,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="C88">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
         <v>395</v>
@@ -8567,7 +8567,7 @@
         <v>601</v>
       </c>
       <c r="F88">
-        <v>109260</v>
+        <v>126250</v>
       </c>
       <c r="G88" t="s">
         <v>608</v>
@@ -8583,7 +8583,7 @@
         <v>602</v>
       </c>
       <c r="K88">
-        <v>61709</v>
+        <v>70098</v>
       </c>
       <c r="L88" t="s">
         <v>900</v>
@@ -8595,7 +8595,7 @@
         <v>605</v>
       </c>
       <c r="O88">
-        <v>8279</v>
+        <v>9998</v>
       </c>
       <c r="P88" t="s">
         <v>900</v>
@@ -9119,7 +9119,7 @@
         <v>16</v>
       </c>
       <c r="C99">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D99" t="s">
         <v>406</v>
@@ -9128,7 +9128,7 @@
         <v>602</v>
       </c>
       <c r="F99">
-        <v>92089</v>
+        <v>94449</v>
       </c>
       <c r="G99" t="s">
         <v>608</v>
@@ -9144,7 +9144,7 @@
         <v>601</v>
       </c>
       <c r="K99">
-        <v>77125</v>
+        <v>78394</v>
       </c>
       <c r="L99" t="s">
         <v>900</v>
@@ -9156,7 +9156,7 @@
         <v>605</v>
       </c>
       <c r="O99">
-        <v>37539</v>
+        <v>38295</v>
       </c>
       <c r="P99" t="s">
         <v>900</v>
@@ -9303,7 +9303,7 @@
         <v>899</v>
       </c>
       <c r="M102" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N102" t="s">
         <v>606</v>
@@ -9323,7 +9323,7 @@
         <v>20</v>
       </c>
       <c r="C103">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D103" t="s">
         <v>410</v>
@@ -9332,10 +9332,10 @@
         <v>602</v>
       </c>
       <c r="F103">
-        <v>76429</v>
+        <v>81670</v>
       </c>
       <c r="G103" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H103">
         <f>F103-K103</f>
@@ -9348,10 +9348,10 @@
         <v>601</v>
       </c>
       <c r="K103">
-        <v>72610</v>
+        <v>78675</v>
       </c>
       <c r="L103" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M103" t="s">
         <v>1000</v>
@@ -9360,10 +9360,10 @@
         <v>606</v>
       </c>
       <c r="O103">
-        <v>44613</v>
+        <v>46181</v>
       </c>
       <c r="P103" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -9527,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D107" t="s">
         <v>414</v>
@@ -9536,10 +9536,10 @@
         <v>601</v>
       </c>
       <c r="F107">
-        <v>71753</v>
+        <v>94351</v>
       </c>
       <c r="G107" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H107">
         <f>F107-K107</f>
@@ -9552,10 +9552,10 @@
         <v>602</v>
       </c>
       <c r="K107">
-        <v>57481</v>
+        <v>73442</v>
       </c>
       <c r="L107" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M107" t="s">
         <v>1004</v>
@@ -9564,10 +9564,10 @@
         <v>1192</v>
       </c>
       <c r="O107">
-        <v>7070</v>
+        <v>9062</v>
       </c>
       <c r="P107" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -9578,7 +9578,7 @@
         <v>14</v>
       </c>
       <c r="C108">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s">
         <v>415</v>
@@ -9587,10 +9587,10 @@
         <v>601</v>
       </c>
       <c r="F108">
-        <v>79332</v>
+        <v>94415</v>
       </c>
       <c r="G108" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H108">
         <f>F108-K108</f>
@@ -9603,10 +9603,10 @@
         <v>602</v>
       </c>
       <c r="K108">
-        <v>62496</v>
+        <v>76759</v>
       </c>
       <c r="L108" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M108" t="s">
         <v>1005</v>
@@ -9615,10 +9615,10 @@
         <v>605</v>
       </c>
       <c r="O108">
-        <v>15597</v>
+        <v>17696</v>
       </c>
       <c r="P108" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -9986,7 +9986,7 @@
         <v>17</v>
       </c>
       <c r="C116">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D116" t="s">
         <v>423</v>
@@ -9995,7 +9995,7 @@
         <v>602</v>
       </c>
       <c r="F116">
-        <v>90558</v>
+        <v>104324</v>
       </c>
       <c r="G116" t="s">
         <v>608</v>
@@ -10011,7 +10011,7 @@
         <v>601</v>
       </c>
       <c r="K116">
-        <v>77779</v>
+        <v>102250</v>
       </c>
       <c r="L116" t="s">
         <v>900</v>
@@ -10023,7 +10023,7 @@
         <v>605</v>
       </c>
       <c r="O116">
-        <v>26833</v>
+        <v>31654</v>
       </c>
       <c r="P116" t="s">
         <v>900</v>
@@ -10139,7 +10139,7 @@
         <v>17</v>
       </c>
       <c r="C119">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D119" t="s">
         <v>426</v>
@@ -10148,7 +10148,7 @@
         <v>601</v>
       </c>
       <c r="F119">
-        <v>82596</v>
+        <v>86049</v>
       </c>
       <c r="G119" t="s">
         <v>608</v>
@@ -10164,7 +10164,7 @@
         <v>602</v>
       </c>
       <c r="K119">
-        <v>77056</v>
+        <v>85076</v>
       </c>
       <c r="L119" t="s">
         <v>900</v>
@@ -10176,7 +10176,7 @@
         <v>606</v>
       </c>
       <c r="O119">
-        <v>23014</v>
+        <v>28805</v>
       </c>
       <c r="P119" t="s">
         <v>900</v>
@@ -10442,10 +10442,10 @@
         <v>139</v>
       </c>
       <c r="B125">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C125">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D125" t="s">
         <v>432</v>
@@ -10454,7 +10454,7 @@
         <v>602</v>
       </c>
       <c r="F125">
-        <v>112802</v>
+        <v>112965</v>
       </c>
       <c r="G125" t="s">
         <v>607</v>
@@ -10470,7 +10470,7 @@
         <v>601</v>
       </c>
       <c r="K125">
-        <v>102957</v>
+        <v>103421</v>
       </c>
       <c r="L125" t="s">
         <v>899</v>
@@ -10482,7 +10482,7 @@
         <v>605</v>
       </c>
       <c r="O125">
-        <v>23700</v>
+        <v>23710</v>
       </c>
       <c r="P125" t="s">
         <v>899</v>
@@ -10955,7 +10955,7 @@
         <v>23</v>
       </c>
       <c r="C135">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D135" t="s">
         <v>442</v>
@@ -10964,10 +10964,10 @@
         <v>602</v>
       </c>
       <c r="F135">
-        <v>93881</v>
+        <v>118991</v>
       </c>
       <c r="G135" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H135">
         <f>F135-K135</f>
@@ -10980,10 +10980,10 @@
         <v>601</v>
       </c>
       <c r="K135">
-        <v>86407</v>
+        <v>113034</v>
       </c>
       <c r="L135" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M135" t="s">
         <v>1032</v>
@@ -10992,10 +10992,10 @@
         <v>605</v>
       </c>
       <c r="O135">
-        <v>17156</v>
+        <v>19160</v>
       </c>
       <c r="P135" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -11003,10 +11003,10 @@
         <v>150</v>
       </c>
       <c r="B136">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C136">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D136" t="s">
         <v>443</v>
@@ -11015,10 +11015,10 @@
         <v>602</v>
       </c>
       <c r="F136">
-        <v>85157</v>
+        <v>93686</v>
       </c>
       <c r="G136" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H136">
         <f>F136-K136</f>
@@ -11031,10 +11031,10 @@
         <v>601</v>
       </c>
       <c r="K136">
-        <v>83956</v>
+        <v>91691</v>
       </c>
       <c r="L136" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M136" t="s">
         <v>1033</v>
@@ -11043,10 +11043,10 @@
         <v>606</v>
       </c>
       <c r="O136">
-        <v>19483</v>
+        <v>21943</v>
       </c>
       <c r="P136" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -11066,7 +11066,7 @@
         <v>602</v>
       </c>
       <c r="F137">
-        <v>108050</v>
+        <v>108194</v>
       </c>
       <c r="G137" t="s">
         <v>607</v>
@@ -11082,7 +11082,7 @@
         <v>601</v>
       </c>
       <c r="K137">
-        <v>81421</v>
+        <v>81844</v>
       </c>
       <c r="L137" t="s">
         <v>899</v>
@@ -11094,7 +11094,7 @@
         <v>605</v>
       </c>
       <c r="O137">
-        <v>18127</v>
+        <v>18151</v>
       </c>
       <c r="P137" t="s">
         <v>899</v>
@@ -11117,7 +11117,7 @@
         <v>602</v>
       </c>
       <c r="F138">
-        <v>109166</v>
+        <v>109625</v>
       </c>
       <c r="G138" t="s">
         <v>608</v>
@@ -11133,7 +11133,7 @@
         <v>601</v>
       </c>
       <c r="K138">
-        <v>83335</v>
+        <v>83820</v>
       </c>
       <c r="L138" t="s">
         <v>900</v>
@@ -11145,7 +11145,7 @@
         <v>605</v>
       </c>
       <c r="O138">
-        <v>17622</v>
+        <v>17713</v>
       </c>
       <c r="P138" t="s">
         <v>900</v>
@@ -11363,7 +11363,7 @@
         <v>19</v>
       </c>
       <c r="C143">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D143" t="s">
         <v>450</v>
@@ -11372,10 +11372,10 @@
         <v>602</v>
       </c>
       <c r="F143">
-        <v>100474</v>
+        <v>113834</v>
       </c>
       <c r="G143" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H143">
         <f>F143-K143</f>
@@ -11388,10 +11388,10 @@
         <v>601</v>
       </c>
       <c r="K143">
-        <v>45102</v>
+        <v>55331</v>
       </c>
       <c r="L143" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M143" t="s">
         <v>1040</v>
@@ -11400,10 +11400,10 @@
         <v>606</v>
       </c>
       <c r="O143">
-        <v>27261</v>
+        <v>28714</v>
       </c>
       <c r="P143" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -11414,7 +11414,7 @@
         <v>22</v>
       </c>
       <c r="C144">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D144" t="s">
         <v>451</v>
@@ -11423,7 +11423,7 @@
         <v>602</v>
       </c>
       <c r="F144">
-        <v>91094</v>
+        <v>104847</v>
       </c>
       <c r="G144" t="s">
         <v>608</v>
@@ -11439,7 +11439,7 @@
         <v>601</v>
       </c>
       <c r="K144">
-        <v>50391</v>
+        <v>68156</v>
       </c>
       <c r="L144" t="s">
         <v>900</v>
@@ -11451,7 +11451,7 @@
         <v>605</v>
       </c>
       <c r="O144">
-        <v>13644</v>
+        <v>15777</v>
       </c>
       <c r="P144" t="s">
         <v>900</v>
@@ -11516,7 +11516,7 @@
         <v>18</v>
       </c>
       <c r="C146">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D146" t="s">
         <v>453</v>
@@ -11525,10 +11525,10 @@
         <v>601</v>
       </c>
       <c r="F146">
-        <v>111016</v>
+        <v>111023</v>
       </c>
       <c r="G146" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H146">
         <f>F146-K146</f>
@@ -11541,10 +11541,10 @@
         <v>602</v>
       </c>
       <c r="K146">
-        <v>109975</v>
+        <v>110622</v>
       </c>
       <c r="L146" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M146" t="s">
         <v>1043</v>
@@ -11553,10 +11553,10 @@
         <v>605</v>
       </c>
       <c r="O146">
-        <v>11718</v>
+        <v>11736</v>
       </c>
       <c r="P146" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -11627,7 +11627,7 @@
         <v>601</v>
       </c>
       <c r="F148">
-        <v>128682</v>
+        <v>128970</v>
       </c>
       <c r="G148" t="s">
         <v>607</v>
@@ -11643,7 +11643,7 @@
         <v>602</v>
       </c>
       <c r="K148">
-        <v>92969</v>
+        <v>93188</v>
       </c>
       <c r="L148" t="s">
         <v>899</v>
@@ -11655,7 +11655,7 @@
         <v>1197</v>
       </c>
       <c r="O148">
-        <v>16751</v>
+        <v>16784</v>
       </c>
       <c r="P148" t="s">
         <v>899</v>
@@ -11771,7 +11771,7 @@
         <v>26</v>
       </c>
       <c r="C151">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D151" t="s">
         <v>458</v>
@@ -11780,10 +11780,10 @@
         <v>601</v>
       </c>
       <c r="F151">
-        <v>92412</v>
+        <v>106199</v>
       </c>
       <c r="G151" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H151">
         <f>F151-K151</f>
@@ -11796,10 +11796,10 @@
         <v>602</v>
       </c>
       <c r="K151">
-        <v>69307</v>
+        <v>78483</v>
       </c>
       <c r="L151" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M151" t="s">
         <v>1048</v>
@@ -11808,10 +11808,10 @@
         <v>605</v>
       </c>
       <c r="O151">
-        <v>35450</v>
+        <v>41148</v>
       </c>
       <c r="P151" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -11873,7 +11873,7 @@
         <v>17</v>
       </c>
       <c r="C153">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D153" t="s">
         <v>460</v>
@@ -11882,10 +11882,10 @@
         <v>601</v>
       </c>
       <c r="F153">
-        <v>88146</v>
+        <v>88407</v>
       </c>
       <c r="G153" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H153">
         <f>F153-K153</f>
@@ -11898,10 +11898,10 @@
         <v>602</v>
       </c>
       <c r="K153">
-        <v>82072</v>
+        <v>82394</v>
       </c>
       <c r="L153" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M153" t="s">
         <v>1050</v>
@@ -11910,10 +11910,10 @@
         <v>605</v>
       </c>
       <c r="O153">
-        <v>30237</v>
+        <v>30335</v>
       </c>
       <c r="P153" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -12230,7 +12230,7 @@
         <v>20</v>
       </c>
       <c r="C160">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D160" t="s">
         <v>467</v>
@@ -12239,10 +12239,10 @@
         <v>601</v>
       </c>
       <c r="F160">
-        <v>60954</v>
+        <v>73917</v>
       </c>
       <c r="G160" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H160">
         <f>F160-K160</f>
@@ -12255,10 +12255,10 @@
         <v>602</v>
       </c>
       <c r="K160">
-        <v>54728</v>
+        <v>58812</v>
       </c>
       <c r="L160" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M160" t="s">
         <v>1057</v>
@@ -12267,10 +12267,10 @@
         <v>605</v>
       </c>
       <c r="O160">
-        <v>2820</v>
+        <v>3556</v>
       </c>
       <c r="P160" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -12740,7 +12740,7 @@
         <v>15</v>
       </c>
       <c r="C170">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D170" t="s">
         <v>477</v>
@@ -12749,7 +12749,7 @@
         <v>601</v>
       </c>
       <c r="F170">
-        <v>44482</v>
+        <v>54588</v>
       </c>
       <c r="G170" t="s">
         <v>608</v>
@@ -12765,7 +12765,7 @@
         <v>602</v>
       </c>
       <c r="K170">
-        <v>34261</v>
+        <v>39734</v>
       </c>
       <c r="L170" t="s">
         <v>900</v>
@@ -12777,7 +12777,7 @@
         <v>605</v>
       </c>
       <c r="O170">
-        <v>9794</v>
+        <v>10831</v>
       </c>
       <c r="P170" t="s">
         <v>900</v>
@@ -13298,10 +13298,10 @@
         <v>195</v>
       </c>
       <c r="B181">
+        <v>20</v>
+      </c>
+      <c r="C181">
         <v>19</v>
-      </c>
-      <c r="C181">
-        <v>17</v>
       </c>
       <c r="D181" t="s">
         <v>488</v>
@@ -13310,7 +13310,7 @@
         <v>602</v>
       </c>
       <c r="F181">
-        <v>91442</v>
+        <v>104617</v>
       </c>
       <c r="G181" t="s">
         <v>608</v>
@@ -13326,7 +13326,7 @@
         <v>601</v>
       </c>
       <c r="K181">
-        <v>86335</v>
+        <v>93143</v>
       </c>
       <c r="L181" t="s">
         <v>900</v>
@@ -13338,7 +13338,7 @@
         <v>605</v>
       </c>
       <c r="O181">
-        <v>12317</v>
+        <v>13907</v>
       </c>
       <c r="P181" t="s">
         <v>900</v>
@@ -13349,10 +13349,10 @@
         <v>196</v>
       </c>
       <c r="B182">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C182">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D182" t="s">
         <v>489</v>
@@ -13361,7 +13361,7 @@
         <v>601</v>
       </c>
       <c r="F182">
-        <v>102983</v>
+        <v>104649</v>
       </c>
       <c r="G182" t="s">
         <v>607</v>
@@ -13377,7 +13377,7 @@
         <v>602</v>
       </c>
       <c r="K182">
-        <v>98995</v>
+        <v>100195</v>
       </c>
       <c r="L182" t="s">
         <v>899</v>
@@ -13389,7 +13389,7 @@
         <v>605</v>
       </c>
       <c r="O182">
-        <v>23111</v>
+        <v>23193</v>
       </c>
       <c r="P182" t="s">
         <v>899</v>
@@ -13400,10 +13400,10 @@
         <v>197</v>
       </c>
       <c r="B183">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C183">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D183" t="s">
         <v>490</v>
@@ -13412,10 +13412,10 @@
         <v>602</v>
       </c>
       <c r="F183">
-        <v>100333</v>
+        <v>105802</v>
       </c>
       <c r="G183" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H183">
         <f>F183-K183</f>
@@ -13428,10 +13428,10 @@
         <v>601</v>
       </c>
       <c r="K183">
-        <v>88401</v>
+        <v>93575</v>
       </c>
       <c r="L183" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M183" t="s">
         <v>1080</v>
@@ -13440,10 +13440,10 @@
         <v>605</v>
       </c>
       <c r="O183">
-        <v>7578</v>
+        <v>7849</v>
       </c>
       <c r="P183" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -13553,10 +13553,10 @@
         <v>200</v>
       </c>
       <c r="B186">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C186">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D186" t="s">
         <v>493</v>
@@ -13565,7 +13565,7 @@
         <v>601</v>
       </c>
       <c r="F186">
-        <v>80458</v>
+        <v>80612</v>
       </c>
       <c r="G186" t="s">
         <v>607</v>
@@ -13581,7 +13581,7 @@
         <v>602</v>
       </c>
       <c r="K186">
-        <v>70167</v>
+        <v>70197</v>
       </c>
       <c r="L186" t="s">
         <v>899</v>
@@ -13593,7 +13593,7 @@
         <v>605</v>
       </c>
       <c r="O186">
-        <v>49812</v>
+        <v>49820</v>
       </c>
       <c r="P186" t="s">
         <v>899</v>
@@ -13757,10 +13757,10 @@
         <v>204</v>
       </c>
       <c r="B190">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C190">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D190" t="s">
         <v>497</v>
@@ -13769,10 +13769,10 @@
         <v>601</v>
       </c>
       <c r="F190">
-        <v>78040</v>
+        <v>86273</v>
       </c>
       <c r="G190" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H190">
         <f>F190-K190</f>
@@ -13785,10 +13785,10 @@
         <v>602</v>
       </c>
       <c r="K190">
-        <v>67356</v>
+        <v>72832</v>
       </c>
       <c r="L190" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M190" t="s">
         <v>1087</v>
@@ -13797,10 +13797,10 @@
         <v>605</v>
       </c>
       <c r="O190">
-        <v>20695</v>
+        <v>22760</v>
       </c>
       <c r="P190" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -14063,10 +14063,10 @@
         <v>210</v>
       </c>
       <c r="B196">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C196">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D196" t="s">
         <v>503</v>
@@ -14075,10 +14075,10 @@
         <v>601</v>
       </c>
       <c r="F196">
-        <v>96953</v>
+        <v>102409</v>
       </c>
       <c r="G196" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H196">
         <f>F196-K196</f>
@@ -14091,10 +14091,10 @@
         <v>602</v>
       </c>
       <c r="K196">
-        <v>95765</v>
+        <v>101547</v>
       </c>
       <c r="L196" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M196" t="s">
         <v>1093</v>
@@ -14103,10 +14103,10 @@
         <v>605</v>
       </c>
       <c r="O196">
-        <v>17542</v>
+        <v>18138</v>
       </c>
       <c r="P196" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -14114,10 +14114,10 @@
         <v>211</v>
       </c>
       <c r="B197">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C197">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D197" t="s">
         <v>504</v>
@@ -14126,10 +14126,10 @@
         <v>601</v>
       </c>
       <c r="F197">
-        <v>102500</v>
+        <v>113332</v>
       </c>
       <c r="G197" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H197">
         <f>F197-K197</f>
@@ -14142,10 +14142,10 @@
         <v>602</v>
       </c>
       <c r="K197">
-        <v>99706</v>
+        <v>109844</v>
       </c>
       <c r="L197" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M197" t="s">
         <v>1094</v>
@@ -14154,10 +14154,10 @@
         <v>606</v>
       </c>
       <c r="O197">
-        <v>11562</v>
+        <v>12537</v>
       </c>
       <c r="P197" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -14573,10 +14573,10 @@
         <v>220</v>
       </c>
       <c r="B206">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C206">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D206" t="s">
         <v>513</v>
@@ -14585,10 +14585,10 @@
         <v>601</v>
       </c>
       <c r="F206">
-        <v>117861</v>
+        <v>137919</v>
       </c>
       <c r="G206" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H206">
         <f>F206-K206</f>
@@ -14601,10 +14601,10 @@
         <v>602</v>
       </c>
       <c r="K206">
-        <v>82808</v>
+        <v>105352</v>
       </c>
       <c r="L206" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M206" t="s">
         <v>1103</v>
@@ -14613,10 +14613,10 @@
         <v>606</v>
       </c>
       <c r="O206">
-        <v>7888</v>
+        <v>8702</v>
       </c>
       <c r="P206" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -14675,10 +14675,10 @@
         <v>222</v>
       </c>
       <c r="B208">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C208">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D208" t="s">
         <v>515</v>
@@ -14687,7 +14687,7 @@
         <v>601</v>
       </c>
       <c r="F208">
-        <v>131060</v>
+        <v>131476</v>
       </c>
       <c r="G208" t="s">
         <v>607</v>
@@ -14703,7 +14703,7 @@
         <v>602</v>
       </c>
       <c r="K208">
-        <v>100649</v>
+        <v>100873</v>
       </c>
       <c r="L208" t="s">
         <v>899</v>
@@ -14715,7 +14715,7 @@
         <v>605</v>
       </c>
       <c r="O208">
-        <v>9014</v>
+        <v>9020</v>
       </c>
       <c r="P208" t="s">
         <v>899</v>
@@ -14993,7 +14993,7 @@
         <v>601</v>
       </c>
       <c r="F214">
-        <v>118972</v>
+        <v>120227</v>
       </c>
       <c r="G214" t="s">
         <v>608</v>
@@ -15009,7 +15009,7 @@
         <v>602</v>
       </c>
       <c r="K214">
-        <v>103450</v>
+        <v>104537</v>
       </c>
       <c r="L214" t="s">
         <v>900</v>
@@ -15021,7 +15021,7 @@
         <v>605</v>
       </c>
       <c r="O214">
-        <v>4294</v>
+        <v>4375</v>
       </c>
       <c r="P214" t="s">
         <v>900</v>
@@ -15032,10 +15032,10 @@
         <v>229</v>
       </c>
       <c r="B215">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C215">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D215" t="s">
         <v>521</v>
@@ -15044,7 +15044,7 @@
         <v>601</v>
       </c>
       <c r="F215">
-        <v>129715</v>
+        <v>130586</v>
       </c>
       <c r="G215" t="s">
         <v>607</v>
@@ -15060,7 +15060,7 @@
         <v>602</v>
       </c>
       <c r="K215">
-        <v>109295</v>
+        <v>109708</v>
       </c>
       <c r="L215" t="s">
         <v>899</v>
@@ -15072,7 +15072,7 @@
         <v>1193</v>
       </c>
       <c r="O215">
-        <v>3655</v>
+        <v>3665</v>
       </c>
       <c r="P215" t="s">
         <v>899</v>
@@ -15086,7 +15086,7 @@
         <v>22</v>
       </c>
       <c r="C216">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D216" t="s">
         <v>522</v>
@@ -15095,10 +15095,10 @@
         <v>601</v>
       </c>
       <c r="F216">
-        <v>125212</v>
+        <v>129875</v>
       </c>
       <c r="G216" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H216">
         <f>F216-K216</f>
@@ -15111,10 +15111,10 @@
         <v>602</v>
       </c>
       <c r="K216">
-        <v>94041</v>
+        <v>97185</v>
       </c>
       <c r="L216" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M216" t="s">
         <v>1113</v>
@@ -15123,10 +15123,10 @@
         <v>605</v>
       </c>
       <c r="O216">
-        <v>5265</v>
+        <v>5365</v>
       </c>
       <c r="P216" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -15327,7 +15327,7 @@
         <v>1197</v>
       </c>
       <c r="O220">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="P220" t="s">
         <v>899</v>
@@ -15545,7 +15545,7 @@
         <v>20</v>
       </c>
       <c r="C225">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D225" t="s">
         <v>530</v>
@@ -15554,10 +15554,10 @@
         <v>601</v>
       </c>
       <c r="F225">
-        <v>88512</v>
+        <v>89885</v>
       </c>
       <c r="G225" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H225">
         <f>F225-K225</f>
@@ -15570,10 +15570,10 @@
         <v>602</v>
       </c>
       <c r="K225">
-        <v>57413</v>
+        <v>59379</v>
       </c>
       <c r="L225" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M225" t="s">
         <v>1122</v>
@@ -15582,10 +15582,10 @@
         <v>605</v>
       </c>
       <c r="O225">
-        <v>5376</v>
+        <v>5451</v>
       </c>
       <c r="P225" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -17400,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="s">
-        <v>593</v>
+        <v>865</v>
       </c>
       <c r="J261" t="s">
         <v>602</v>
@@ -17451,7 +17451,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J262" t="s">
         <v>602</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="I263" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J263" t="s">
         <v>602</v>
@@ -17553,7 +17553,7 @@
         <v>0</v>
       </c>
       <c r="I264" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J264" t="s">
         <v>602</v>
@@ -17604,7 +17604,7 @@
         <v>0</v>
       </c>
       <c r="I265" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J265" t="s">
         <v>602</v>
@@ -17655,7 +17655,7 @@
         <v>0</v>
       </c>
       <c r="I266" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J266" t="s">
         <v>602</v>
@@ -17687,7 +17687,7 @@
         <v>16</v>
       </c>
       <c r="C267">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D267" t="s">
         <v>572</v>
@@ -17696,7 +17696,7 @@
         <v>602</v>
       </c>
       <c r="F267">
-        <v>74796</v>
+        <v>107832</v>
       </c>
       <c r="G267" t="s">
         <v>608</v>
@@ -17706,13 +17706,13 @@
         <v>0</v>
       </c>
       <c r="I267" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J267" t="s">
         <v>601</v>
       </c>
       <c r="K267">
-        <v>60328</v>
+        <v>98625</v>
       </c>
       <c r="L267" t="s">
         <v>900</v>
@@ -17724,7 +17724,7 @@
         <v>605</v>
       </c>
       <c r="O267">
-        <v>12361</v>
+        <v>18579</v>
       </c>
       <c r="P267" t="s">
         <v>900</v>
@@ -17757,7 +17757,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J268" t="s">
         <v>602</v>
@@ -17808,7 +17808,7 @@
         <v>0</v>
       </c>
       <c r="I269" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J269" t="s">
         <v>602</v>
@@ -17859,7 +17859,7 @@
         <v>0</v>
       </c>
       <c r="I270" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J270" t="s">
         <v>602</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="I271" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="J271" t="s">
         <v>602</v>
@@ -17961,7 +17961,7 @@
         <v>0</v>
       </c>
       <c r="I272" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J272" t="s">
         <v>602</v>
@@ -18012,7 +18012,7 @@
         <v>0</v>
       </c>
       <c r="I273" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J273" t="s">
         <v>602</v>
@@ -18063,7 +18063,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J274" t="s">
         <v>602</v>
@@ -18114,7 +18114,7 @@
         <v>0</v>
       </c>
       <c r="I275" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="J275" t="s">
         <v>602</v>
@@ -18165,7 +18165,7 @@
         <v>0</v>
       </c>
       <c r="I276" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J276" t="s">
         <v>602</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="I277" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J277" t="s">
         <v>602</v>
@@ -18267,7 +18267,7 @@
         <v>0</v>
       </c>
       <c r="I278" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="J278" t="s">
         <v>602</v>
@@ -18318,7 +18318,7 @@
         <v>0</v>
       </c>
       <c r="I279" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J279" t="s">
         <v>602</v>
@@ -18369,7 +18369,7 @@
         <v>0</v>
       </c>
       <c r="I280" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="J280" t="s">
         <v>602</v>
@@ -18420,7 +18420,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J281" t="s">
         <v>602</v>
@@ -18471,7 +18471,7 @@
         <v>0</v>
       </c>
       <c r="I282" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J282" t="s">
         <v>602</v>
@@ -18522,7 +18522,7 @@
         <v>0</v>
       </c>
       <c r="I283" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="J283" t="s">
         <v>602</v>
@@ -18573,7 +18573,7 @@
         <v>0</v>
       </c>
       <c r="I284" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="J284" t="s">
         <v>602</v>
@@ -18624,7 +18624,7 @@
         <v>0</v>
       </c>
       <c r="I285" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J285" t="s">
         <v>602</v>
@@ -18653,10 +18653,10 @@
         <v>300</v>
       </c>
       <c r="B286">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C286">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D286" t="s">
         <v>591</v>
@@ -18665,26 +18665,26 @@
         <v>601</v>
       </c>
       <c r="F286">
-        <v>117754</v>
+        <v>124243</v>
       </c>
       <c r="G286" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H286">
         <f>F286-K286</f>
         <v>0</v>
       </c>
       <c r="I286" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="J286" t="s">
         <v>602</v>
       </c>
       <c r="K286">
-        <v>83964</v>
+        <v>95557</v>
       </c>
       <c r="L286" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M286" t="s">
         <v>1182</v>
@@ -18693,10 +18693,10 @@
         <v>605</v>
       </c>
       <c r="O286">
-        <v>7152</v>
+        <v>8064</v>
       </c>
       <c r="P286" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -18707,7 +18707,7 @@
         <v>23</v>
       </c>
       <c r="C287">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D287" t="s">
         <v>592</v>
@@ -18716,10 +18716,10 @@
         <v>602</v>
       </c>
       <c r="F287">
-        <v>109333</v>
+        <v>114915</v>
       </c>
       <c r="G287" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H287">
         <f>F287-K287</f>
@@ -18732,10 +18732,10 @@
         <v>601</v>
       </c>
       <c r="K287">
-        <v>95979</v>
+        <v>101727</v>
       </c>
       <c r="L287" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M287" t="s">
         <v>1183</v>
@@ -18744,10 +18744,10 @@
         <v>606</v>
       </c>
       <c r="O287">
-        <v>17526</v>
+        <v>18390</v>
       </c>
       <c r="P287" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -18758,35 +18758,35 @@
         <v>24</v>
       </c>
       <c r="C288">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D288" t="s">
         <v>593</v>
       </c>
       <c r="E288" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F288">
-        <v>96177</v>
+        <v>119910</v>
       </c>
       <c r="G288" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H288">
         <f>F288-K288</f>
         <v>0</v>
       </c>
       <c r="I288" t="s">
-        <v>890</v>
+        <v>865</v>
       </c>
       <c r="J288" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K288">
-        <v>89529</v>
+        <v>111788</v>
       </c>
       <c r="L288" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M288" t="s">
         <v>1184</v>
@@ -18795,10 +18795,10 @@
         <v>605</v>
       </c>
       <c r="O288">
-        <v>7278</v>
+        <v>10589</v>
       </c>
       <c r="P288" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -18806,10 +18806,10 @@
         <v>303</v>
       </c>
       <c r="B289">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C289">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D289" t="s">
         <v>594</v>
@@ -18818,7 +18818,7 @@
         <v>601</v>
       </c>
       <c r="F289">
-        <v>105830</v>
+        <v>106402</v>
       </c>
       <c r="G289" t="s">
         <v>607</v>
@@ -18834,7 +18834,7 @@
         <v>602</v>
       </c>
       <c r="K289">
-        <v>102647</v>
+        <v>102852</v>
       </c>
       <c r="L289" t="s">
         <v>899</v>
@@ -18846,7 +18846,7 @@
         <v>605</v>
       </c>
       <c r="O289">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="P289" t="s">
         <v>899</v>
@@ -18962,7 +18962,7 @@
         <v>23</v>
       </c>
       <c r="C292">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D292" t="s">
         <v>597</v>
@@ -18971,10 +18971,10 @@
         <v>601</v>
       </c>
       <c r="F292">
-        <v>111249</v>
+        <v>111920</v>
       </c>
       <c r="G292" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H292">
         <f>F292-K292</f>
@@ -18987,10 +18987,10 @@
         <v>602</v>
       </c>
       <c r="K292">
-        <v>87335</v>
+        <v>87687</v>
       </c>
       <c r="L292" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M292" t="s">
         <v>1188</v>
@@ -18999,10 +18999,10 @@
         <v>605</v>
       </c>
       <c r="O292">
-        <v>22918</v>
+        <v>22994</v>
       </c>
       <c r="P292" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -19013,7 +19013,7 @@
         <v>21</v>
       </c>
       <c r="C293">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D293" t="s">
         <v>598</v>
@@ -19022,7 +19022,7 @@
         <v>602</v>
       </c>
       <c r="F293">
-        <v>81389</v>
+        <v>87827</v>
       </c>
       <c r="G293" t="s">
         <v>608</v>
@@ -19038,7 +19038,7 @@
         <v>601</v>
       </c>
       <c r="K293">
-        <v>43919</v>
+        <v>56684</v>
       </c>
       <c r="L293" t="s">
         <v>900</v>
@@ -19050,7 +19050,7 @@
         <v>605</v>
       </c>
       <c r="O293">
-        <v>19309</v>
+        <v>19796</v>
       </c>
       <c r="P293" t="s">
         <v>900</v>
@@ -19061,10 +19061,10 @@
         <v>308</v>
       </c>
       <c r="B294">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C294">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D294" t="s">
         <v>599</v>
@@ -19073,7 +19073,7 @@
         <v>602</v>
       </c>
       <c r="F294">
-        <v>65787</v>
+        <v>84854</v>
       </c>
       <c r="G294" t="s">
         <v>608</v>
@@ -19089,7 +19089,7 @@
         <v>601</v>
       </c>
       <c r="K294">
-        <v>59048</v>
+        <v>69715</v>
       </c>
       <c r="L294" t="s">
         <v>900</v>
@@ -19101,7 +19101,7 @@
         <v>603</v>
       </c>
       <c r="O294">
-        <v>29045</v>
+        <v>44425</v>
       </c>
       <c r="P294" t="s">
         <v>900</v>

--- a/WB_Election_Results_2026.xlsx
+++ b/WB_Election_Results_2026.xlsx
@@ -1295,898 +1295,898 @@
     <t>TARUNJYOTI TEWARI</t>
   </si>
   <si>
+    <t>RATHIN GHOSH</t>
+  </si>
+  <si>
+    <t>SANKAR CHATTERJEE</t>
+  </si>
+  <si>
+    <t>ANISUR RAHAMAN BIDESH</t>
+  </si>
+  <si>
+    <t>ABDUL MATIN MUHAMMAD</t>
+  </si>
+  <si>
+    <t>USHA RANI MONDAL</t>
+  </si>
+  <si>
+    <t>SANAT SARDAR</t>
+  </si>
+  <si>
+    <t>SURAJIT MITRA (BADAL)</t>
+  </si>
+  <si>
+    <t>MD. TAUSEFFUR RAHMAN</t>
+  </si>
+  <si>
+    <t>REKHA PATRA</t>
+  </si>
+  <si>
+    <t>BIKARNA NASKAR</t>
+  </si>
+  <si>
+    <t>NILIMA MISTRY BISHAL</t>
+  </si>
+  <si>
+    <t>GANESH CHANDRA MONDAL</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR JANA</t>
+  </si>
+  <si>
+    <t>DIPANKAR JANA</t>
+  </si>
+  <si>
+    <t>SUMANTA MANDAL</t>
+  </si>
+  <si>
+    <t>BARNALI DHARA</t>
+  </si>
+  <si>
+    <t>TAPAS MONDAL S/O-SHIBPRASAD MONDAL</t>
+  </si>
+  <si>
+    <t>JOYDEB HALDER S/O - KARTICK CHANDRA HALDER</t>
+  </si>
+  <si>
+    <t>BISWANATH DAS</t>
+  </si>
+  <si>
+    <t>BIVAS SARDAR</t>
+  </si>
+  <si>
+    <t>PARESH RAM DAS</t>
+  </si>
+  <si>
+    <t>MD BAHARUL ISLAM</t>
+  </si>
+  <si>
+    <t>BIMAN BANERJEE</t>
+  </si>
+  <si>
+    <t>SARMISTHA PURKAIT</t>
+  </si>
+  <si>
+    <t>MD. SAMIM AHAMED MOLLA</t>
+  </si>
+  <si>
+    <t>PANNA LAL HALDER</t>
+  </si>
+  <si>
+    <t>ABDUR RAZZAK MOLLA</t>
+  </si>
+  <si>
+    <t>AGNISWAR NASKAR</t>
+  </si>
+  <si>
+    <t>DILIP MONDAL</t>
+  </si>
+  <si>
+    <t>RUPA GANGULY</t>
+  </si>
+  <si>
+    <t>MD NAWSAD SIDDIQUE</t>
+  </si>
+  <si>
+    <t>AHMED JAVED KHAN</t>
+  </si>
+  <si>
+    <t>SARBORI MUKHERJEE</t>
+  </si>
+  <si>
+    <t>DEBASISH DHAR</t>
+  </si>
+  <si>
+    <t>PAPIA ADHIKARY</t>
+  </si>
+  <si>
+    <t>SANKAR SIKDER</t>
+  </si>
+  <si>
+    <t>DR. INDRANIL KHAN</t>
+  </si>
+  <si>
+    <t>SUBHASIS DAS</t>
+  </si>
+  <si>
+    <t>ASHOK KUMAR DEB</t>
+  </si>
+  <si>
+    <t>ABDUL KHALEQUE MOLLA</t>
+  </si>
+  <si>
+    <t>FIRHAD HAKIM</t>
+  </si>
+  <si>
+    <t>ADHIKARI SUVENDU</t>
+  </si>
+  <si>
+    <t>DASGUPTA SWAPAN</t>
+  </si>
+  <si>
+    <t>SOBHANDEB CHATTOPADHYAY</t>
+  </si>
+  <si>
+    <t>BANDYOPADHYAY NAYNA</t>
+  </si>
+  <si>
+    <t>SANDIPAN SAHA</t>
+  </si>
+  <si>
+    <t>KUNAL KUMAR GHOSH</t>
+  </si>
+  <si>
+    <t>VIJAY OJHA</t>
+  </si>
+  <si>
+    <t>PURNIMA CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>TAPAS ROY</t>
+  </si>
+  <si>
+    <t>RITESH TIWARI</t>
+  </si>
+  <si>
+    <t>SANJAY KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>UMESH RAI</t>
+  </si>
+  <si>
+    <t>ARUP ROY</t>
+  </si>
+  <si>
+    <t>RUDRANIL GHOSH</t>
+  </si>
+  <si>
+    <t>NANDITA CHOWDHURY</t>
+  </si>
+  <si>
+    <t>PRIYA PAUL</t>
+  </si>
+  <si>
+    <t>GULSAN MULLICK</t>
+  </si>
+  <si>
+    <t>RITABRATA BANERJEE</t>
+  </si>
+  <si>
+    <t>CHIRAN BERA</t>
+  </si>
+  <si>
+    <t>PULAK ROY</t>
+  </si>
+  <si>
+    <t>DR. HIRANMOY CHATTOPADHYAYA (HIRAAN)</t>
+  </si>
+  <si>
+    <t>ARUNAVA SEN</t>
+  </si>
+  <si>
+    <t>AMIT SAMANTA</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR PANJA</t>
+  </si>
+  <si>
+    <t>ANUPAM GHOSH</t>
+  </si>
+  <si>
+    <t>TAPAS MAITY</t>
+  </si>
+  <si>
+    <t>DIPANJAN CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>BHASKAR BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>DILIP SINGH</t>
+  </si>
+  <si>
+    <t>ARUP KUMAR DAS</t>
+  </si>
+  <si>
+    <t>Deepanjan Kumar Guha</t>
+  </si>
+  <si>
+    <t>SUBIR NAG</t>
+  </si>
+  <si>
+    <t>SUMANA SARKAR</t>
+  </si>
+  <si>
+    <t>TUSAR KUMAR MAJUMDAR</t>
+  </si>
+  <si>
+    <t>SWARAJ GHOSH</t>
+  </si>
+  <si>
+    <t>SWATI KHANDOKER</t>
+  </si>
+  <si>
+    <t>PROSENJIT BAG</t>
+  </si>
+  <si>
+    <t>MADHUMITA GHOSH</t>
+  </si>
+  <si>
+    <t>ASIMA PATRA</t>
+  </si>
+  <si>
+    <t>SANTU PAN</t>
+  </si>
+  <si>
+    <t>BIMAN GHOSH</t>
+  </si>
+  <si>
+    <t>BAG HEMANTA</t>
+  </si>
+  <si>
+    <t>PRASANTA DIGAR</t>
+  </si>
+  <si>
+    <t>SUSANTA GHOSH</t>
+  </si>
+  <si>
+    <t>HARE KRISHNA BERA</t>
+  </si>
+  <si>
+    <t>SUBRATA MAITY(RANA)</t>
+  </si>
+  <si>
+    <t>SINTU SENAPATI</t>
+  </si>
+  <si>
+    <t>ASHOKE DINDA</t>
+  </si>
+  <si>
+    <t>KHANRA NIRMAL</t>
+  </si>
+  <si>
+    <t>SUBHAS CHANDRA PANJA</t>
+  </si>
+  <si>
+    <t>PRADIP KUMAR BIJALI</t>
+  </si>
+  <si>
+    <t>PIJUSH KANTI DAS</t>
+  </si>
+  <si>
+    <t>TAPAN MAITY</t>
+  </si>
+  <si>
+    <t>SUMITA SINHA</t>
+  </si>
+  <si>
+    <t>SANTANU PRAMANIK</t>
+  </si>
+  <si>
+    <t>SUBRATA PAIK</t>
+  </si>
+  <si>
+    <t>DR. CHANDRA SEKHAR MONDAL</t>
+  </si>
+  <si>
+    <t>ADHIKARI DIBYENDU</t>
+  </si>
+  <si>
+    <t>AJIT KUMAR JANA</t>
+  </si>
+  <si>
+    <t>AMIYA KISKU</t>
+  </si>
+  <si>
+    <t>RAJESH MAHATA</t>
+  </si>
+  <si>
+    <t>LAKSHMI KANTA SAU</t>
+  </si>
+  <si>
+    <t>BHADRA HEMRAM</t>
+  </si>
+  <si>
+    <t>DILIP GHOSH</t>
+  </si>
+  <si>
+    <t>GIRI RAMAPRASAD</t>
+  </si>
+  <si>
+    <t>AMAL KUMAR PANDA</t>
+  </si>
+  <si>
+    <t>SWAGATA MANNA</t>
+  </si>
+  <si>
+    <t>DINEN ROY</t>
+  </si>
+  <si>
+    <t>SUBHASHIS OM</t>
+  </si>
+  <si>
+    <t>TAPAN KUMAR DUTTA</t>
+  </si>
+  <si>
+    <t>SITAL KAPAT</t>
+  </si>
+  <si>
+    <t>SUKANTA DOLUI</t>
+  </si>
+  <si>
+    <t>PRADIP LODHA</t>
+  </si>
+  <si>
+    <t>BIMAN MAHATA</t>
+  </si>
+  <si>
+    <t>SEULI SAHA</t>
+  </si>
+  <si>
+    <t>SANKAR KUMAR GUCHHAIT</t>
+  </si>
+  <si>
+    <t>DR. PRANAT TUDU</t>
+  </si>
+  <si>
+    <t>LABSEN BASKEY</t>
+  </si>
+  <si>
+    <t>JALADHAR MAHATO</t>
+  </si>
+  <si>
+    <t>RAHIDAS MAHATO</t>
+  </si>
+  <si>
+    <t>BISWAJIT MAHATO</t>
+  </si>
+  <si>
+    <t>SUDIP KUMAR MUKHERJEE</t>
+  </si>
+  <si>
+    <t>MAYNA MURMU</t>
+  </si>
+  <si>
+    <t>KAMALA KANTA HANSDA</t>
+  </si>
+  <si>
+    <t>NADIAR CHAND BOURI</t>
+  </si>
+  <si>
+    <t>MAMONI BAURI</t>
+  </si>
+  <si>
+    <t>CHANDANA BAURI</t>
+  </si>
+  <si>
+    <t>SATYANARAYAN MUKHOPADHYAY</t>
+  </si>
+  <si>
+    <t>KSHUDIRAM TUDU</t>
+  </si>
+  <si>
+    <t>KSHETRAMOHAN HANSDA</t>
+  </si>
+  <si>
+    <t>SOUVIK PATRA</t>
+  </si>
+  <si>
+    <t>NILADRI SEKHAR DANA</t>
+  </si>
+  <si>
+    <t>BILLESWAR SINHA</t>
+  </si>
+  <si>
+    <t>AMARNATH SHAKHA</t>
+  </si>
+  <si>
+    <t>SHUKLA CHATTERJEE</t>
+  </si>
+  <si>
+    <t>LAKSHMI KANTA MAJUMDAR</t>
+  </si>
+  <si>
+    <t>NIRMAL KUMAR DHARA</t>
+  </si>
+  <si>
+    <t>DIBAKAR GHARAMI</t>
+  </si>
+  <si>
+    <t>NABIN CHANDRA BAG</t>
+  </si>
+  <si>
+    <t>MOUMITA BISWAS MISRA</t>
+  </si>
+  <si>
+    <t>SUBHASH PATRA</t>
+  </si>
+  <si>
+    <t>ARUN HALDER</t>
+  </si>
+  <si>
+    <t>SAIKAT PANJA</t>
+  </si>
+  <si>
+    <t>SIDDHARTHA MAJUMDAR</t>
+  </si>
+  <si>
+    <t>MANAB GUHA</t>
+  </si>
+  <si>
+    <t>NISITH KUMAR MALIK</t>
+  </si>
+  <si>
+    <t>KARFA SOUMEN</t>
+  </si>
+  <si>
+    <t>PRAN KRISHNA TAPADAR</t>
+  </si>
+  <si>
+    <t>GOPAL CHATTOPADHYAY</t>
+  </si>
+  <si>
+    <t>KRISHNA GHOSH</t>
+  </si>
+  <si>
+    <t>ANADI GHOSH</t>
+  </si>
+  <si>
+    <t>SHISHIR GHOSH</t>
+  </si>
+  <si>
+    <t>KALITA MAJI</t>
+  </si>
+  <si>
+    <t>RAJU PATRA</t>
+  </si>
+  <si>
+    <t>JITENDRA KUMAR TEWARI</t>
+  </si>
+  <si>
+    <t>CHANDRA SEKHAR BANERJEE</t>
+  </si>
+  <si>
+    <t>LAKSHMAN CHANDRA GHORUI</t>
+  </si>
+  <si>
+    <t>PARTHA GHOSH</t>
+  </si>
+  <si>
+    <t>DR. BIJAN MUKHERJEE</t>
+  </si>
+  <si>
+    <t>AGNIMITRA PAUL</t>
+  </si>
+  <si>
+    <t>KRISHNENDU MUKHERJEE</t>
+  </si>
+  <si>
+    <t>AJAY KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>ARIJIT ROY</t>
+  </si>
+  <si>
+    <t>ANUP KUMAR SAHA</t>
+  </si>
+  <si>
+    <t>JAGANNATH CHATTOPADHYAY</t>
+  </si>
+  <si>
+    <t>CHANDRANATH SINHA</t>
+  </si>
+  <si>
+    <t>BIDHAN CHANDRA MAJHI</t>
+  </si>
+  <si>
+    <t>DEBASIS OJHA (HAKU DA)</t>
+  </si>
+  <si>
+    <t>KRISHNA KANTA SAHA</t>
+  </si>
+  <si>
+    <t>DUDH KUMAR MONDAL</t>
+  </si>
+  <si>
+    <t>DHRUBA SAHA</t>
+  </si>
+  <si>
+    <t>FAYEZUL HAQUE (KAJAL SK)</t>
+  </si>
+  <si>
+    <t>RAJENDRA PRASAD SINGH(RAJU SINGH)</t>
+  </si>
+  <si>
+    <t>DR. MOSARRAF HOSSAIN</t>
+  </si>
+  <si>
+    <t>Bharatiya Janata Party</t>
+  </si>
+  <si>
+    <t>All India Trinamool Congress</t>
+  </si>
+  <si>
+    <t>Indian National Congress</t>
+  </si>
+  <si>
+    <t>Aam Janata Unnayan party</t>
+  </si>
+  <si>
+    <t>Communist Party of India (Marxist)</t>
+  </si>
+  <si>
+    <t>All India Secular Front</t>
+  </si>
+  <si>
+    <t>Won</t>
+  </si>
+  <si>
+    <t>Leading</t>
+  </si>
+  <si>
+    <t>ADHIKARY PARESH CHANDRA</t>
+  </si>
+  <si>
+    <t>DR. SABLU BARMAN</t>
+  </si>
+  <si>
+    <t>PARTHA PRATIM RAY</t>
+  </si>
+  <si>
+    <t>AVIJIT DE BHOWMIK</t>
+  </si>
+  <si>
+    <t>HARIHAR DAS</t>
+  </si>
+  <si>
+    <t>ASHUTOSH BARMA</t>
+  </si>
+  <si>
+    <t>UDAYAN GUHA</t>
+  </si>
+  <si>
+    <t>SAILENDRA NATH BARMA</t>
+  </si>
+  <si>
+    <t>SHIBSANKAR PAUL</t>
+  </si>
+  <si>
+    <t>RAJEEV TIRKEY</t>
+  </si>
+  <si>
+    <t>BIRENDRA BARA (ORAON)</t>
+  </si>
+  <si>
+    <t>SUMAN KANJILAL</t>
+  </si>
+  <si>
+    <t>SUBHASH CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>JAYPRAKASH TOPPO</t>
+  </si>
+  <si>
+    <t>NIRMAL CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>RAMMOHAN RAY</t>
+  </si>
+  <si>
+    <t>KRISHNA DAS</t>
+  </si>
+  <si>
+    <t>SWAPNA BARMAN</t>
+  </si>
+  <si>
+    <t>RANJAN SIL SHARMA</t>
+  </si>
+  <si>
+    <t>BULU CHIK BARAIK</t>
+  </si>
+  <si>
+    <t>SANJAY KUJUR</t>
+  </si>
+  <si>
+    <t>RUDEN SADA LEPCHA</t>
+  </si>
+  <si>
+    <t>BIJOY KUMAR RAI</t>
+  </si>
+  <si>
+    <t>AMAR LAMA</t>
+  </si>
+  <si>
+    <t>SHANKAR MALAKAR</t>
+  </si>
+  <si>
+    <t>GOUTAM DEB</t>
+  </si>
+  <si>
+    <t>REENA TOPNO EKKA</t>
+  </si>
+  <si>
+    <t>SANKAR ADHIKARI</t>
+  </si>
+  <si>
+    <t>CHITRAJIT ROY</t>
+  </si>
+  <si>
+    <t>SARAJIT BISWAS</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR JAIN</t>
+  </si>
+  <si>
+    <t>GOUTAM PAUL</t>
+  </si>
+  <si>
+    <t>SATYAJIT BARMAN</t>
+  </si>
+  <si>
+    <t>NITAI BAISHYA</t>
+  </si>
+  <si>
+    <t>KRISHNA KALYANI</t>
+  </si>
+  <si>
+    <t>SABITA BARMAN</t>
+  </si>
+  <si>
+    <t>REKHA ROY</t>
+  </si>
+  <si>
+    <t>SUBHENDU SARKAR</t>
+  </si>
+  <si>
+    <t>ARPITA GHOSH</t>
+  </si>
+  <si>
+    <t>CHINTAMANI BIHA</t>
+  </si>
+  <si>
+    <t>Goutam Das</t>
+  </si>
+  <si>
+    <t>DEBABRATA MAJUMDER</t>
+  </si>
+  <si>
+    <t>AMAL KISKU</t>
+  </si>
+  <si>
+    <t>PRASENJIT DAS</t>
+  </si>
+  <si>
+    <t>RATAN DAS</t>
+  </si>
+  <si>
+    <t>MAUSAM B NOOR</t>
+  </si>
+  <si>
+    <t>ABISHEK SINGHANIA</t>
+  </si>
+  <si>
+    <t>KABITA MANDAL</t>
+  </si>
+  <si>
+    <t>LIPIKA BARMAN GHOSH</t>
+  </si>
+  <si>
+    <t>ASIS KUNDU (PATA)</t>
+  </si>
+  <si>
+    <t>NIBARAN GHOSH</t>
+  </si>
+  <si>
+    <t>ABDUL HANNAN</t>
+  </si>
+  <si>
+    <t>CHANDANA SARKAR</t>
+  </si>
+  <si>
+    <t>SUNIL CHOWDHURI</t>
+  </si>
+  <si>
+    <t>MD NAJME ALAM</t>
+  </si>
+  <si>
+    <t>MAHABIR GHOSH</t>
+  </si>
+  <si>
+    <t>JAKIR HOSSAIN</t>
+  </si>
+  <si>
+    <t>NASIR SAIKH</t>
+  </si>
+  <si>
+    <t>TAPAS KUMAR CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>TOUHIDUR RAHAMAN SUMAN</t>
+  </si>
+  <si>
+    <t>MAHAMUDAL HASAN</t>
+  </si>
+  <si>
+    <t>ABDUL SOUMIK HOSSAIN</t>
+  </si>
+  <si>
+    <t>SHAONI SINGHA ROY</t>
+  </si>
+  <si>
+    <t>PRONAB CHANDRA DAS</t>
+  </si>
+  <si>
+    <t>ASHIS MARJIT</t>
+  </si>
+  <si>
+    <t>PROTIMA RAJAK</t>
+  </si>
+  <si>
+    <t>APURBA SARKAR (DAVID)</t>
+  </si>
+  <si>
+    <t>ANAMIKA GHOSH</t>
+  </si>
+  <si>
+    <t>BAPAN GHOSH</t>
+  </si>
+  <si>
+    <t>RABIUL ALAM CHOWDHURY</t>
+  </si>
+  <si>
+    <t>ADHIR RANJAN CHOWDHURY</t>
+  </si>
+  <si>
+    <t>BIJOY SEKH</t>
+  </si>
+  <si>
+    <t>RANA MANDAL</t>
+  </si>
+  <si>
+    <t>IANUS ALI SARKAR</t>
+  </si>
+  <si>
+    <t>SOHAM CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>DILIP KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>ANIMA DUTTA</t>
+  </si>
+  <si>
+    <t>KALLOL KHAN</t>
+  </si>
+  <si>
+    <t>SAIKAT SARKAR</t>
+  </si>
+  <si>
+    <t>SOMNATH DUTTA</t>
+  </si>
+  <si>
+    <t>PUNDARIKAKSHYA SAHA</t>
+  </si>
+  <si>
+    <t>UJJAL BISWAS</t>
+  </si>
+  <si>
+    <t>BRAJAKISHORE GOSWAMI</t>
+  </si>
+  <si>
+    <t>TAPAS KUMAR GHOSH</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>BARNALI DEY ROY</t>
+  </si>
+  <si>
+    <t>SOUGATA KUMAR BURMAN</t>
+  </si>
+  <si>
+    <t>SUBHANKAR SINGHA (JISHU)</t>
+  </si>
+  <si>
+    <t>DR. ATINDRA NATH MONDAL</t>
+  </si>
+  <si>
+    <t>DR. RAJIB BISWAS.</t>
+  </si>
+  <si>
+    <t>MADHUPARNA THAKUR</t>
+  </si>
+  <si>
+    <t>BISWAJIT DAS</t>
+  </si>
+  <si>
+    <t>RITUPARNA ADDHYA</t>
+  </si>
+  <si>
+    <t>NAROTTAM BISWAS</t>
+  </si>
+  <si>
+    <t>TARAK SAHA</t>
+  </si>
+  <si>
+    <t>SUKRITI KUMAR SARKAR</t>
+  </si>
+  <si>
+    <t>JYOTI PRIYA MALLICK</t>
+  </si>
+  <si>
+    <t>NARAYAN GOSWAMI</t>
+  </si>
+  <si>
+    <t>ARINDAM DEY</t>
+  </si>
+  <si>
+    <t>SUBODH ADHIKARY</t>
+  </si>
+  <si>
+    <t>SANAT DEY</t>
+  </si>
+  <si>
+    <t>AMIT GUPTA</t>
+  </si>
+  <si>
+    <t>SOMENATH SHYAM ICHINI</t>
+  </si>
+  <si>
+    <t>TRINANKUR BHATTACHARJEE</t>
+  </si>
+  <si>
+    <t>RAJ CHAKRABORTY (RAJU)</t>
+  </si>
+  <si>
+    <t>DEVADEEP PUROHIT</t>
+  </si>
+  <si>
+    <t>CHANDRIMA BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>TIRTHANKAR GHOSH</t>
+  </si>
+  <si>
+    <t>ARUP CHOUDHURY (PULAK)</t>
+  </si>
+  <si>
+    <t>SAYANTIKA BANERJEE</t>
+  </si>
+  <si>
+    <t>BRATYABRATA BASU</t>
+  </si>
+  <si>
+    <t>PIYUSH KANODIA</t>
+  </si>
+  <si>
+    <t>SUJIT BOSE</t>
+  </si>
+  <si>
+    <t>ADITI MUNSHI</t>
+  </si>
+  <si>
     <t>ANINDYA BANERJEE</t>
-  </si>
-  <si>
-    <t>SANKAR CHATTERJEE</t>
-  </si>
-  <si>
-    <t>ANISUR RAHAMAN BIDESH</t>
-  </si>
-  <si>
-    <t>ABDUL MATIN MUHAMMAD</t>
-  </si>
-  <si>
-    <t>USHA RANI MONDAL</t>
-  </si>
-  <si>
-    <t>SANAT SARDAR</t>
-  </si>
-  <si>
-    <t>SURAJIT MITRA (BADAL)</t>
-  </si>
-  <si>
-    <t>MD. TAUSEFFUR RAHMAN</t>
-  </si>
-  <si>
-    <t>REKHA PATRA</t>
-  </si>
-  <si>
-    <t>BIKARNA NASKAR</t>
-  </si>
-  <si>
-    <t>NILIMA MISTRY BISHAL</t>
-  </si>
-  <si>
-    <t>GANESH CHANDRA MONDAL</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR JANA</t>
-  </si>
-  <si>
-    <t>DIPANKAR JANA</t>
-  </si>
-  <si>
-    <t>SUMANTA MANDAL</t>
-  </si>
-  <si>
-    <t>BARNALI DHARA</t>
-  </si>
-  <si>
-    <t>TAPAS MONDAL S/O-SHIBPRASAD MONDAL</t>
-  </si>
-  <si>
-    <t>JOYDEB HALDER S/O - KARTICK CHANDRA HALDER</t>
-  </si>
-  <si>
-    <t>BISWANATH DAS</t>
-  </si>
-  <si>
-    <t>BIVAS SARDAR</t>
-  </si>
-  <si>
-    <t>PARESH RAM DAS</t>
-  </si>
-  <si>
-    <t>MD BAHARUL ISLAM</t>
-  </si>
-  <si>
-    <t>BIMAN BANERJEE</t>
-  </si>
-  <si>
-    <t>SARMISTHA PURKAIT</t>
-  </si>
-  <si>
-    <t>MD. SAMIM AHAMED MOLLA</t>
-  </si>
-  <si>
-    <t>PANNA LAL HALDER</t>
-  </si>
-  <si>
-    <t>ABDUR RAZZAK MOLLA</t>
-  </si>
-  <si>
-    <t>AGNISWAR NASKAR</t>
-  </si>
-  <si>
-    <t>DILIP MONDAL</t>
-  </si>
-  <si>
-    <t>RUPA GANGULY</t>
-  </si>
-  <si>
-    <t>MD NAWSAD SIDDIQUE</t>
-  </si>
-  <si>
-    <t>AHMED JAVED KHAN</t>
-  </si>
-  <si>
-    <t>SARBORI MUKHERJEE</t>
-  </si>
-  <si>
-    <t>DEBASISH DHAR</t>
-  </si>
-  <si>
-    <t>PAPIA ADHIKARY</t>
-  </si>
-  <si>
-    <t>SANKAR SIKDER</t>
-  </si>
-  <si>
-    <t>DR. INDRANIL KHAN</t>
-  </si>
-  <si>
-    <t>SUBHASIS DAS</t>
-  </si>
-  <si>
-    <t>ASHOK KUMAR DEB</t>
-  </si>
-  <si>
-    <t>ABDUL KHALEQUE MOLLA</t>
-  </si>
-  <si>
-    <t>FIRHAD HAKIM</t>
-  </si>
-  <si>
-    <t>ADHIKARI SUVENDU</t>
-  </si>
-  <si>
-    <t>DASGUPTA SWAPAN</t>
-  </si>
-  <si>
-    <t>SOBHANDEB CHATTOPADHYAY</t>
-  </si>
-  <si>
-    <t>BANDYOPADHYAY NAYNA</t>
-  </si>
-  <si>
-    <t>SANDIPAN SAHA</t>
-  </si>
-  <si>
-    <t>KUNAL KUMAR GHOSH</t>
-  </si>
-  <si>
-    <t>VIJAY OJHA</t>
-  </si>
-  <si>
-    <t>PURNIMA CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>TAPAS ROY</t>
-  </si>
-  <si>
-    <t>RITESH TIWARI</t>
-  </si>
-  <si>
-    <t>SANJAY KUMAR SINGH</t>
-  </si>
-  <si>
-    <t>UMESH RAI</t>
-  </si>
-  <si>
-    <t>ARUP ROY</t>
-  </si>
-  <si>
-    <t>RUDRANIL GHOSH</t>
-  </si>
-  <si>
-    <t>NANDITA CHOWDHURY</t>
-  </si>
-  <si>
-    <t>PRIYA PAUL</t>
-  </si>
-  <si>
-    <t>GULSAN MULLICK</t>
-  </si>
-  <si>
-    <t>RITABRATA BANERJEE</t>
-  </si>
-  <si>
-    <t>CHIRAN BERA</t>
-  </si>
-  <si>
-    <t>PULAK ROY</t>
-  </si>
-  <si>
-    <t>DR. HIRANMOY CHATTOPADHYAYA (HIRAAN)</t>
-  </si>
-  <si>
-    <t>ARUNAVA SEN</t>
-  </si>
-  <si>
-    <t>AMIT SAMANTA</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR PANJA</t>
-  </si>
-  <si>
-    <t>ANUPAM GHOSH</t>
-  </si>
-  <si>
-    <t>TAPAS MAITY</t>
-  </si>
-  <si>
-    <t>DIPANJAN CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>BHASKAR BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>DILIP SINGH</t>
-  </si>
-  <si>
-    <t>ARUP KUMAR DAS</t>
-  </si>
-  <si>
-    <t>Deepanjan Kumar Guha</t>
-  </si>
-  <si>
-    <t>SUBIR NAG</t>
-  </si>
-  <si>
-    <t>SUMANA SARKAR</t>
-  </si>
-  <si>
-    <t>TUSAR KUMAR MAJUMDAR</t>
-  </si>
-  <si>
-    <t>SWARAJ GHOSH</t>
-  </si>
-  <si>
-    <t>SWATI KHANDOKER</t>
-  </si>
-  <si>
-    <t>PROSENJIT BAG</t>
-  </si>
-  <si>
-    <t>MADHUMITA GHOSH</t>
-  </si>
-  <si>
-    <t>ASIMA PATRA</t>
-  </si>
-  <si>
-    <t>SANTU PAN</t>
-  </si>
-  <si>
-    <t>BIMAN GHOSH</t>
-  </si>
-  <si>
-    <t>BAG HEMANTA</t>
-  </si>
-  <si>
-    <t>PRASANTA DIGAR</t>
-  </si>
-  <si>
-    <t>SUSANTA GHOSH</t>
-  </si>
-  <si>
-    <t>HARE KRISHNA BERA</t>
-  </si>
-  <si>
-    <t>SUBRATA MAITY(RANA)</t>
-  </si>
-  <si>
-    <t>SINTU SENAPATI</t>
-  </si>
-  <si>
-    <t>ASHOKE DINDA</t>
-  </si>
-  <si>
-    <t>KHANRA NIRMAL</t>
-  </si>
-  <si>
-    <t>SUBHAS CHANDRA PANJA</t>
-  </si>
-  <si>
-    <t>PRADIP KUMAR BIJALI</t>
-  </si>
-  <si>
-    <t>PIJUSH KANTI DAS</t>
-  </si>
-  <si>
-    <t>TAPAN MAITY</t>
-  </si>
-  <si>
-    <t>SUMITA SINHA</t>
-  </si>
-  <si>
-    <t>SANTANU PRAMANIK</t>
-  </si>
-  <si>
-    <t>SUBRATA PAIK</t>
-  </si>
-  <si>
-    <t>DR. CHANDRA SEKHAR MONDAL</t>
-  </si>
-  <si>
-    <t>ADHIKARI DIBYENDU</t>
-  </si>
-  <si>
-    <t>AJIT KUMAR JANA</t>
-  </si>
-  <si>
-    <t>AMIYA KISKU</t>
-  </si>
-  <si>
-    <t>RAJESH MAHATA</t>
-  </si>
-  <si>
-    <t>LAKSHMI KANTA SAU</t>
-  </si>
-  <si>
-    <t>BHADRA HEMRAM</t>
-  </si>
-  <si>
-    <t>DILIP GHOSH</t>
-  </si>
-  <si>
-    <t>GIRI RAMAPRASAD</t>
-  </si>
-  <si>
-    <t>AMAL KUMAR PANDA</t>
-  </si>
-  <si>
-    <t>SWAGATA MANNA</t>
-  </si>
-  <si>
-    <t>DINEN ROY</t>
-  </si>
-  <si>
-    <t>SUBHASHIS OM</t>
-  </si>
-  <si>
-    <t>TAPAN KUMAR DUTTA</t>
-  </si>
-  <si>
-    <t>SITAL KAPAT</t>
-  </si>
-  <si>
-    <t>SUKANTA DOLUI</t>
-  </si>
-  <si>
-    <t>PRADIP LODHA</t>
-  </si>
-  <si>
-    <t>BIMAN MAHATA</t>
-  </si>
-  <si>
-    <t>SEULI SAHA</t>
-  </si>
-  <si>
-    <t>SANKAR KUMAR GUCHHAIT</t>
-  </si>
-  <si>
-    <t>DR. PRANAT TUDU</t>
-  </si>
-  <si>
-    <t>LABSEN BASKEY</t>
-  </si>
-  <si>
-    <t>JALADHAR MAHATO</t>
-  </si>
-  <si>
-    <t>RAHIDAS MAHATO</t>
-  </si>
-  <si>
-    <t>BISWAJIT MAHATO</t>
-  </si>
-  <si>
-    <t>SUDIP KUMAR MUKHERJEE</t>
-  </si>
-  <si>
-    <t>MAYNA MURMU</t>
-  </si>
-  <si>
-    <t>KAMALA KANTA HANSDA</t>
-  </si>
-  <si>
-    <t>NADIAR CHAND BOURI</t>
-  </si>
-  <si>
-    <t>MAMONI BAURI</t>
-  </si>
-  <si>
-    <t>CHANDANA BAURI</t>
-  </si>
-  <si>
-    <t>SATYANARAYAN MUKHOPADHYAY</t>
-  </si>
-  <si>
-    <t>KSHUDIRAM TUDU</t>
-  </si>
-  <si>
-    <t>KSHETRAMOHAN HANSDA</t>
-  </si>
-  <si>
-    <t>SOUVIK PATRA</t>
-  </si>
-  <si>
-    <t>NILADRI SEKHAR DANA</t>
-  </si>
-  <si>
-    <t>BILLESWAR SINHA</t>
-  </si>
-  <si>
-    <t>AMARNATH SHAKHA</t>
-  </si>
-  <si>
-    <t>SHUKLA CHATTERJEE</t>
-  </si>
-  <si>
-    <t>LAKSHMI KANTA MAJUMDAR</t>
-  </si>
-  <si>
-    <t>NIRMAL KUMAR DHARA</t>
-  </si>
-  <si>
-    <t>DIBAKAR GHARAMI</t>
-  </si>
-  <si>
-    <t>NABIN CHANDRA BAG</t>
-  </si>
-  <si>
-    <t>MOUMITA BISWAS MISRA</t>
-  </si>
-  <si>
-    <t>SUBHASH PATRA</t>
-  </si>
-  <si>
-    <t>ARUN HALDER</t>
-  </si>
-  <si>
-    <t>SAIKAT PANJA</t>
-  </si>
-  <si>
-    <t>SIDDHARTHA MAJUMDAR</t>
-  </si>
-  <si>
-    <t>MANAB GUHA</t>
-  </si>
-  <si>
-    <t>NISITH KUMAR MALIK</t>
-  </si>
-  <si>
-    <t>KARFA SOUMEN</t>
-  </si>
-  <si>
-    <t>PRAN KRISHNA TAPADAR</t>
-  </si>
-  <si>
-    <t>GOPAL CHATTOPADHYAY</t>
-  </si>
-  <si>
-    <t>KRISHNA GHOSH</t>
-  </si>
-  <si>
-    <t>ANADI GHOSH</t>
-  </si>
-  <si>
-    <t>SHISHIR GHOSH</t>
-  </si>
-  <si>
-    <t>KALITA MAJI</t>
-  </si>
-  <si>
-    <t>RAJU PATRA</t>
-  </si>
-  <si>
-    <t>JITENDRA KUMAR TEWARI</t>
-  </si>
-  <si>
-    <t>CHANDRA SEKHAR BANERJEE</t>
-  </si>
-  <si>
-    <t>LAKSHMAN CHANDRA GHORUI</t>
-  </si>
-  <si>
-    <t>PARTHA GHOSH</t>
-  </si>
-  <si>
-    <t>DR. BIJAN MUKHERJEE</t>
-  </si>
-  <si>
-    <t>AGNIMITRA PAUL</t>
-  </si>
-  <si>
-    <t>KRISHNENDU MUKHERJEE</t>
-  </si>
-  <si>
-    <t>AJAY KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>ARIJIT ROY</t>
-  </si>
-  <si>
-    <t>ANUP KUMAR SAHA</t>
-  </si>
-  <si>
-    <t>JAGANNATH CHATTOPADHYAY</t>
-  </si>
-  <si>
-    <t>CHANDRANATH SINHA</t>
-  </si>
-  <si>
-    <t>BIDHAN CHANDRA MAJHI</t>
-  </si>
-  <si>
-    <t>DEBASIS OJHA (HAKU DA)</t>
-  </si>
-  <si>
-    <t>KRISHNA KANTA SAHA</t>
-  </si>
-  <si>
-    <t>DUDH KUMAR MONDAL</t>
-  </si>
-  <si>
-    <t>DHRUBA SAHA</t>
-  </si>
-  <si>
-    <t>FAYEZUL HAQUE (KAJAL SK)</t>
-  </si>
-  <si>
-    <t>RAJENDRA PRASAD SINGH(RAJU SINGH)</t>
-  </si>
-  <si>
-    <t>DR. MOSARRAF HOSSAIN</t>
-  </si>
-  <si>
-    <t>Bharatiya Janata Party</t>
-  </si>
-  <si>
-    <t>All India Trinamool Congress</t>
-  </si>
-  <si>
-    <t>Indian National Congress</t>
-  </si>
-  <si>
-    <t>Aam Janata Unnayan party</t>
-  </si>
-  <si>
-    <t>Communist Party of India (Marxist)</t>
-  </si>
-  <si>
-    <t>All India Secular Front</t>
-  </si>
-  <si>
-    <t>Won</t>
-  </si>
-  <si>
-    <t>Leading</t>
-  </si>
-  <si>
-    <t>ADHIKARY PARESH CHANDRA</t>
-  </si>
-  <si>
-    <t>DR. SABLU BARMAN</t>
-  </si>
-  <si>
-    <t>PARTHA PRATIM RAY</t>
-  </si>
-  <si>
-    <t>AVIJIT DE BHOWMIK</t>
-  </si>
-  <si>
-    <t>HARIHAR DAS</t>
-  </si>
-  <si>
-    <t>ASHUTOSH BARMA</t>
-  </si>
-  <si>
-    <t>UDAYAN GUHA</t>
-  </si>
-  <si>
-    <t>SAILENDRA NATH BARMA</t>
-  </si>
-  <si>
-    <t>SHIBSANKAR PAUL</t>
-  </si>
-  <si>
-    <t>RAJEEV TIRKEY</t>
-  </si>
-  <si>
-    <t>BIRENDRA BARA (ORAON)</t>
-  </si>
-  <si>
-    <t>SUMAN KANJILAL</t>
-  </si>
-  <si>
-    <t>SUBHASH CHANDRA ROY</t>
-  </si>
-  <si>
-    <t>JAYPRAKASH TOPPO</t>
-  </si>
-  <si>
-    <t>NIRMAL CHANDRA ROY</t>
-  </si>
-  <si>
-    <t>RAMMOHAN RAY</t>
-  </si>
-  <si>
-    <t>KRISHNA DAS</t>
-  </si>
-  <si>
-    <t>SWAPNA BARMAN</t>
-  </si>
-  <si>
-    <t>RANJAN SIL SHARMA</t>
-  </si>
-  <si>
-    <t>BULU CHIK BARAIK</t>
-  </si>
-  <si>
-    <t>SANJAY KUJUR</t>
-  </si>
-  <si>
-    <t>RUDEN SADA LEPCHA</t>
-  </si>
-  <si>
-    <t>BIJOY KUMAR RAI</t>
-  </si>
-  <si>
-    <t>AMAR LAMA</t>
-  </si>
-  <si>
-    <t>SHANKAR MALAKAR</t>
-  </si>
-  <si>
-    <t>GOUTAM DEB</t>
-  </si>
-  <si>
-    <t>REENA TOPNO EKKA</t>
-  </si>
-  <si>
-    <t>SANKAR ADHIKARI</t>
-  </si>
-  <si>
-    <t>CHITRAJIT ROY</t>
-  </si>
-  <si>
-    <t>SARAJIT BISWAS</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR JAIN</t>
-  </si>
-  <si>
-    <t>GOUTAM PAUL</t>
-  </si>
-  <si>
-    <t>SATYAJIT BARMAN</t>
-  </si>
-  <si>
-    <t>NITAI BAISHYA</t>
-  </si>
-  <si>
-    <t>KRISHNA KALYANI</t>
-  </si>
-  <si>
-    <t>SABITA BARMAN</t>
-  </si>
-  <si>
-    <t>REKHA ROY</t>
-  </si>
-  <si>
-    <t>SUBHENDU SARKAR</t>
-  </si>
-  <si>
-    <t>ARPITA GHOSH</t>
-  </si>
-  <si>
-    <t>CHINTAMANI BIHA</t>
-  </si>
-  <si>
-    <t>Goutam Das</t>
-  </si>
-  <si>
-    <t>DEBABRATA MAJUMDER</t>
-  </si>
-  <si>
-    <t>AMAL KISKU</t>
-  </si>
-  <si>
-    <t>PRASENJIT DAS</t>
-  </si>
-  <si>
-    <t>RATAN DAS</t>
-  </si>
-  <si>
-    <t>MAUSAM B NOOR</t>
-  </si>
-  <si>
-    <t>ABISHEK SINGHANIA</t>
-  </si>
-  <si>
-    <t>KABITA MANDAL</t>
-  </si>
-  <si>
-    <t>LIPIKA BARMAN GHOSH</t>
-  </si>
-  <si>
-    <t>ASIS KUNDU (PATA)</t>
-  </si>
-  <si>
-    <t>NIBARAN GHOSH</t>
-  </si>
-  <si>
-    <t>ABDUL HANNAN</t>
-  </si>
-  <si>
-    <t>CHANDANA SARKAR</t>
-  </si>
-  <si>
-    <t>SUNIL CHOWDHURI</t>
-  </si>
-  <si>
-    <t>MD NAJME ALAM</t>
-  </si>
-  <si>
-    <t>MAHABIR GHOSH</t>
-  </si>
-  <si>
-    <t>JAKIR HOSSAIN</t>
-  </si>
-  <si>
-    <t>NASIR SAIKH</t>
-  </si>
-  <si>
-    <t>TAPAS KUMAR CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>TOUHIDUR RAHAMAN SUMAN</t>
-  </si>
-  <si>
-    <t>MAHAMUDAL HASAN</t>
-  </si>
-  <si>
-    <t>ABDUL SOUMIK HOSSAIN</t>
-  </si>
-  <si>
-    <t>SHAONI SINGHA ROY</t>
-  </si>
-  <si>
-    <t>PRONAB CHANDRA DAS</t>
-  </si>
-  <si>
-    <t>ASHIS MARJIT</t>
-  </si>
-  <si>
-    <t>PROTIMA RAJAK</t>
-  </si>
-  <si>
-    <t>APURBA SARKAR (DAVID)</t>
-  </si>
-  <si>
-    <t>ANAMIKA GHOSH</t>
-  </si>
-  <si>
-    <t>BAPAN GHOSH</t>
-  </si>
-  <si>
-    <t>RABIUL ALAM CHOWDHURY</t>
-  </si>
-  <si>
-    <t>ADHIR RANJAN CHOWDHURY</t>
-  </si>
-  <si>
-    <t>BIJOY SEKH</t>
-  </si>
-  <si>
-    <t>RANA MANDAL</t>
-  </si>
-  <si>
-    <t>IANUS ALI SARKAR</t>
-  </si>
-  <si>
-    <t>SOHAM CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>DILIP KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>ANIMA DUTTA</t>
-  </si>
-  <si>
-    <t>KALLOL KHAN</t>
-  </si>
-  <si>
-    <t>SAIKAT SARKAR</t>
-  </si>
-  <si>
-    <t>SOMNATH DUTTA</t>
-  </si>
-  <si>
-    <t>PUNDARIKAKSHYA SAHA</t>
-  </si>
-  <si>
-    <t>UJJAL BISWAS</t>
-  </si>
-  <si>
-    <t>BRAJAKISHORE GOSWAMI</t>
-  </si>
-  <si>
-    <t>TAPAS KUMAR GHOSH</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>BARNALI DEY ROY</t>
-  </si>
-  <si>
-    <t>SOUGATA KUMAR BURMAN</t>
-  </si>
-  <si>
-    <t>SUBHANKAR SINGHA (JISHU)</t>
-  </si>
-  <si>
-    <t>DR. ATINDRA NATH MONDAL</t>
-  </si>
-  <si>
-    <t>DR. RAJIB BISWAS.</t>
-  </si>
-  <si>
-    <t>MADHUPARNA THAKUR</t>
-  </si>
-  <si>
-    <t>BISWAJIT DAS</t>
-  </si>
-  <si>
-    <t>RITUPARNA ADDHYA</t>
-  </si>
-  <si>
-    <t>NAROTTAM BISWAS</t>
-  </si>
-  <si>
-    <t>TARAK SAHA</t>
-  </si>
-  <si>
-    <t>SUKRITI KUMAR SARKAR</t>
-  </si>
-  <si>
-    <t>JYOTI PRIYA MALLICK</t>
-  </si>
-  <si>
-    <t>NARAYAN GOSWAMI</t>
-  </si>
-  <si>
-    <t>ARINDAM DEY</t>
-  </si>
-  <si>
-    <t>SUBODH ADHIKARY</t>
-  </si>
-  <si>
-    <t>SANAT DEY</t>
-  </si>
-  <si>
-    <t>AMIT GUPTA</t>
-  </si>
-  <si>
-    <t>SOMENATH SHYAM ICHINI</t>
-  </si>
-  <si>
-    <t>TRINANKUR BHATTACHARJEE</t>
-  </si>
-  <si>
-    <t>RAJ CHAKRABORTY (RAJU)</t>
-  </si>
-  <si>
-    <t>DEVADEEP PUROHIT</t>
-  </si>
-  <si>
-    <t>CHANDRIMA BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>TIRTHANKAR GHOSH</t>
-  </si>
-  <si>
-    <t>ARUP CHOUDHURY (PULAK)</t>
-  </si>
-  <si>
-    <t>SAYANTIKA BANERJEE</t>
-  </si>
-  <si>
-    <t>BRATYABRATA BASU</t>
-  </si>
-  <si>
-    <t>PIYUSH KANODIA</t>
-  </si>
-  <si>
-    <t>SUJIT BOSE</t>
-  </si>
-  <si>
-    <t>ADITI MUNSHI</t>
-  </si>
-  <si>
-    <t>RATHIN GHOSH</t>
   </si>
   <si>
     <t>SABYASACHI DUTTA</t>
@@ -4730,10 +4730,10 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
         <v>321</v>
@@ -4742,10 +4742,10 @@
         <v>601</v>
       </c>
       <c r="F13">
-        <v>131687</v>
+        <v>143242</v>
       </c>
       <c r="G13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H13">
         <f>F13-K13</f>
@@ -4758,10 +4758,10 @@
         <v>602</v>
       </c>
       <c r="K13">
-        <v>67609</v>
+        <v>72822</v>
       </c>
       <c r="L13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M13" t="s">
         <v>912</v>
@@ -4770,10 +4770,10 @@
         <v>605</v>
       </c>
       <c r="O13">
-        <v>6819</v>
+        <v>7301</v>
       </c>
       <c r="P13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -8147,10 +8147,10 @@
         <v>94</v>
       </c>
       <c r="B80">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D80" t="s">
         <v>387</v>
@@ -8159,10 +8159,10 @@
         <v>602</v>
       </c>
       <c r="F80">
-        <v>79193</v>
+        <v>89241</v>
       </c>
       <c r="G80" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H80">
         <f>F80-K80</f>
@@ -8175,10 +8175,10 @@
         <v>601</v>
       </c>
       <c r="K80">
-        <v>71331</v>
+        <v>77787</v>
       </c>
       <c r="L80" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M80" t="s">
         <v>978</v>
@@ -8187,10 +8187,10 @@
         <v>606</v>
       </c>
       <c r="O80">
-        <v>30894</v>
+        <v>34584</v>
       </c>
       <c r="P80" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -8507,7 +8507,7 @@
         <v>17</v>
       </c>
       <c r="C87">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
         <v>394</v>
@@ -8516,10 +8516,10 @@
         <v>601</v>
       </c>
       <c r="F87">
-        <v>117157</v>
+        <v>117941</v>
       </c>
       <c r="G87" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H87">
         <f>F87-K87</f>
@@ -8532,10 +8532,10 @@
         <v>602</v>
       </c>
       <c r="K87">
-        <v>72464</v>
+        <v>72565</v>
       </c>
       <c r="L87" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M87" t="s">
         <v>985</v>
@@ -8544,10 +8544,10 @@
         <v>605</v>
       </c>
       <c r="O87">
-        <v>11511</v>
+        <v>11533</v>
       </c>
       <c r="P87" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -8558,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="C88">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
         <v>395</v>
@@ -8567,10 +8567,10 @@
         <v>601</v>
       </c>
       <c r="F88">
-        <v>126250</v>
+        <v>129046</v>
       </c>
       <c r="G88" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H88">
         <f>F88-K88</f>
@@ -8583,10 +8583,10 @@
         <v>602</v>
       </c>
       <c r="K88">
-        <v>70098</v>
+        <v>71495</v>
       </c>
       <c r="L88" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M88" t="s">
         <v>986</v>
@@ -8595,10 +8595,10 @@
         <v>605</v>
       </c>
       <c r="O88">
-        <v>9998</v>
+        <v>10280</v>
       </c>
       <c r="P88" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -9119,7 +9119,7 @@
         <v>16</v>
       </c>
       <c r="C99">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D99" t="s">
         <v>406</v>
@@ -9128,10 +9128,10 @@
         <v>602</v>
       </c>
       <c r="F99">
-        <v>94449</v>
+        <v>94813</v>
       </c>
       <c r="G99" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H99">
         <f>F99-K99</f>
@@ -9144,10 +9144,10 @@
         <v>601</v>
       </c>
       <c r="K99">
-        <v>78394</v>
+        <v>78796</v>
       </c>
       <c r="L99" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M99" t="s">
         <v>997</v>
@@ -9156,10 +9156,10 @@
         <v>605</v>
       </c>
       <c r="O99">
-        <v>38295</v>
+        <v>38409</v>
       </c>
       <c r="P99" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -9983,10 +9983,10 @@
         <v>130</v>
       </c>
       <c r="B116">
+        <v>18</v>
+      </c>
+      <c r="C116">
         <v>17</v>
-      </c>
-      <c r="C116">
-        <v>16</v>
       </c>
       <c r="D116" t="s">
         <v>423</v>
@@ -9995,7 +9995,7 @@
         <v>602</v>
       </c>
       <c r="F116">
-        <v>104324</v>
+        <v>106250</v>
       </c>
       <c r="G116" t="s">
         <v>608</v>
@@ -10011,7 +10011,7 @@
         <v>601</v>
       </c>
       <c r="K116">
-        <v>102250</v>
+        <v>105927</v>
       </c>
       <c r="L116" t="s">
         <v>900</v>
@@ -10023,7 +10023,7 @@
         <v>605</v>
       </c>
       <c r="O116">
-        <v>31654</v>
+        <v>32245</v>
       </c>
       <c r="P116" t="s">
         <v>900</v>
@@ -10139,19 +10139,19 @@
         <v>17</v>
       </c>
       <c r="C119">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
         <v>426</v>
       </c>
       <c r="E119" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F119">
-        <v>86049</v>
+        <v>95995</v>
       </c>
       <c r="G119" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H119">
         <f>F119-K119</f>
@@ -10161,13 +10161,13 @@
         <v>723</v>
       </c>
       <c r="J119" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K119">
-        <v>85076</v>
+        <v>93596</v>
       </c>
       <c r="L119" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M119" t="s">
         <v>1016</v>
@@ -10176,10 +10176,10 @@
         <v>606</v>
       </c>
       <c r="O119">
-        <v>28805</v>
+        <v>35501</v>
       </c>
       <c r="P119" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -11108,7 +11108,7 @@
         <v>18</v>
       </c>
       <c r="C138">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D138" t="s">
         <v>445</v>
@@ -11117,10 +11117,10 @@
         <v>602</v>
       </c>
       <c r="F138">
-        <v>109625</v>
+        <v>120987</v>
       </c>
       <c r="G138" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H138">
         <f>F138-K138</f>
@@ -11133,10 +11133,10 @@
         <v>601</v>
       </c>
       <c r="K138">
-        <v>83820</v>
+        <v>89172</v>
       </c>
       <c r="L138" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M138" t="s">
         <v>1035</v>
@@ -11145,10 +11145,10 @@
         <v>605</v>
       </c>
       <c r="O138">
-        <v>17713</v>
+        <v>19649</v>
       </c>
       <c r="P138" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -11411,10 +11411,10 @@
         <v>158</v>
       </c>
       <c r="B144">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C144">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D144" t="s">
         <v>451</v>
@@ -11423,10 +11423,10 @@
         <v>602</v>
       </c>
       <c r="F144">
-        <v>104847</v>
+        <v>119320</v>
       </c>
       <c r="G144" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H144">
         <f>F144-K144</f>
@@ -11439,10 +11439,10 @@
         <v>601</v>
       </c>
       <c r="K144">
-        <v>68156</v>
+        <v>88054</v>
       </c>
       <c r="L144" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M144" t="s">
         <v>1041</v>
@@ -11451,10 +11451,10 @@
         <v>605</v>
       </c>
       <c r="O144">
-        <v>15777</v>
+        <v>17594</v>
       </c>
       <c r="P144" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -12740,7 +12740,7 @@
         <v>15</v>
       </c>
       <c r="C170">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D170" t="s">
         <v>477</v>
@@ -12749,10 +12749,10 @@
         <v>601</v>
       </c>
       <c r="F170">
-        <v>54588</v>
+        <v>57639</v>
       </c>
       <c r="G170" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H170">
         <f>F170-K170</f>
@@ -12765,10 +12765,10 @@
         <v>602</v>
       </c>
       <c r="K170">
-        <v>39734</v>
+        <v>45642</v>
       </c>
       <c r="L170" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M170" t="s">
         <v>1067</v>
@@ -12777,10 +12777,10 @@
         <v>605</v>
       </c>
       <c r="O170">
-        <v>10831</v>
+        <v>11284</v>
       </c>
       <c r="P170" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -13301,7 +13301,7 @@
         <v>20</v>
       </c>
       <c r="C181">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D181" t="s">
         <v>488</v>
@@ -13310,10 +13310,10 @@
         <v>602</v>
       </c>
       <c r="F181">
-        <v>104617</v>
+        <v>105060</v>
       </c>
       <c r="G181" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H181">
         <f>F181-K181</f>
@@ -13326,10 +13326,10 @@
         <v>601</v>
       </c>
       <c r="K181">
-        <v>93143</v>
+        <v>93744</v>
       </c>
       <c r="L181" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M181" t="s">
         <v>1078</v>
@@ -13338,10 +13338,10 @@
         <v>605</v>
       </c>
       <c r="O181">
-        <v>13907</v>
+        <v>13921</v>
       </c>
       <c r="P181" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -14981,10 +14981,10 @@
         <v>228</v>
       </c>
       <c r="B214">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C214">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D214" t="s">
         <v>520</v>
@@ -14993,10 +14993,10 @@
         <v>601</v>
       </c>
       <c r="F214">
-        <v>120227</v>
+        <v>130088</v>
       </c>
       <c r="G214" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H214">
         <f>F214-K214</f>
@@ -15009,10 +15009,10 @@
         <v>602</v>
       </c>
       <c r="K214">
-        <v>104537</v>
+        <v>110033</v>
       </c>
       <c r="L214" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M214" t="s">
         <v>1111</v>
@@ -15021,10 +15021,10 @@
         <v>605</v>
       </c>
       <c r="O214">
-        <v>4375</v>
+        <v>4645</v>
       </c>
       <c r="P214" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -17684,10 +17684,10 @@
         <v>281</v>
       </c>
       <c r="B267">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C267">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D267" t="s">
         <v>572</v>
@@ -17696,10 +17696,10 @@
         <v>602</v>
       </c>
       <c r="F267">
-        <v>107832</v>
+        <v>112688</v>
       </c>
       <c r="G267" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H267">
         <f>F267-K267</f>
@@ -17712,10 +17712,10 @@
         <v>601</v>
       </c>
       <c r="K267">
-        <v>98625</v>
+        <v>106228</v>
       </c>
       <c r="L267" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M267" t="s">
         <v>1163</v>
@@ -17724,10 +17724,10 @@
         <v>605</v>
       </c>
       <c r="O267">
-        <v>18579</v>
+        <v>19465</v>
       </c>
       <c r="P267" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -19010,10 +19010,10 @@
         <v>307</v>
       </c>
       <c r="B293">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C293">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D293" t="s">
         <v>598</v>
@@ -19022,10 +19022,10 @@
         <v>602</v>
       </c>
       <c r="F293">
-        <v>87827</v>
+        <v>103223</v>
       </c>
       <c r="G293" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H293">
         <f>F293-K293</f>
@@ -19038,10 +19038,10 @@
         <v>601</v>
       </c>
       <c r="K293">
-        <v>56684</v>
+        <v>74925</v>
       </c>
       <c r="L293" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M293" t="s">
         <v>1189</v>
@@ -19050,10 +19050,10 @@
         <v>605</v>
       </c>
       <c r="O293">
-        <v>19796</v>
+        <v>22111</v>
       </c>
       <c r="P293" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -19064,7 +19064,7 @@
         <v>21</v>
       </c>
       <c r="C294">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D294" t="s">
         <v>599</v>
@@ -19073,10 +19073,10 @@
         <v>602</v>
       </c>
       <c r="F294">
-        <v>84854</v>
+        <v>87744</v>
       </c>
       <c r="G294" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H294">
         <f>F294-K294</f>
@@ -19089,10 +19089,10 @@
         <v>601</v>
       </c>
       <c r="K294">
-        <v>69715</v>
+        <v>74298</v>
       </c>
       <c r="L294" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M294" t="s">
         <v>1190</v>
@@ -19101,10 +19101,10 @@
         <v>603</v>
       </c>
       <c r="O294">
-        <v>44425</v>
+        <v>44991</v>
       </c>
       <c r="P294" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="295" spans="1:16">

--- a/WB_Election_Results_2026.xlsx
+++ b/WB_Election_Results_2026.xlsx
@@ -1286,898 +1286,898 @@
     <t>ARIJIT BAKSHI</t>
   </si>
   <si>
+    <t>PIYUSH KANODIA</t>
+  </si>
+  <si>
+    <t>SHARADWAT MUKHERJEE</t>
+  </si>
+  <si>
+    <t>TARUNJYOTI TEWARI</t>
+  </si>
+  <si>
+    <t>RATHIN GHOSH</t>
+  </si>
+  <si>
+    <t>SANKAR CHATTERJEE</t>
+  </si>
+  <si>
+    <t>ANISUR RAHAMAN BIDESH</t>
+  </si>
+  <si>
+    <t>ABDUL MATIN MUHAMMAD</t>
+  </si>
+  <si>
+    <t>USHA RANI MONDAL</t>
+  </si>
+  <si>
+    <t>SANAT SARDAR</t>
+  </si>
+  <si>
+    <t>SURAJIT MITRA (BADAL)</t>
+  </si>
+  <si>
+    <t>MD. TAUSEFFUR RAHMAN</t>
+  </si>
+  <si>
+    <t>REKHA PATRA</t>
+  </si>
+  <si>
+    <t>BIKARNA NASKAR</t>
+  </si>
+  <si>
+    <t>NILIMA MISTRY BISHAL</t>
+  </si>
+  <si>
+    <t>GANESH CHANDRA MONDAL</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR JANA</t>
+  </si>
+  <si>
+    <t>DIPANKAR JANA</t>
+  </si>
+  <si>
+    <t>SUMANTA MANDAL</t>
+  </si>
+  <si>
+    <t>BARNALI DHARA</t>
+  </si>
+  <si>
+    <t>TAPAS MONDAL S/O-SHIBPRASAD MONDAL</t>
+  </si>
+  <si>
+    <t>JOYDEB HALDER S/O - KARTICK CHANDRA HALDER</t>
+  </si>
+  <si>
+    <t>BISWANATH DAS</t>
+  </si>
+  <si>
+    <t>BIVAS SARDAR</t>
+  </si>
+  <si>
+    <t>PARESH RAM DAS</t>
+  </si>
+  <si>
+    <t>MD BAHARUL ISLAM</t>
+  </si>
+  <si>
+    <t>BIMAN BANERJEE</t>
+  </si>
+  <si>
+    <t>SARMISTHA PURKAIT</t>
+  </si>
+  <si>
+    <t>MD. SAMIM AHAMED MOLLA</t>
+  </si>
+  <si>
+    <t>PANNA LAL HALDER</t>
+  </si>
+  <si>
+    <t>ABDUR RAZZAK MOLLA</t>
+  </si>
+  <si>
+    <t>AGNISWAR NASKAR</t>
+  </si>
+  <si>
+    <t>DILIP MONDAL</t>
+  </si>
+  <si>
+    <t>RUPA GANGULY</t>
+  </si>
+  <si>
+    <t>MD NAWSAD SIDDIQUE</t>
+  </si>
+  <si>
+    <t>AHMED JAVED KHAN</t>
+  </si>
+  <si>
+    <t>SARBORI MUKHERJEE</t>
+  </si>
+  <si>
+    <t>DEBASISH DHAR</t>
+  </si>
+  <si>
+    <t>PAPIA ADHIKARY</t>
+  </si>
+  <si>
+    <t>SANKAR SIKDER</t>
+  </si>
+  <si>
+    <t>DR. INDRANIL KHAN</t>
+  </si>
+  <si>
+    <t>SUBHASIS DAS</t>
+  </si>
+  <si>
+    <t>ASHOK KUMAR DEB</t>
+  </si>
+  <si>
+    <t>ABDUL KHALEQUE MOLLA</t>
+  </si>
+  <si>
+    <t>FIRHAD HAKIM</t>
+  </si>
+  <si>
+    <t>ADHIKARI SUVENDU</t>
+  </si>
+  <si>
+    <t>DASGUPTA SWAPAN</t>
+  </si>
+  <si>
+    <t>SOBHANDEB CHATTOPADHYAY</t>
+  </si>
+  <si>
+    <t>BANDYOPADHYAY NAYNA</t>
+  </si>
+  <si>
+    <t>SANDIPAN SAHA</t>
+  </si>
+  <si>
+    <t>KUNAL KUMAR GHOSH</t>
+  </si>
+  <si>
+    <t>VIJAY OJHA</t>
+  </si>
+  <si>
+    <t>PURNIMA CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>TAPAS ROY</t>
+  </si>
+  <si>
+    <t>RITESH TIWARI</t>
+  </si>
+  <si>
+    <t>SANJAY KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>UMESH RAI</t>
+  </si>
+  <si>
+    <t>ARUP ROY</t>
+  </si>
+  <si>
+    <t>RUDRANIL GHOSH</t>
+  </si>
+  <si>
+    <t>NANDITA CHOWDHURY</t>
+  </si>
+  <si>
+    <t>PRIYA PAUL</t>
+  </si>
+  <si>
+    <t>GULSAN MULLICK</t>
+  </si>
+  <si>
+    <t>RITABRATA BANERJEE</t>
+  </si>
+  <si>
+    <t>CHIRAN BERA</t>
+  </si>
+  <si>
+    <t>PULAK ROY</t>
+  </si>
+  <si>
+    <t>DR. HIRANMOY CHATTOPADHYAYA (HIRAAN)</t>
+  </si>
+  <si>
+    <t>ARUNAVA SEN</t>
+  </si>
+  <si>
+    <t>AMIT SAMANTA</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR PANJA</t>
+  </si>
+  <si>
+    <t>ANUPAM GHOSH</t>
+  </si>
+  <si>
+    <t>TAPAS MAITY</t>
+  </si>
+  <si>
+    <t>DIPANJAN CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>BHASKAR BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>DILIP SINGH</t>
+  </si>
+  <si>
+    <t>ARUP KUMAR DAS</t>
+  </si>
+  <si>
+    <t>Deepanjan Kumar Guha</t>
+  </si>
+  <si>
+    <t>SUBIR NAG</t>
+  </si>
+  <si>
+    <t>SUMANA SARKAR</t>
+  </si>
+  <si>
+    <t>TUSAR KUMAR MAJUMDAR</t>
+  </si>
+  <si>
+    <t>SWARAJ GHOSH</t>
+  </si>
+  <si>
+    <t>SWATI KHANDOKER</t>
+  </si>
+  <si>
+    <t>PROSENJIT BAG</t>
+  </si>
+  <si>
+    <t>MADHUMITA GHOSH</t>
+  </si>
+  <si>
+    <t>ASIMA PATRA</t>
+  </si>
+  <si>
+    <t>SANTU PAN</t>
+  </si>
+  <si>
+    <t>BIMAN GHOSH</t>
+  </si>
+  <si>
+    <t>BAG HEMANTA</t>
+  </si>
+  <si>
+    <t>PRASANTA DIGAR</t>
+  </si>
+  <si>
+    <t>SUSANTA GHOSH</t>
+  </si>
+  <si>
+    <t>HARE KRISHNA BERA</t>
+  </si>
+  <si>
+    <t>SUBRATA MAITY(RANA)</t>
+  </si>
+  <si>
+    <t>SINTU SENAPATI</t>
+  </si>
+  <si>
+    <t>ASHOKE DINDA</t>
+  </si>
+  <si>
+    <t>KHANRA NIRMAL</t>
+  </si>
+  <si>
+    <t>SUBHAS CHANDRA PANJA</t>
+  </si>
+  <si>
+    <t>PRADIP KUMAR BIJALI</t>
+  </si>
+  <si>
+    <t>PIJUSH KANTI DAS</t>
+  </si>
+  <si>
+    <t>TAPAN MAITY</t>
+  </si>
+  <si>
+    <t>SUMITA SINHA</t>
+  </si>
+  <si>
+    <t>SANTANU PRAMANIK</t>
+  </si>
+  <si>
+    <t>SUBRATA PAIK</t>
+  </si>
+  <si>
+    <t>DR. CHANDRA SEKHAR MONDAL</t>
+  </si>
+  <si>
+    <t>ADHIKARI DIBYENDU</t>
+  </si>
+  <si>
+    <t>AJIT KUMAR JANA</t>
+  </si>
+  <si>
+    <t>AMIYA KISKU</t>
+  </si>
+  <si>
+    <t>RAJESH MAHATA</t>
+  </si>
+  <si>
+    <t>LAKSHMI KANTA SAU</t>
+  </si>
+  <si>
+    <t>BHADRA HEMRAM</t>
+  </si>
+  <si>
+    <t>DILIP GHOSH</t>
+  </si>
+  <si>
+    <t>GIRI RAMAPRASAD</t>
+  </si>
+  <si>
+    <t>AMAL KUMAR PANDA</t>
+  </si>
+  <si>
+    <t>SWAGATA MANNA</t>
+  </si>
+  <si>
+    <t>DINEN ROY</t>
+  </si>
+  <si>
+    <t>SUBHASHIS OM</t>
+  </si>
+  <si>
+    <t>TAPAN KUMAR DUTTA</t>
+  </si>
+  <si>
+    <t>SITAL KAPAT</t>
+  </si>
+  <si>
+    <t>SUKANTA DOLUI</t>
+  </si>
+  <si>
+    <t>PRADIP LODHA</t>
+  </si>
+  <si>
+    <t>BIMAN MAHATA</t>
+  </si>
+  <si>
+    <t>SEULI SAHA</t>
+  </si>
+  <si>
+    <t>SANKAR KUMAR GUCHHAIT</t>
+  </si>
+  <si>
+    <t>DR. PRANAT TUDU</t>
+  </si>
+  <si>
+    <t>LABSEN BASKEY</t>
+  </si>
+  <si>
+    <t>JALADHAR MAHATO</t>
+  </si>
+  <si>
+    <t>RAHIDAS MAHATO</t>
+  </si>
+  <si>
+    <t>BISWAJIT MAHATO</t>
+  </si>
+  <si>
+    <t>SUDIP KUMAR MUKHERJEE</t>
+  </si>
+  <si>
+    <t>MAYNA MURMU</t>
+  </si>
+  <si>
+    <t>KAMALA KANTA HANSDA</t>
+  </si>
+  <si>
+    <t>NADIAR CHAND BOURI</t>
+  </si>
+  <si>
+    <t>MAMONI BAURI</t>
+  </si>
+  <si>
+    <t>CHANDANA BAURI</t>
+  </si>
+  <si>
+    <t>SATYANARAYAN MUKHOPADHYAY</t>
+  </si>
+  <si>
+    <t>KSHUDIRAM TUDU</t>
+  </si>
+  <si>
+    <t>KSHETRAMOHAN HANSDA</t>
+  </si>
+  <si>
+    <t>SOUVIK PATRA</t>
+  </si>
+  <si>
+    <t>NILADRI SEKHAR DANA</t>
+  </si>
+  <si>
+    <t>BILLESWAR SINHA</t>
+  </si>
+  <si>
+    <t>AMARNATH SHAKHA</t>
+  </si>
+  <si>
+    <t>SHUKLA CHATTERJEE</t>
+  </si>
+  <si>
+    <t>LAKSHMI KANTA MAJUMDAR</t>
+  </si>
+  <si>
+    <t>NIRMAL KUMAR DHARA</t>
+  </si>
+  <si>
+    <t>DIBAKAR GHARAMI</t>
+  </si>
+  <si>
+    <t>NABIN CHANDRA BAG</t>
+  </si>
+  <si>
+    <t>MOUMITA BISWAS MISRA</t>
+  </si>
+  <si>
+    <t>SUBHASH PATRA</t>
+  </si>
+  <si>
+    <t>ARUN HALDER</t>
+  </si>
+  <si>
+    <t>SAIKAT PANJA</t>
+  </si>
+  <si>
+    <t>SIDDHARTHA MAJUMDAR</t>
+  </si>
+  <si>
+    <t>MANAB GUHA</t>
+  </si>
+  <si>
+    <t>NISITH KUMAR MALIK</t>
+  </si>
+  <si>
+    <t>KARFA SOUMEN</t>
+  </si>
+  <si>
+    <t>PRAN KRISHNA TAPADAR</t>
+  </si>
+  <si>
+    <t>GOPAL CHATTOPADHYAY</t>
+  </si>
+  <si>
+    <t>KRISHNA GHOSH</t>
+  </si>
+  <si>
+    <t>ANADI GHOSH</t>
+  </si>
+  <si>
+    <t>SHISHIR GHOSH</t>
+  </si>
+  <si>
+    <t>KALITA MAJI</t>
+  </si>
+  <si>
+    <t>RAJU PATRA</t>
+  </si>
+  <si>
+    <t>JITENDRA KUMAR TEWARI</t>
+  </si>
+  <si>
+    <t>CHANDRA SEKHAR BANERJEE</t>
+  </si>
+  <si>
+    <t>LAKSHMAN CHANDRA GHORUI</t>
+  </si>
+  <si>
+    <t>PARTHA GHOSH</t>
+  </si>
+  <si>
+    <t>DR. BIJAN MUKHERJEE</t>
+  </si>
+  <si>
+    <t>AGNIMITRA PAUL</t>
+  </si>
+  <si>
+    <t>KRISHNENDU MUKHERJEE</t>
+  </si>
+  <si>
+    <t>AJAY KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>ARIJIT ROY</t>
+  </si>
+  <si>
+    <t>ANUP KUMAR SAHA</t>
+  </si>
+  <si>
+    <t>JAGANNATH CHATTOPADHYAY</t>
+  </si>
+  <si>
+    <t>CHANDRANATH SINHA</t>
+  </si>
+  <si>
+    <t>BIDHAN CHANDRA MAJHI</t>
+  </si>
+  <si>
+    <t>DEBASIS OJHA (HAKU DA)</t>
+  </si>
+  <si>
+    <t>KRISHNA KANTA SAHA</t>
+  </si>
+  <si>
+    <t>DUDH KUMAR MONDAL</t>
+  </si>
+  <si>
+    <t>DHRUBA SAHA</t>
+  </si>
+  <si>
+    <t>FAYEZUL HAQUE (KAJAL SK)</t>
+  </si>
+  <si>
+    <t>RAJENDRA PRASAD SINGH(RAJU SINGH)</t>
+  </si>
+  <si>
+    <t>DR. MOSARRAF HOSSAIN</t>
+  </si>
+  <si>
+    <t>Bharatiya Janata Party</t>
+  </si>
+  <si>
+    <t>All India Trinamool Congress</t>
+  </si>
+  <si>
+    <t>Indian National Congress</t>
+  </si>
+  <si>
+    <t>Aam Janata Unnayan party</t>
+  </si>
+  <si>
+    <t>Communist Party of India (Marxist)</t>
+  </si>
+  <si>
+    <t>All India Secular Front</t>
+  </si>
+  <si>
+    <t>Won</t>
+  </si>
+  <si>
+    <t>Leading</t>
+  </si>
+  <si>
+    <t>ADHIKARY PARESH CHANDRA</t>
+  </si>
+  <si>
+    <t>DR. SABLU BARMAN</t>
+  </si>
+  <si>
+    <t>PARTHA PRATIM RAY</t>
+  </si>
+  <si>
+    <t>AVIJIT DE BHOWMIK</t>
+  </si>
+  <si>
+    <t>HARIHAR DAS</t>
+  </si>
+  <si>
+    <t>ASHUTOSH BARMA</t>
+  </si>
+  <si>
+    <t>UDAYAN GUHA</t>
+  </si>
+  <si>
+    <t>SAILENDRA NATH BARMA</t>
+  </si>
+  <si>
+    <t>SHIBSANKAR PAUL</t>
+  </si>
+  <si>
+    <t>RAJEEV TIRKEY</t>
+  </si>
+  <si>
+    <t>BIRENDRA BARA (ORAON)</t>
+  </si>
+  <si>
+    <t>SUMAN KANJILAL</t>
+  </si>
+  <si>
+    <t>SUBHASH CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>JAYPRAKASH TOPPO</t>
+  </si>
+  <si>
+    <t>NIRMAL CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>RAMMOHAN RAY</t>
+  </si>
+  <si>
+    <t>KRISHNA DAS</t>
+  </si>
+  <si>
+    <t>SWAPNA BARMAN</t>
+  </si>
+  <si>
+    <t>RANJAN SIL SHARMA</t>
+  </si>
+  <si>
+    <t>BULU CHIK BARAIK</t>
+  </si>
+  <si>
+    <t>SANJAY KUJUR</t>
+  </si>
+  <si>
+    <t>RUDEN SADA LEPCHA</t>
+  </si>
+  <si>
+    <t>BIJOY KUMAR RAI</t>
+  </si>
+  <si>
+    <t>AMAR LAMA</t>
+  </si>
+  <si>
+    <t>SHANKAR MALAKAR</t>
+  </si>
+  <si>
+    <t>GOUTAM DEB</t>
+  </si>
+  <si>
+    <t>REENA TOPNO EKKA</t>
+  </si>
+  <si>
+    <t>SANKAR ADHIKARI</t>
+  </si>
+  <si>
+    <t>CHITRAJIT ROY</t>
+  </si>
+  <si>
+    <t>SARAJIT BISWAS</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR JAIN</t>
+  </si>
+  <si>
+    <t>GOUTAM PAUL</t>
+  </si>
+  <si>
+    <t>SATYAJIT BARMAN</t>
+  </si>
+  <si>
+    <t>NITAI BAISHYA</t>
+  </si>
+  <si>
+    <t>KRISHNA KALYANI</t>
+  </si>
+  <si>
+    <t>SABITA BARMAN</t>
+  </si>
+  <si>
+    <t>REKHA ROY</t>
+  </si>
+  <si>
+    <t>SUBHENDU SARKAR</t>
+  </si>
+  <si>
+    <t>ARPITA GHOSH</t>
+  </si>
+  <si>
+    <t>CHINTAMANI BIHA</t>
+  </si>
+  <si>
+    <t>Goutam Das</t>
+  </si>
+  <si>
+    <t>DEBABRATA MAJUMDER</t>
+  </si>
+  <si>
+    <t>AMAL KISKU</t>
+  </si>
+  <si>
+    <t>PRASENJIT DAS</t>
+  </si>
+  <si>
+    <t>RATAN DAS</t>
+  </si>
+  <si>
+    <t>MAUSAM B NOOR</t>
+  </si>
+  <si>
+    <t>ABISHEK SINGHANIA</t>
+  </si>
+  <si>
+    <t>KABITA MANDAL</t>
+  </si>
+  <si>
+    <t>LIPIKA BARMAN GHOSH</t>
+  </si>
+  <si>
+    <t>ASIS KUNDU (PATA)</t>
+  </si>
+  <si>
+    <t>NIBARAN GHOSH</t>
+  </si>
+  <si>
+    <t>ABDUL HANNAN</t>
+  </si>
+  <si>
+    <t>CHANDANA SARKAR</t>
+  </si>
+  <si>
+    <t>SUNIL CHOWDHURI</t>
+  </si>
+  <si>
+    <t>MD NAJME ALAM</t>
+  </si>
+  <si>
+    <t>MAHABIR GHOSH</t>
+  </si>
+  <si>
+    <t>JAKIR HOSSAIN</t>
+  </si>
+  <si>
+    <t>NASIR SAIKH</t>
+  </si>
+  <si>
+    <t>TAPAS KUMAR CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>TOUHIDUR RAHAMAN SUMAN</t>
+  </si>
+  <si>
+    <t>MAHAMUDAL HASAN</t>
+  </si>
+  <si>
+    <t>ABDUL SOUMIK HOSSAIN</t>
+  </si>
+  <si>
+    <t>SHAONI SINGHA ROY</t>
+  </si>
+  <si>
+    <t>PRONAB CHANDRA DAS</t>
+  </si>
+  <si>
+    <t>ASHIS MARJIT</t>
+  </si>
+  <si>
+    <t>PROTIMA RAJAK</t>
+  </si>
+  <si>
+    <t>APURBA SARKAR (DAVID)</t>
+  </si>
+  <si>
+    <t>ANAMIKA GHOSH</t>
+  </si>
+  <si>
+    <t>BAPAN GHOSH</t>
+  </si>
+  <si>
+    <t>RABIUL ALAM CHOWDHURY</t>
+  </si>
+  <si>
+    <t>ADHIR RANJAN CHOWDHURY</t>
+  </si>
+  <si>
+    <t>BIJOY SEKH</t>
+  </si>
+  <si>
+    <t>RANA MANDAL</t>
+  </si>
+  <si>
+    <t>IANUS ALI SARKAR</t>
+  </si>
+  <si>
+    <t>SOHAM CHAKRABORTY</t>
+  </si>
+  <si>
+    <t>DILIP KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>ANIMA DUTTA</t>
+  </si>
+  <si>
+    <t>KALLOL KHAN</t>
+  </si>
+  <si>
+    <t>SAIKAT SARKAR</t>
+  </si>
+  <si>
+    <t>SOMNATH DUTTA</t>
+  </si>
+  <si>
+    <t>PUNDARIKAKSHYA SAHA</t>
+  </si>
+  <si>
+    <t>UJJAL BISWAS</t>
+  </si>
+  <si>
+    <t>BRAJAKISHORE GOSWAMI</t>
+  </si>
+  <si>
+    <t>TAPAS KUMAR GHOSH</t>
+  </si>
+  <si>
+    <t>SAMIR KUMAR PODDAR</t>
+  </si>
+  <si>
+    <t>BARNALI DEY ROY</t>
+  </si>
+  <si>
+    <t>SOUGATA KUMAR BURMAN</t>
+  </si>
+  <si>
+    <t>SUBHANKAR SINGHA (JISHU)</t>
+  </si>
+  <si>
+    <t>DR. ATINDRA NATH MONDAL</t>
+  </si>
+  <si>
+    <t>DR. RAJIB BISWAS.</t>
+  </si>
+  <si>
+    <t>MADHUPARNA THAKUR</t>
+  </si>
+  <si>
+    <t>BISWAJIT DAS</t>
+  </si>
+  <si>
+    <t>RITUPARNA ADDHYA</t>
+  </si>
+  <si>
+    <t>NAROTTAM BISWAS</t>
+  </si>
+  <si>
+    <t>TARAK SAHA</t>
+  </si>
+  <si>
+    <t>SUKRITI KUMAR SARKAR</t>
+  </si>
+  <si>
+    <t>JYOTI PRIYA MALLICK</t>
+  </si>
+  <si>
+    <t>NARAYAN GOSWAMI</t>
+  </si>
+  <si>
+    <t>ARINDAM DEY</t>
+  </si>
+  <si>
+    <t>SUBODH ADHIKARY</t>
+  </si>
+  <si>
+    <t>SANAT DEY</t>
+  </si>
+  <si>
+    <t>AMIT GUPTA</t>
+  </si>
+  <si>
+    <t>SOMENATH SHYAM ICHINI</t>
+  </si>
+  <si>
+    <t>TRINANKUR BHATTACHARJEE</t>
+  </si>
+  <si>
+    <t>RAJ CHAKRABORTY (RAJU)</t>
+  </si>
+  <si>
+    <t>DEVADEEP PUROHIT</t>
+  </si>
+  <si>
+    <t>CHANDRIMA BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>TIRTHANKAR GHOSH</t>
+  </si>
+  <si>
+    <t>ARUP CHOUDHURY (PULAK)</t>
+  </si>
+  <si>
+    <t>SAYANTIKA BANERJEE</t>
+  </si>
+  <si>
+    <t>BRATYABRATA BASU</t>
+  </si>
+  <si>
     <t>TAPASH CHATTERJEE</t>
-  </si>
-  <si>
-    <t>SHARADWAT MUKHERJEE</t>
-  </si>
-  <si>
-    <t>TARUNJYOTI TEWARI</t>
-  </si>
-  <si>
-    <t>RATHIN GHOSH</t>
-  </si>
-  <si>
-    <t>SANKAR CHATTERJEE</t>
-  </si>
-  <si>
-    <t>ANISUR RAHAMAN BIDESH</t>
-  </si>
-  <si>
-    <t>ABDUL MATIN MUHAMMAD</t>
-  </si>
-  <si>
-    <t>USHA RANI MONDAL</t>
-  </si>
-  <si>
-    <t>SANAT SARDAR</t>
-  </si>
-  <si>
-    <t>SURAJIT MITRA (BADAL)</t>
-  </si>
-  <si>
-    <t>MD. TAUSEFFUR RAHMAN</t>
-  </si>
-  <si>
-    <t>REKHA PATRA</t>
-  </si>
-  <si>
-    <t>BIKARNA NASKAR</t>
-  </si>
-  <si>
-    <t>NILIMA MISTRY BISHAL</t>
-  </si>
-  <si>
-    <t>GANESH CHANDRA MONDAL</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR JANA</t>
-  </si>
-  <si>
-    <t>DIPANKAR JANA</t>
-  </si>
-  <si>
-    <t>SUMANTA MANDAL</t>
-  </si>
-  <si>
-    <t>BARNALI DHARA</t>
-  </si>
-  <si>
-    <t>TAPAS MONDAL S/O-SHIBPRASAD MONDAL</t>
-  </si>
-  <si>
-    <t>JOYDEB HALDER S/O - KARTICK CHANDRA HALDER</t>
-  </si>
-  <si>
-    <t>BISWANATH DAS</t>
-  </si>
-  <si>
-    <t>BIVAS SARDAR</t>
-  </si>
-  <si>
-    <t>PARESH RAM DAS</t>
-  </si>
-  <si>
-    <t>MD BAHARUL ISLAM</t>
-  </si>
-  <si>
-    <t>BIMAN BANERJEE</t>
-  </si>
-  <si>
-    <t>SARMISTHA PURKAIT</t>
-  </si>
-  <si>
-    <t>MD. SAMIM AHAMED MOLLA</t>
-  </si>
-  <si>
-    <t>PANNA LAL HALDER</t>
-  </si>
-  <si>
-    <t>ABDUR RAZZAK MOLLA</t>
-  </si>
-  <si>
-    <t>AGNISWAR NASKAR</t>
-  </si>
-  <si>
-    <t>DILIP MONDAL</t>
-  </si>
-  <si>
-    <t>RUPA GANGULY</t>
-  </si>
-  <si>
-    <t>MD NAWSAD SIDDIQUE</t>
-  </si>
-  <si>
-    <t>AHMED JAVED KHAN</t>
-  </si>
-  <si>
-    <t>SARBORI MUKHERJEE</t>
-  </si>
-  <si>
-    <t>DEBASISH DHAR</t>
-  </si>
-  <si>
-    <t>PAPIA ADHIKARY</t>
-  </si>
-  <si>
-    <t>SANKAR SIKDER</t>
-  </si>
-  <si>
-    <t>DR. INDRANIL KHAN</t>
-  </si>
-  <si>
-    <t>SUBHASIS DAS</t>
-  </si>
-  <si>
-    <t>ASHOK KUMAR DEB</t>
-  </si>
-  <si>
-    <t>ABDUL KHALEQUE MOLLA</t>
-  </si>
-  <si>
-    <t>FIRHAD HAKIM</t>
-  </si>
-  <si>
-    <t>ADHIKARI SUVENDU</t>
-  </si>
-  <si>
-    <t>DASGUPTA SWAPAN</t>
-  </si>
-  <si>
-    <t>SOBHANDEB CHATTOPADHYAY</t>
-  </si>
-  <si>
-    <t>BANDYOPADHYAY NAYNA</t>
-  </si>
-  <si>
-    <t>SANDIPAN SAHA</t>
-  </si>
-  <si>
-    <t>KUNAL KUMAR GHOSH</t>
-  </si>
-  <si>
-    <t>VIJAY OJHA</t>
-  </si>
-  <si>
-    <t>PURNIMA CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>TAPAS ROY</t>
-  </si>
-  <si>
-    <t>RITESH TIWARI</t>
-  </si>
-  <si>
-    <t>SANJAY KUMAR SINGH</t>
-  </si>
-  <si>
-    <t>UMESH RAI</t>
-  </si>
-  <si>
-    <t>ARUP ROY</t>
-  </si>
-  <si>
-    <t>RUDRANIL GHOSH</t>
-  </si>
-  <si>
-    <t>NANDITA CHOWDHURY</t>
-  </si>
-  <si>
-    <t>PRIYA PAUL</t>
-  </si>
-  <si>
-    <t>GULSAN MULLICK</t>
-  </si>
-  <si>
-    <t>RITABRATA BANERJEE</t>
-  </si>
-  <si>
-    <t>CHIRAN BERA</t>
-  </si>
-  <si>
-    <t>PULAK ROY</t>
-  </si>
-  <si>
-    <t>DR. HIRANMOY CHATTOPADHYAYA (HIRAAN)</t>
-  </si>
-  <si>
-    <t>ARUNAVA SEN</t>
-  </si>
-  <si>
-    <t>AMIT SAMANTA</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR PANJA</t>
-  </si>
-  <si>
-    <t>ANUPAM GHOSH</t>
-  </si>
-  <si>
-    <t>TAPAS MAITY</t>
-  </si>
-  <si>
-    <t>DIPANJAN CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>BHASKAR BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>DILIP SINGH</t>
-  </si>
-  <si>
-    <t>ARUP KUMAR DAS</t>
-  </si>
-  <si>
-    <t>Deepanjan Kumar Guha</t>
-  </si>
-  <si>
-    <t>SUBIR NAG</t>
-  </si>
-  <si>
-    <t>SUMANA SARKAR</t>
-  </si>
-  <si>
-    <t>TUSAR KUMAR MAJUMDAR</t>
-  </si>
-  <si>
-    <t>SWARAJ GHOSH</t>
-  </si>
-  <si>
-    <t>SWATI KHANDOKER</t>
-  </si>
-  <si>
-    <t>PROSENJIT BAG</t>
-  </si>
-  <si>
-    <t>MADHUMITA GHOSH</t>
-  </si>
-  <si>
-    <t>ASIMA PATRA</t>
-  </si>
-  <si>
-    <t>SANTU PAN</t>
-  </si>
-  <si>
-    <t>BIMAN GHOSH</t>
-  </si>
-  <si>
-    <t>BAG HEMANTA</t>
-  </si>
-  <si>
-    <t>PRASANTA DIGAR</t>
-  </si>
-  <si>
-    <t>SUSANTA GHOSH</t>
-  </si>
-  <si>
-    <t>HARE KRISHNA BERA</t>
-  </si>
-  <si>
-    <t>SUBRATA MAITY(RANA)</t>
-  </si>
-  <si>
-    <t>SINTU SENAPATI</t>
-  </si>
-  <si>
-    <t>ASHOKE DINDA</t>
-  </si>
-  <si>
-    <t>KHANRA NIRMAL</t>
-  </si>
-  <si>
-    <t>SUBHAS CHANDRA PANJA</t>
-  </si>
-  <si>
-    <t>PRADIP KUMAR BIJALI</t>
-  </si>
-  <si>
-    <t>PIJUSH KANTI DAS</t>
-  </si>
-  <si>
-    <t>TAPAN MAITY</t>
-  </si>
-  <si>
-    <t>SUMITA SINHA</t>
-  </si>
-  <si>
-    <t>SANTANU PRAMANIK</t>
-  </si>
-  <si>
-    <t>SUBRATA PAIK</t>
-  </si>
-  <si>
-    <t>DR. CHANDRA SEKHAR MONDAL</t>
-  </si>
-  <si>
-    <t>ADHIKARI DIBYENDU</t>
-  </si>
-  <si>
-    <t>AJIT KUMAR JANA</t>
-  </si>
-  <si>
-    <t>AMIYA KISKU</t>
-  </si>
-  <si>
-    <t>RAJESH MAHATA</t>
-  </si>
-  <si>
-    <t>LAKSHMI KANTA SAU</t>
-  </si>
-  <si>
-    <t>BHADRA HEMRAM</t>
-  </si>
-  <si>
-    <t>DILIP GHOSH</t>
-  </si>
-  <si>
-    <t>GIRI RAMAPRASAD</t>
-  </si>
-  <si>
-    <t>AMAL KUMAR PANDA</t>
-  </si>
-  <si>
-    <t>SWAGATA MANNA</t>
-  </si>
-  <si>
-    <t>DINEN ROY</t>
-  </si>
-  <si>
-    <t>SUBHASHIS OM</t>
-  </si>
-  <si>
-    <t>TAPAN KUMAR DUTTA</t>
-  </si>
-  <si>
-    <t>SITAL KAPAT</t>
-  </si>
-  <si>
-    <t>SUKANTA DOLUI</t>
-  </si>
-  <si>
-    <t>PRADIP LODHA</t>
-  </si>
-  <si>
-    <t>BIMAN MAHATA</t>
-  </si>
-  <si>
-    <t>SEULI SAHA</t>
-  </si>
-  <si>
-    <t>SANKAR KUMAR GUCHHAIT</t>
-  </si>
-  <si>
-    <t>DR. PRANAT TUDU</t>
-  </si>
-  <si>
-    <t>LABSEN BASKEY</t>
-  </si>
-  <si>
-    <t>JALADHAR MAHATO</t>
-  </si>
-  <si>
-    <t>RAHIDAS MAHATO</t>
-  </si>
-  <si>
-    <t>BISWAJIT MAHATO</t>
-  </si>
-  <si>
-    <t>SUDIP KUMAR MUKHERJEE</t>
-  </si>
-  <si>
-    <t>MAYNA MURMU</t>
-  </si>
-  <si>
-    <t>KAMALA KANTA HANSDA</t>
-  </si>
-  <si>
-    <t>NADIAR CHAND BOURI</t>
-  </si>
-  <si>
-    <t>MAMONI BAURI</t>
-  </si>
-  <si>
-    <t>CHANDANA BAURI</t>
-  </si>
-  <si>
-    <t>SATYANARAYAN MUKHOPADHYAY</t>
-  </si>
-  <si>
-    <t>KSHUDIRAM TUDU</t>
-  </si>
-  <si>
-    <t>KSHETRAMOHAN HANSDA</t>
-  </si>
-  <si>
-    <t>SOUVIK PATRA</t>
-  </si>
-  <si>
-    <t>NILADRI SEKHAR DANA</t>
-  </si>
-  <si>
-    <t>BILLESWAR SINHA</t>
-  </si>
-  <si>
-    <t>AMARNATH SHAKHA</t>
-  </si>
-  <si>
-    <t>SHUKLA CHATTERJEE</t>
-  </si>
-  <si>
-    <t>LAKSHMI KANTA MAJUMDAR</t>
-  </si>
-  <si>
-    <t>NIRMAL KUMAR DHARA</t>
-  </si>
-  <si>
-    <t>DIBAKAR GHARAMI</t>
-  </si>
-  <si>
-    <t>NABIN CHANDRA BAG</t>
-  </si>
-  <si>
-    <t>MOUMITA BISWAS MISRA</t>
-  </si>
-  <si>
-    <t>SUBHASH PATRA</t>
-  </si>
-  <si>
-    <t>ARUN HALDER</t>
-  </si>
-  <si>
-    <t>SAIKAT PANJA</t>
-  </si>
-  <si>
-    <t>SIDDHARTHA MAJUMDAR</t>
-  </si>
-  <si>
-    <t>MANAB GUHA</t>
-  </si>
-  <si>
-    <t>NISITH KUMAR MALIK</t>
-  </si>
-  <si>
-    <t>KARFA SOUMEN</t>
-  </si>
-  <si>
-    <t>PRAN KRISHNA TAPADAR</t>
-  </si>
-  <si>
-    <t>GOPAL CHATTOPADHYAY</t>
-  </si>
-  <si>
-    <t>KRISHNA GHOSH</t>
-  </si>
-  <si>
-    <t>ANADI GHOSH</t>
-  </si>
-  <si>
-    <t>SHISHIR GHOSH</t>
-  </si>
-  <si>
-    <t>KALITA MAJI</t>
-  </si>
-  <si>
-    <t>RAJU PATRA</t>
-  </si>
-  <si>
-    <t>JITENDRA KUMAR TEWARI</t>
-  </si>
-  <si>
-    <t>CHANDRA SEKHAR BANERJEE</t>
-  </si>
-  <si>
-    <t>LAKSHMAN CHANDRA GHORUI</t>
-  </si>
-  <si>
-    <t>PARTHA GHOSH</t>
-  </si>
-  <si>
-    <t>DR. BIJAN MUKHERJEE</t>
-  </si>
-  <si>
-    <t>AGNIMITRA PAUL</t>
-  </si>
-  <si>
-    <t>KRISHNENDU MUKHERJEE</t>
-  </si>
-  <si>
-    <t>AJAY KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>ARIJIT ROY</t>
-  </si>
-  <si>
-    <t>ANUP KUMAR SAHA</t>
-  </si>
-  <si>
-    <t>JAGANNATH CHATTOPADHYAY</t>
-  </si>
-  <si>
-    <t>CHANDRANATH SINHA</t>
-  </si>
-  <si>
-    <t>BIDHAN CHANDRA MAJHI</t>
-  </si>
-  <si>
-    <t>DEBASIS OJHA (HAKU DA)</t>
-  </si>
-  <si>
-    <t>KRISHNA KANTA SAHA</t>
-  </si>
-  <si>
-    <t>DUDH KUMAR MONDAL</t>
-  </si>
-  <si>
-    <t>DHRUBA SAHA</t>
-  </si>
-  <si>
-    <t>FAYEZUL HAQUE (KAJAL SK)</t>
-  </si>
-  <si>
-    <t>RAJENDRA PRASAD SINGH(RAJU SINGH)</t>
-  </si>
-  <si>
-    <t>DR. MOSARRAF HOSSAIN</t>
-  </si>
-  <si>
-    <t>Bharatiya Janata Party</t>
-  </si>
-  <si>
-    <t>All India Trinamool Congress</t>
-  </si>
-  <si>
-    <t>Indian National Congress</t>
-  </si>
-  <si>
-    <t>Aam Janata Unnayan party</t>
-  </si>
-  <si>
-    <t>Communist Party of India (Marxist)</t>
-  </si>
-  <si>
-    <t>All India Secular Front</t>
-  </si>
-  <si>
-    <t>Won</t>
-  </si>
-  <si>
-    <t>Leading</t>
-  </si>
-  <si>
-    <t>ADHIKARY PARESH CHANDRA</t>
-  </si>
-  <si>
-    <t>DR. SABLU BARMAN</t>
-  </si>
-  <si>
-    <t>PARTHA PRATIM RAY</t>
-  </si>
-  <si>
-    <t>AVIJIT DE BHOWMIK</t>
-  </si>
-  <si>
-    <t>HARIHAR DAS</t>
-  </si>
-  <si>
-    <t>ASHUTOSH BARMA</t>
-  </si>
-  <si>
-    <t>UDAYAN GUHA</t>
-  </si>
-  <si>
-    <t>SAILENDRA NATH BARMA</t>
-  </si>
-  <si>
-    <t>SHIBSANKAR PAUL</t>
-  </si>
-  <si>
-    <t>RAJEEV TIRKEY</t>
-  </si>
-  <si>
-    <t>BIRENDRA BARA (ORAON)</t>
-  </si>
-  <si>
-    <t>SUMAN KANJILAL</t>
-  </si>
-  <si>
-    <t>SUBHASH CHANDRA ROY</t>
-  </si>
-  <si>
-    <t>JAYPRAKASH TOPPO</t>
-  </si>
-  <si>
-    <t>NIRMAL CHANDRA ROY</t>
-  </si>
-  <si>
-    <t>RAMMOHAN RAY</t>
-  </si>
-  <si>
-    <t>KRISHNA DAS</t>
-  </si>
-  <si>
-    <t>SWAPNA BARMAN</t>
-  </si>
-  <si>
-    <t>RANJAN SIL SHARMA</t>
-  </si>
-  <si>
-    <t>BULU CHIK BARAIK</t>
-  </si>
-  <si>
-    <t>SANJAY KUJUR</t>
-  </si>
-  <si>
-    <t>RUDEN SADA LEPCHA</t>
-  </si>
-  <si>
-    <t>BIJOY KUMAR RAI</t>
-  </si>
-  <si>
-    <t>AMAR LAMA</t>
-  </si>
-  <si>
-    <t>SHANKAR MALAKAR</t>
-  </si>
-  <si>
-    <t>GOUTAM DEB</t>
-  </si>
-  <si>
-    <t>REENA TOPNO EKKA</t>
-  </si>
-  <si>
-    <t>SANKAR ADHIKARI</t>
-  </si>
-  <si>
-    <t>CHITRAJIT ROY</t>
-  </si>
-  <si>
-    <t>SARAJIT BISWAS</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR JAIN</t>
-  </si>
-  <si>
-    <t>GOUTAM PAUL</t>
-  </si>
-  <si>
-    <t>SATYAJIT BARMAN</t>
-  </si>
-  <si>
-    <t>NITAI BAISHYA</t>
-  </si>
-  <si>
-    <t>KRISHNA KALYANI</t>
-  </si>
-  <si>
-    <t>SABITA BARMAN</t>
-  </si>
-  <si>
-    <t>REKHA ROY</t>
-  </si>
-  <si>
-    <t>SUBHENDU SARKAR</t>
-  </si>
-  <si>
-    <t>ARPITA GHOSH</t>
-  </si>
-  <si>
-    <t>CHINTAMANI BIHA</t>
-  </si>
-  <si>
-    <t>Goutam Das</t>
-  </si>
-  <si>
-    <t>DEBABRATA MAJUMDER</t>
-  </si>
-  <si>
-    <t>AMAL KISKU</t>
-  </si>
-  <si>
-    <t>PRASENJIT DAS</t>
-  </si>
-  <si>
-    <t>RATAN DAS</t>
-  </si>
-  <si>
-    <t>MAUSAM B NOOR</t>
-  </si>
-  <si>
-    <t>ABISHEK SINGHANIA</t>
-  </si>
-  <si>
-    <t>KABITA MANDAL</t>
-  </si>
-  <si>
-    <t>LIPIKA BARMAN GHOSH</t>
-  </si>
-  <si>
-    <t>ASIS KUNDU (PATA)</t>
-  </si>
-  <si>
-    <t>NIBARAN GHOSH</t>
-  </si>
-  <si>
-    <t>ABDUL HANNAN</t>
-  </si>
-  <si>
-    <t>CHANDANA SARKAR</t>
-  </si>
-  <si>
-    <t>SUNIL CHOWDHURI</t>
-  </si>
-  <si>
-    <t>MD NAJME ALAM</t>
-  </si>
-  <si>
-    <t>MAHABIR GHOSH</t>
-  </si>
-  <si>
-    <t>JAKIR HOSSAIN</t>
-  </si>
-  <si>
-    <t>NASIR SAIKH</t>
-  </si>
-  <si>
-    <t>TAPAS KUMAR CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>TOUHIDUR RAHAMAN SUMAN</t>
-  </si>
-  <si>
-    <t>MAHAMUDAL HASAN</t>
-  </si>
-  <si>
-    <t>ABDUL SOUMIK HOSSAIN</t>
-  </si>
-  <si>
-    <t>SHAONI SINGHA ROY</t>
-  </si>
-  <si>
-    <t>PRONAB CHANDRA DAS</t>
-  </si>
-  <si>
-    <t>ASHIS MARJIT</t>
-  </si>
-  <si>
-    <t>PROTIMA RAJAK</t>
-  </si>
-  <si>
-    <t>APURBA SARKAR (DAVID)</t>
-  </si>
-  <si>
-    <t>ANAMIKA GHOSH</t>
-  </si>
-  <si>
-    <t>BAPAN GHOSH</t>
-  </si>
-  <si>
-    <t>RABIUL ALAM CHOWDHURY</t>
-  </si>
-  <si>
-    <t>ADHIR RANJAN CHOWDHURY</t>
-  </si>
-  <si>
-    <t>BIJOY SEKH</t>
-  </si>
-  <si>
-    <t>RANA MANDAL</t>
-  </si>
-  <si>
-    <t>IANUS ALI SARKAR</t>
-  </si>
-  <si>
-    <t>SOHAM CHAKRABORTY</t>
-  </si>
-  <si>
-    <t>DILIP KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>ANIMA DUTTA</t>
-  </si>
-  <si>
-    <t>KALLOL KHAN</t>
-  </si>
-  <si>
-    <t>SAIKAT SARKAR</t>
-  </si>
-  <si>
-    <t>SOMNATH DUTTA</t>
-  </si>
-  <si>
-    <t>PUNDARIKAKSHYA SAHA</t>
-  </si>
-  <si>
-    <t>UJJAL BISWAS</t>
-  </si>
-  <si>
-    <t>BRAJAKISHORE GOSWAMI</t>
-  </si>
-  <si>
-    <t>TAPAS KUMAR GHOSH</t>
-  </si>
-  <si>
-    <t>SAMIR KUMAR PODDAR</t>
-  </si>
-  <si>
-    <t>BARNALI DEY ROY</t>
-  </si>
-  <si>
-    <t>SOUGATA KUMAR BURMAN</t>
-  </si>
-  <si>
-    <t>SUBHANKAR SINGHA (JISHU)</t>
-  </si>
-  <si>
-    <t>DR. ATINDRA NATH MONDAL</t>
-  </si>
-  <si>
-    <t>DR. RAJIB BISWAS.</t>
-  </si>
-  <si>
-    <t>MADHUPARNA THAKUR</t>
-  </si>
-  <si>
-    <t>BISWAJIT DAS</t>
-  </si>
-  <si>
-    <t>RITUPARNA ADDHYA</t>
-  </si>
-  <si>
-    <t>NAROTTAM BISWAS</t>
-  </si>
-  <si>
-    <t>TARAK SAHA</t>
-  </si>
-  <si>
-    <t>SUKRITI KUMAR SARKAR</t>
-  </si>
-  <si>
-    <t>JYOTI PRIYA MALLICK</t>
-  </si>
-  <si>
-    <t>NARAYAN GOSWAMI</t>
-  </si>
-  <si>
-    <t>ARINDAM DEY</t>
-  </si>
-  <si>
-    <t>SUBODH ADHIKARY</t>
-  </si>
-  <si>
-    <t>SANAT DEY</t>
-  </si>
-  <si>
-    <t>AMIT GUPTA</t>
-  </si>
-  <si>
-    <t>SOMENATH SHYAM ICHINI</t>
-  </si>
-  <si>
-    <t>TRINANKUR BHATTACHARJEE</t>
-  </si>
-  <si>
-    <t>RAJ CHAKRABORTY (RAJU)</t>
-  </si>
-  <si>
-    <t>DEVADEEP PUROHIT</t>
-  </si>
-  <si>
-    <t>CHANDRIMA BHATTACHARYA</t>
-  </si>
-  <si>
-    <t>TIRTHANKAR GHOSH</t>
-  </si>
-  <si>
-    <t>ARUP CHOUDHURY (PULAK)</t>
-  </si>
-  <si>
-    <t>SAYANTIKA BANERJEE</t>
-  </si>
-  <si>
-    <t>BRATYABRATA BASU</t>
-  </si>
-  <si>
-    <t>PIYUSH KANODIA</t>
   </si>
   <si>
     <t>SUJIT BOSE</t>
@@ -9986,19 +9986,19 @@
         <v>18</v>
       </c>
       <c r="C116">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D116" t="s">
         <v>423</v>
       </c>
       <c r="E116" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F116">
-        <v>106250</v>
+        <v>106564</v>
       </c>
       <c r="G116" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H116">
         <f>F116-K116</f>
@@ -10008,13 +10008,13 @@
         <v>720</v>
       </c>
       <c r="J116" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K116">
-        <v>105927</v>
+        <v>106248</v>
       </c>
       <c r="L116" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M116" t="s">
         <v>1013</v>
@@ -10023,10 +10023,10 @@
         <v>605</v>
       </c>
       <c r="O116">
-        <v>32245</v>
+        <v>32246</v>
       </c>
       <c r="P116" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="117" spans="1:16">
